--- a/planogram/breira-default/FOR-ALL.xlsx
+++ b/planogram/breira-default/FOR-ALL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sverdlik\Desktop\WORKSPACE\COLUMBUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADB3BA6-6C07-481A-AE57-E1372764C09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287ECEB9-45E1-4E25-B1EB-AC2AE6BD46BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" xr2:uid="{62A603EA-5BBD-476C-B555-DE322FFD4B76}"/>
   </bookViews>
@@ -1406,7 +1406,23 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="177"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
@@ -1495,23 +1511,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="177"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
@@ -1693,17 +1692,17 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B42FE6-343B-4F83-8C87-75AA163AECE2}" name="Table2" displayName="Table2" ref="A2:G213" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A2:G213" xr:uid="{C8B42FE6-343B-4F83-8C87-75AA163AECE2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G213">
-    <sortCondition ref="B2:B213"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A169:G213">
+    <sortCondition ref="G2:G213"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="2" xr3:uid="{2899FD27-9C4F-4A76-BC34-E3378399681D}" name="מחלקה" dataDxfId="6"/>
     <tableColumn id="10" xr3:uid="{F090C2AC-4F62-4BB7-92ED-E19E15C9B3F8}" name="סדר הדפסה" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8D27EFC1-4CCD-4EA6-B70E-C5D20852B119}" name="בי" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{9B0849F3-129A-43F9-9247-D13729C620D2}" name="מיקום" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{EDDE42CC-C936-4028-8824-1CDEA3BE2F62}" name="מקט" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{33A04FA6-060E-492F-A89C-053CB4C02FFC}" name="שם" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{7DFD70C4-42DD-4369-9871-2BAA01B67DF1}" name="משפחה" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{DA08E62A-0D8B-44F0-96AD-81021848C7F1}" name="בי" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{EDDE42CC-C936-4028-8824-1CDEA3BE2F62}" name="מקט" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{33A04FA6-060E-492F-A89C-053CB4C02FFC}" name="שם" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{7DFD70C4-42DD-4369-9871-2BAA01B67DF1}" name="משפחה" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2011,8 +2010,8 @@
   <cols>
     <col min="1" max="1" width="8.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" customWidth="1"/>
-    <col min="4" max="4" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.09765625" customWidth="1"/>
     <col min="5" max="5" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="56.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.3984375" bestFit="1" customWidth="1"/>
@@ -2025,11 +2024,11 @@
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>2</v>
@@ -2049,10 +2048,10 @@
         <v>101</v>
       </c>
       <c r="C3" s="6">
+        <v>101</v>
+      </c>
+      <c r="D3" s="6">
         <v>1</v>
-      </c>
-      <c r="D3" s="6">
-        <v>101</v>
       </c>
       <c r="E3" s="6">
         <v>800</v>
@@ -2071,11 +2070,11 @@
       <c r="B4" s="8">
         <v>102</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
+        <v>102</v>
+      </c>
+      <c r="D4" s="6">
         <v>2</v>
-      </c>
-      <c r="D4" s="6">
-        <v>102</v>
       </c>
       <c r="E4" s="8">
         <v>732</v>
@@ -2095,10 +2094,10 @@
         <v>103</v>
       </c>
       <c r="C5" s="6">
+        <v>103</v>
+      </c>
+      <c r="D5" s="6">
         <v>3</v>
-      </c>
-      <c r="D5" s="6">
-        <v>103</v>
       </c>
       <c r="E5" s="6">
         <v>604</v>
@@ -2117,11 +2116,11 @@
       <c r="B6" s="8">
         <v>104</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
+        <v>104</v>
+      </c>
+      <c r="D6" s="6">
         <v>4</v>
-      </c>
-      <c r="D6" s="6">
-        <v>104</v>
       </c>
       <c r="E6" s="8">
         <v>736</v>
@@ -2141,10 +2140,10 @@
         <v>105</v>
       </c>
       <c r="C7" s="6">
+        <v>105</v>
+      </c>
+      <c r="D7" s="6">
         <v>5</v>
-      </c>
-      <c r="D7" s="6">
-        <v>105</v>
       </c>
       <c r="E7" s="6">
         <v>739</v>
@@ -2163,11 +2162,11 @@
       <c r="B8" s="8">
         <v>106</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
+        <v>106</v>
+      </c>
+      <c r="D8" s="6">
         <v>6</v>
-      </c>
-      <c r="D8" s="6">
-        <v>106</v>
       </c>
       <c r="E8" s="8">
         <v>740</v>
@@ -2187,10 +2186,10 @@
         <v>107</v>
       </c>
       <c r="C9" s="6">
+        <v>108</v>
+      </c>
+      <c r="D9" s="6">
         <v>8</v>
-      </c>
-      <c r="D9" s="6">
-        <v>108</v>
       </c>
       <c r="E9" s="6">
         <v>802</v>
@@ -2209,11 +2208,11 @@
       <c r="B10" s="8">
         <v>108</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
+        <v>107</v>
+      </c>
+      <c r="D10" s="6">
         <v>7</v>
-      </c>
-      <c r="D10" s="6">
-        <v>107</v>
       </c>
       <c r="E10" s="8">
         <v>803</v>
@@ -2233,10 +2232,10 @@
         <v>109</v>
       </c>
       <c r="C11" s="6">
+        <v>110</v>
+      </c>
+      <c r="D11" s="6">
         <v>10</v>
-      </c>
-      <c r="D11" s="6">
-        <v>110</v>
       </c>
       <c r="E11" s="6">
         <v>1191</v>
@@ -2255,11 +2254,11 @@
       <c r="B12" s="8">
         <v>110</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
+        <v>109</v>
+      </c>
+      <c r="D12" s="6">
         <v>9</v>
-      </c>
-      <c r="D12" s="6">
-        <v>109</v>
       </c>
       <c r="E12" s="8">
         <v>1192</v>
@@ -2279,10 +2278,10 @@
         <v>111</v>
       </c>
       <c r="C13" s="6">
+        <v>111</v>
+      </c>
+      <c r="D13" s="6">
         <v>11</v>
-      </c>
-      <c r="D13" s="6">
-        <v>111</v>
       </c>
       <c r="E13" s="6">
         <v>1190</v>
@@ -2301,11 +2300,11 @@
       <c r="B14" s="8">
         <v>112</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
+        <v>112</v>
+      </c>
+      <c r="D14" s="6">
         <v>12</v>
-      </c>
-      <c r="D14" s="6">
-        <v>112</v>
       </c>
       <c r="E14" s="8">
         <v>1193</v>
@@ -2325,10 +2324,10 @@
         <v>113</v>
       </c>
       <c r="C15" s="6">
+        <v>113</v>
+      </c>
+      <c r="D15" s="6">
         <v>13</v>
-      </c>
-      <c r="D15" s="6">
-        <v>113</v>
       </c>
       <c r="E15" s="6">
         <v>1198</v>
@@ -2347,11 +2346,11 @@
       <c r="B16" s="8">
         <v>114</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
+        <v>114</v>
+      </c>
+      <c r="D16" s="6">
         <v>14</v>
-      </c>
-      <c r="D16" s="6">
-        <v>114</v>
       </c>
       <c r="E16" s="8">
         <v>1185</v>
@@ -2371,10 +2370,10 @@
         <v>115</v>
       </c>
       <c r="C17" s="6">
+        <v>115</v>
+      </c>
+      <c r="D17" s="6">
         <v>15</v>
-      </c>
-      <c r="D17" s="6">
-        <v>115</v>
       </c>
       <c r="E17" s="6">
         <v>1187</v>
@@ -2393,11 +2392,11 @@
       <c r="B18" s="8">
         <v>116</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
+        <v>116</v>
+      </c>
+      <c r="D18" s="6">
         <v>16</v>
-      </c>
-      <c r="D18" s="6">
-        <v>116</v>
       </c>
       <c r="E18" s="8">
         <v>1180</v>
@@ -2417,10 +2416,10 @@
         <v>117</v>
       </c>
       <c r="C19" s="6">
+        <v>117</v>
+      </c>
+      <c r="D19" s="6">
         <v>17</v>
-      </c>
-      <c r="D19" s="6">
-        <v>117</v>
       </c>
       <c r="E19" s="6">
         <v>1184</v>
@@ -2439,11 +2438,11 @@
       <c r="B20" s="8">
         <v>118</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="6">
+        <v>118</v>
+      </c>
+      <c r="D20" s="6">
         <v>18</v>
-      </c>
-      <c r="D20" s="6">
-        <v>118</v>
       </c>
       <c r="E20" s="8">
         <v>1182</v>
@@ -2463,10 +2462,10 @@
         <v>119</v>
       </c>
       <c r="C21" s="6">
+        <v>119</v>
+      </c>
+      <c r="D21" s="6">
         <v>19</v>
-      </c>
-      <c r="D21" s="6">
-        <v>119</v>
       </c>
       <c r="E21" s="6">
         <v>1195</v>
@@ -2485,11 +2484,11 @@
       <c r="B22" s="8">
         <v>120</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
+        <v>120</v>
+      </c>
+      <c r="D22" s="6">
         <v>20</v>
-      </c>
-      <c r="D22" s="6">
-        <v>120</v>
       </c>
       <c r="E22" s="8">
         <v>1196</v>
@@ -2509,10 +2508,10 @@
         <v>121</v>
       </c>
       <c r="C23" s="6">
+        <v>121</v>
+      </c>
+      <c r="D23" s="6">
         <v>21</v>
-      </c>
-      <c r="D23" s="6">
-        <v>121</v>
       </c>
       <c r="E23" s="6">
         <v>1197</v>
@@ -2531,11 +2530,11 @@
       <c r="B24" s="8">
         <v>122</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="6">
+        <v>122</v>
+      </c>
+      <c r="D24" s="6">
         <v>22</v>
-      </c>
-      <c r="D24" s="6">
-        <v>122</v>
       </c>
       <c r="E24" s="8">
         <v>1194</v>
@@ -2555,10 +2554,10 @@
         <v>123</v>
       </c>
       <c r="C25" s="6">
+        <v>123</v>
+      </c>
+      <c r="D25" s="6">
         <v>23</v>
-      </c>
-      <c r="D25" s="6">
-        <v>123</v>
       </c>
       <c r="E25" s="6">
         <v>420003</v>
@@ -2577,11 +2576,11 @@
       <c r="B26" s="8">
         <v>124</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
+        <v>124</v>
+      </c>
+      <c r="D26" s="6">
         <v>24</v>
-      </c>
-      <c r="D26" s="6">
-        <v>124</v>
       </c>
       <c r="E26" s="8">
         <v>420004</v>
@@ -2601,10 +2600,10 @@
         <v>125</v>
       </c>
       <c r="C27" s="6">
+        <v>125</v>
+      </c>
+      <c r="D27" s="6">
         <v>25</v>
-      </c>
-      <c r="D27" s="6">
-        <v>125</v>
       </c>
       <c r="E27" s="6">
         <v>420005</v>
@@ -2623,11 +2622,11 @@
       <c r="B28" s="8">
         <v>126</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="6">
+        <v>126</v>
+      </c>
+      <c r="D28" s="6">
         <v>26</v>
-      </c>
-      <c r="D28" s="6">
-        <v>126</v>
       </c>
       <c r="E28" s="8">
         <v>420006</v>
@@ -2647,10 +2646,10 @@
         <v>127</v>
       </c>
       <c r="C29" s="6">
+        <v>127</v>
+      </c>
+      <c r="D29" s="6">
         <v>27</v>
-      </c>
-      <c r="D29" s="6">
-        <v>127</v>
       </c>
       <c r="E29" s="6">
         <v>420007</v>
@@ -2669,11 +2668,11 @@
       <c r="B30" s="8">
         <v>128</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="6">
+        <v>128</v>
+      </c>
+      <c r="D30" s="6">
         <v>28</v>
-      </c>
-      <c r="D30" s="6">
-        <v>128</v>
       </c>
       <c r="E30" s="8">
         <v>420008</v>
@@ -2693,10 +2692,10 @@
         <v>129</v>
       </c>
       <c r="C31" s="6">
+        <v>129</v>
+      </c>
+      <c r="D31" s="6">
         <v>29</v>
-      </c>
-      <c r="D31" s="6">
-        <v>129</v>
       </c>
       <c r="E31" s="6">
         <v>420002</v>
@@ -2715,11 +2714,11 @@
       <c r="B32" s="8">
         <v>130</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="6">
+        <v>130</v>
+      </c>
+      <c r="D32" s="6">
         <v>30</v>
-      </c>
-      <c r="D32" s="6">
-        <v>130</v>
       </c>
       <c r="E32" s="8">
         <v>420001</v>
@@ -2739,10 +2738,10 @@
         <v>131</v>
       </c>
       <c r="C33" s="6">
+        <v>131</v>
+      </c>
+      <c r="D33" s="6">
         <v>31</v>
-      </c>
-      <c r="D33" s="6">
-        <v>131</v>
       </c>
       <c r="E33" s="6">
         <v>818</v>
@@ -2761,11 +2760,11 @@
       <c r="B34" s="8">
         <v>132</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="6">
+        <v>132</v>
+      </c>
+      <c r="D34" s="6">
         <v>32</v>
-      </c>
-      <c r="D34" s="6">
-        <v>132</v>
       </c>
       <c r="E34" s="8">
         <v>815</v>
@@ -2785,10 +2784,10 @@
         <v>133</v>
       </c>
       <c r="C35" s="6">
+        <v>133</v>
+      </c>
+      <c r="D35" s="6">
         <v>33</v>
-      </c>
-      <c r="D35" s="6">
-        <v>133</v>
       </c>
       <c r="E35" s="6">
         <v>816</v>
@@ -2807,11 +2806,11 @@
       <c r="B36" s="8">
         <v>134</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="6">
+        <v>134</v>
+      </c>
+      <c r="D36" s="6">
         <v>34</v>
-      </c>
-      <c r="D36" s="6">
-        <v>134</v>
       </c>
       <c r="E36" s="8">
         <v>817</v>
@@ -2831,10 +2830,10 @@
         <v>135</v>
       </c>
       <c r="C37" s="6">
+        <v>137</v>
+      </c>
+      <c r="D37" s="6">
         <v>37</v>
-      </c>
-      <c r="D37" s="6">
-        <v>137</v>
       </c>
       <c r="E37" s="6">
         <v>1051</v>
@@ -2853,11 +2852,11 @@
       <c r="B38" s="8">
         <v>136</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="6">
+        <v>135</v>
+      </c>
+      <c r="D38" s="6">
         <v>35</v>
-      </c>
-      <c r="D38" s="6">
-        <v>135</v>
       </c>
       <c r="E38" s="8">
         <v>1045</v>
@@ -2877,10 +2876,10 @@
         <v>137</v>
       </c>
       <c r="C39" s="6">
+        <v>136</v>
+      </c>
+      <c r="D39" s="6">
         <v>36</v>
-      </c>
-      <c r="D39" s="6">
-        <v>136</v>
       </c>
       <c r="E39" s="6">
         <v>1046</v>
@@ -2899,11 +2898,11 @@
       <c r="B40" s="8">
         <v>138</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="6">
+        <v>144</v>
+      </c>
+      <c r="D40" s="6">
         <v>44</v>
-      </c>
-      <c r="D40" s="6">
-        <v>144</v>
       </c>
       <c r="E40" s="8">
         <v>1031</v>
@@ -2923,10 +2922,10 @@
         <v>139</v>
       </c>
       <c r="C41" s="6">
+        <v>145</v>
+      </c>
+      <c r="D41" s="6">
         <v>45</v>
-      </c>
-      <c r="D41" s="6">
-        <v>145</v>
       </c>
       <c r="E41" s="6">
         <v>1030</v>
@@ -2945,11 +2944,11 @@
       <c r="B42" s="8">
         <v>140</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="6">
+        <v>146</v>
+      </c>
+      <c r="D42" s="6">
         <v>46</v>
-      </c>
-      <c r="D42" s="6">
-        <v>146</v>
       </c>
       <c r="E42" s="8">
         <v>1032</v>
@@ -2969,10 +2968,10 @@
         <v>141</v>
       </c>
       <c r="C43" s="6">
+        <v>147</v>
+      </c>
+      <c r="D43" s="6">
         <v>47</v>
-      </c>
-      <c r="D43" s="6">
-        <v>147</v>
       </c>
       <c r="E43" s="6">
         <v>1034</v>
@@ -2991,11 +2990,11 @@
       <c r="B44" s="8">
         <v>142</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="6">
+        <v>148</v>
+      </c>
+      <c r="D44" s="6">
         <v>48</v>
-      </c>
-      <c r="D44" s="6">
-        <v>148</v>
       </c>
       <c r="E44" s="8">
         <v>1035</v>
@@ -3015,10 +3014,10 @@
         <v>143</v>
       </c>
       <c r="C45" s="6">
+        <v>149</v>
+      </c>
+      <c r="D45" s="6">
         <v>49</v>
-      </c>
-      <c r="D45" s="6">
-        <v>149</v>
       </c>
       <c r="E45" s="6">
         <v>1036</v>
@@ -3037,11 +3036,11 @@
       <c r="B46" s="8">
         <v>144</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="6">
+        <v>150</v>
+      </c>
+      <c r="D46" s="6">
         <v>50</v>
-      </c>
-      <c r="D46" s="6">
-        <v>150</v>
       </c>
       <c r="E46" s="8">
         <v>1216</v>
@@ -3061,10 +3060,10 @@
         <v>145</v>
       </c>
       <c r="C47" s="6">
+        <v>151</v>
+      </c>
+      <c r="D47" s="6">
         <v>51</v>
-      </c>
-      <c r="D47" s="6">
-        <v>151</v>
       </c>
       <c r="E47" s="6">
         <v>1215</v>
@@ -3083,11 +3082,11 @@
       <c r="B48" s="8">
         <v>146</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="6">
+        <v>152</v>
+      </c>
+      <c r="D48" s="6">
         <v>52</v>
-      </c>
-      <c r="D48" s="6">
-        <v>152</v>
       </c>
       <c r="E48" s="8">
         <v>1214</v>
@@ -3107,10 +3106,10 @@
         <v>147</v>
       </c>
       <c r="C49" s="6">
+        <v>153</v>
+      </c>
+      <c r="D49" s="6">
         <v>53</v>
-      </c>
-      <c r="D49" s="6">
-        <v>153</v>
       </c>
       <c r="E49" s="6">
         <v>1213</v>
@@ -3129,11 +3128,11 @@
       <c r="B50" s="8">
         <v>148</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="6">
+        <v>154</v>
+      </c>
+      <c r="D50" s="6">
         <v>54</v>
-      </c>
-      <c r="D50" s="6">
-        <v>154</v>
       </c>
       <c r="E50" s="8">
         <v>1217</v>
@@ -3153,10 +3152,10 @@
         <v>149</v>
       </c>
       <c r="C51" s="6">
+        <v>155</v>
+      </c>
+      <c r="D51" s="6">
         <v>55</v>
-      </c>
-      <c r="D51" s="6">
-        <v>155</v>
       </c>
       <c r="E51" s="6">
         <v>1218</v>
@@ -3175,11 +3174,11 @@
       <c r="B52" s="8">
         <v>150</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="6">
+        <v>156</v>
+      </c>
+      <c r="D52" s="6">
         <v>56</v>
-      </c>
-      <c r="D52" s="6">
-        <v>156</v>
       </c>
       <c r="E52" s="8">
         <v>1219</v>
@@ -3199,10 +3198,10 @@
         <v>151</v>
       </c>
       <c r="C53" s="6">
+        <v>159</v>
+      </c>
+      <c r="D53" s="6">
         <v>59</v>
-      </c>
-      <c r="D53" s="6">
-        <v>159</v>
       </c>
       <c r="E53" s="6">
         <v>1208</v>
@@ -3221,11 +3220,11 @@
       <c r="B54" s="8">
         <v>152</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="6">
+        <v>160</v>
+      </c>
+      <c r="D54" s="6">
         <v>60</v>
-      </c>
-      <c r="D54" s="6">
-        <v>160</v>
       </c>
       <c r="E54" s="8">
         <v>1211</v>
@@ -3245,10 +3244,10 @@
         <v>153</v>
       </c>
       <c r="C55" s="6">
+        <v>161</v>
+      </c>
+      <c r="D55" s="6">
         <v>61</v>
-      </c>
-      <c r="D55" s="6">
-        <v>161</v>
       </c>
       <c r="E55" s="6">
         <v>1209</v>
@@ -3265,13 +3264,13 @@
         <v>73</v>
       </c>
       <c r="B56" s="8">
+        <v>501</v>
+      </c>
+      <c r="C56" s="6">
         <v>201</v>
       </c>
-      <c r="C56" s="8">
+      <c r="D56" s="6">
         <v>1</v>
-      </c>
-      <c r="D56" s="6">
-        <v>201</v>
       </c>
       <c r="E56" s="8">
         <v>755</v>
@@ -3288,13 +3287,13 @@
         <v>73</v>
       </c>
       <c r="B57" s="6">
+        <v>502</v>
+      </c>
+      <c r="C57" s="6">
         <v>202</v>
       </c>
-      <c r="C57" s="6">
+      <c r="D57" s="6">
         <v>2</v>
-      </c>
-      <c r="D57" s="6">
-        <v>202</v>
       </c>
       <c r="E57" s="6">
         <v>660</v>
@@ -3311,13 +3310,13 @@
         <v>73</v>
       </c>
       <c r="B58" s="8">
+        <v>503</v>
+      </c>
+      <c r="C58" s="6">
         <v>203</v>
       </c>
-      <c r="C58" s="8">
+      <c r="D58" s="6">
         <v>3</v>
-      </c>
-      <c r="D58" s="6">
-        <v>203</v>
       </c>
       <c r="E58" s="8">
         <v>662</v>
@@ -3334,13 +3333,13 @@
         <v>73</v>
       </c>
       <c r="B59" s="6">
+        <v>504</v>
+      </c>
+      <c r="C59" s="6">
         <v>204</v>
       </c>
-      <c r="C59" s="6">
+      <c r="D59" s="6">
         <v>4</v>
-      </c>
-      <c r="D59" s="6">
-        <v>204</v>
       </c>
       <c r="E59" s="6">
         <v>661</v>
@@ -3357,13 +3356,13 @@
         <v>73</v>
       </c>
       <c r="B60" s="8">
+        <v>505</v>
+      </c>
+      <c r="C60" s="6">
         <v>205</v>
       </c>
-      <c r="C60" s="8">
+      <c r="D60" s="6">
         <v>5</v>
-      </c>
-      <c r="D60" s="6">
-        <v>205</v>
       </c>
       <c r="E60" s="8">
         <v>664</v>
@@ -3380,13 +3379,13 @@
         <v>73</v>
       </c>
       <c r="B61" s="6">
+        <v>506</v>
+      </c>
+      <c r="C61" s="6">
         <v>206</v>
       </c>
-      <c r="C61" s="6">
+      <c r="D61" s="6">
         <v>6</v>
-      </c>
-      <c r="D61" s="6">
-        <v>206</v>
       </c>
       <c r="E61" s="6">
         <v>413001</v>
@@ -3403,13 +3402,13 @@
         <v>73</v>
       </c>
       <c r="B62" s="8">
+        <v>507</v>
+      </c>
+      <c r="C62" s="6">
         <v>207</v>
       </c>
-      <c r="C62" s="8">
+      <c r="D62" s="6">
         <v>7</v>
-      </c>
-      <c r="D62" s="6">
-        <v>207</v>
       </c>
       <c r="E62" s="8">
         <v>413002</v>
@@ -3426,13 +3425,13 @@
         <v>73</v>
       </c>
       <c r="B63" s="6">
+        <v>508</v>
+      </c>
+      <c r="C63" s="6">
         <v>208</v>
       </c>
-      <c r="C63" s="6">
+      <c r="D63" s="6">
         <v>8</v>
-      </c>
-      <c r="D63" s="6">
-        <v>208</v>
       </c>
       <c r="E63" s="6">
         <v>413000</v>
@@ -3451,11 +3450,11 @@
       <c r="B64" s="8">
         <v>209</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="6">
+        <v>224</v>
+      </c>
+      <c r="D64" s="6">
         <v>24</v>
-      </c>
-      <c r="D64" s="6">
-        <v>224</v>
       </c>
       <c r="E64" s="8">
         <v>630</v>
@@ -3475,10 +3474,10 @@
         <v>210</v>
       </c>
       <c r="C65" s="6">
+        <v>223</v>
+      </c>
+      <c r="D65" s="6">
         <v>23</v>
-      </c>
-      <c r="D65" s="6">
-        <v>223</v>
       </c>
       <c r="E65" s="6">
         <v>624</v>
@@ -3497,11 +3496,11 @@
       <c r="B66" s="8">
         <v>211</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="6">
+        <v>222</v>
+      </c>
+      <c r="D66" s="6">
         <v>22</v>
-      </c>
-      <c r="D66" s="6">
-        <v>222</v>
       </c>
       <c r="E66" s="8">
         <v>631</v>
@@ -3521,10 +3520,10 @@
         <v>212</v>
       </c>
       <c r="C67" s="6">
+        <v>221</v>
+      </c>
+      <c r="D67" s="6">
         <v>21</v>
-      </c>
-      <c r="D67" s="6">
-        <v>221</v>
       </c>
       <c r="E67" s="6">
         <v>1076</v>
@@ -3543,11 +3542,11 @@
       <c r="B68" s="8">
         <v>213</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="6">
+        <v>220</v>
+      </c>
+      <c r="D68" s="6">
         <v>20</v>
-      </c>
-      <c r="D68" s="6">
-        <v>220</v>
       </c>
       <c r="E68" s="8">
         <v>1077</v>
@@ -3567,10 +3566,10 @@
         <v>214</v>
       </c>
       <c r="C69" s="6">
+        <v>219</v>
+      </c>
+      <c r="D69" s="6">
         <v>19</v>
-      </c>
-      <c r="D69" s="6">
-        <v>219</v>
       </c>
       <c r="E69" s="6">
         <v>659</v>
@@ -3589,11 +3588,11 @@
       <c r="B70" s="8">
         <v>215</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="6">
+        <v>216</v>
+      </c>
+      <c r="D70" s="6">
         <v>16</v>
-      </c>
-      <c r="D70" s="6">
-        <v>216</v>
       </c>
       <c r="E70" s="8">
         <v>1052</v>
@@ -3613,10 +3612,10 @@
         <v>216</v>
       </c>
       <c r="C71" s="6">
+        <v>217</v>
+      </c>
+      <c r="D71" s="6">
         <v>17</v>
-      </c>
-      <c r="D71" s="6">
-        <v>217</v>
       </c>
       <c r="E71" s="6">
         <v>1050</v>
@@ -3635,11 +3634,11 @@
       <c r="B72" s="8">
         <v>217</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="6">
+        <v>218</v>
+      </c>
+      <c r="D72" s="6">
         <v>18</v>
-      </c>
-      <c r="D72" s="6">
-        <v>218</v>
       </c>
       <c r="E72" s="8">
         <v>1053</v>
@@ -3659,10 +3658,10 @@
         <v>218</v>
       </c>
       <c r="C73" s="6">
+        <v>215</v>
+      </c>
+      <c r="D73" s="6">
         <v>15</v>
-      </c>
-      <c r="D73" s="6">
-        <v>215</v>
       </c>
       <c r="E73" s="6">
         <v>1060</v>
@@ -3681,11 +3680,11 @@
       <c r="B74" s="8">
         <v>219</v>
       </c>
-      <c r="C74" s="8">
+      <c r="C74" s="6">
+        <v>214</v>
+      </c>
+      <c r="D74" s="6">
         <v>14</v>
-      </c>
-      <c r="D74" s="6">
-        <v>214</v>
       </c>
       <c r="E74" s="8">
         <v>1062</v>
@@ -3705,10 +3704,10 @@
         <v>220</v>
       </c>
       <c r="C75" s="6">
+        <v>225</v>
+      </c>
+      <c r="D75" s="6">
         <v>25</v>
-      </c>
-      <c r="D75" s="6">
-        <v>225</v>
       </c>
       <c r="E75" s="6">
         <v>677</v>
@@ -3727,11 +3726,11 @@
       <c r="B76" s="8">
         <v>221</v>
       </c>
-      <c r="C76" s="8">
+      <c r="C76" s="6">
+        <v>226</v>
+      </c>
+      <c r="D76" s="6">
         <v>26</v>
-      </c>
-      <c r="D76" s="6">
-        <v>226</v>
       </c>
       <c r="E76" s="8">
         <v>669</v>
@@ -3751,10 +3750,10 @@
         <v>222</v>
       </c>
       <c r="C77" s="6">
+        <v>227</v>
+      </c>
+      <c r="D77" s="6">
         <v>27</v>
-      </c>
-      <c r="D77" s="6">
-        <v>227</v>
       </c>
       <c r="E77" s="6">
         <v>667</v>
@@ -3773,11 +3772,11 @@
       <c r="B78" s="8">
         <v>223</v>
       </c>
-      <c r="C78" s="8">
+      <c r="C78" s="6">
+        <v>228</v>
+      </c>
+      <c r="D78" s="6">
         <v>28</v>
-      </c>
-      <c r="D78" s="6">
-        <v>228</v>
       </c>
       <c r="E78" s="8">
         <v>668</v>
@@ -3797,10 +3796,10 @@
         <v>224</v>
       </c>
       <c r="C79" s="6">
+        <v>229</v>
+      </c>
+      <c r="D79" s="6">
         <v>29</v>
-      </c>
-      <c r="D79" s="6">
-        <v>229</v>
       </c>
       <c r="E79" s="6">
         <v>650</v>
@@ -3819,11 +3818,11 @@
       <c r="B80" s="8">
         <v>225</v>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="6">
+        <v>230</v>
+      </c>
+      <c r="D80" s="6">
         <v>30</v>
-      </c>
-      <c r="D80" s="6">
-        <v>230</v>
       </c>
       <c r="E80" s="8">
         <v>649</v>
@@ -3843,10 +3842,10 @@
         <v>226</v>
       </c>
       <c r="C81" s="6">
+        <v>231</v>
+      </c>
+      <c r="D81" s="6">
         <v>31</v>
-      </c>
-      <c r="D81" s="6">
-        <v>231</v>
       </c>
       <c r="E81" s="6">
         <v>645</v>
@@ -3865,11 +3864,11 @@
       <c r="B82" s="8">
         <v>227</v>
       </c>
-      <c r="C82" s="8">
+      <c r="C82" s="6">
+        <v>232</v>
+      </c>
+      <c r="D82" s="6">
         <v>32</v>
-      </c>
-      <c r="D82" s="6">
-        <v>232</v>
       </c>
       <c r="E82" s="8">
         <v>646</v>
@@ -3889,10 +3888,10 @@
         <v>228</v>
       </c>
       <c r="C83" s="6">
+        <v>233</v>
+      </c>
+      <c r="D83" s="6">
         <v>33</v>
-      </c>
-      <c r="D83" s="6">
-        <v>233</v>
       </c>
       <c r="E83" s="6">
         <v>644</v>
@@ -3911,11 +3910,11 @@
       <c r="B84" s="8">
         <v>229</v>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="6">
+        <v>234</v>
+      </c>
+      <c r="D84" s="6">
         <v>34</v>
-      </c>
-      <c r="D84" s="6">
-        <v>234</v>
       </c>
       <c r="E84" s="8">
         <v>643</v>
@@ -3935,10 +3934,10 @@
         <v>230</v>
       </c>
       <c r="C85" s="6">
+        <v>235</v>
+      </c>
+      <c r="D85" s="6">
         <v>35</v>
-      </c>
-      <c r="D85" s="6">
-        <v>235</v>
       </c>
       <c r="E85" s="6">
         <v>628</v>
@@ -3957,11 +3956,11 @@
       <c r="B86" s="8">
         <v>231</v>
       </c>
-      <c r="C86" s="8">
+      <c r="C86" s="6">
+        <v>237</v>
+      </c>
+      <c r="D86" s="6">
         <v>37</v>
-      </c>
-      <c r="D86" s="6">
-        <v>237</v>
       </c>
       <c r="E86" s="8">
         <v>665</v>
@@ -3981,10 +3980,10 @@
         <v>232</v>
       </c>
       <c r="C87" s="6">
+        <v>238</v>
+      </c>
+      <c r="D87" s="6">
         <v>38</v>
-      </c>
-      <c r="D87" s="6">
-        <v>238</v>
       </c>
       <c r="E87" s="6">
         <v>673</v>
@@ -4003,11 +4002,11 @@
       <c r="B88" s="8">
         <v>233</v>
       </c>
-      <c r="C88" s="8">
+      <c r="C88" s="6">
+        <v>239</v>
+      </c>
+      <c r="D88" s="6">
         <v>39</v>
-      </c>
-      <c r="D88" s="6">
-        <v>239</v>
       </c>
       <c r="E88" s="8">
         <v>670</v>
@@ -4027,10 +4026,10 @@
         <v>234</v>
       </c>
       <c r="C89" s="6">
+        <v>240</v>
+      </c>
+      <c r="D89" s="6">
         <v>40</v>
-      </c>
-      <c r="D89" s="6">
-        <v>240</v>
       </c>
       <c r="E89" s="6">
         <v>672</v>
@@ -4049,11 +4048,11 @@
       <c r="B90" s="8">
         <v>235</v>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="6">
+        <v>241</v>
+      </c>
+      <c r="D90" s="6">
         <v>41</v>
-      </c>
-      <c r="D90" s="6">
-        <v>241</v>
       </c>
       <c r="E90" s="8">
         <v>412202</v>
@@ -4073,10 +4072,10 @@
         <v>236</v>
       </c>
       <c r="C91" s="6">
+        <v>242</v>
+      </c>
+      <c r="D91" s="6">
         <v>42</v>
-      </c>
-      <c r="D91" s="6">
-        <v>242</v>
       </c>
       <c r="E91" s="6">
         <v>412200</v>
@@ -4095,11 +4094,11 @@
       <c r="B92" s="8">
         <v>237</v>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="6">
+        <v>243</v>
+      </c>
+      <c r="D92" s="6">
         <v>43</v>
-      </c>
-      <c r="D92" s="6">
-        <v>243</v>
       </c>
       <c r="E92" s="8">
         <v>412201</v>
@@ -4119,10 +4118,10 @@
         <v>238</v>
       </c>
       <c r="C93" s="6">
+        <v>244</v>
+      </c>
+      <c r="D93" s="6">
         <v>44</v>
-      </c>
-      <c r="D93" s="6">
-        <v>244</v>
       </c>
       <c r="E93" s="6">
         <v>410000</v>
@@ -4141,11 +4140,11 @@
       <c r="B94" s="8">
         <v>239</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="6">
+        <v>245</v>
+      </c>
+      <c r="D94" s="6">
         <v>45</v>
-      </c>
-      <c r="D94" s="6">
-        <v>245</v>
       </c>
       <c r="E94" s="8">
         <v>410001</v>
@@ -4165,10 +4164,10 @@
         <v>240</v>
       </c>
       <c r="C95" s="6">
+        <v>246</v>
+      </c>
+      <c r="D95" s="6">
         <v>46</v>
-      </c>
-      <c r="D95" s="6">
-        <v>246</v>
       </c>
       <c r="E95" s="6">
         <v>410002</v>
@@ -4187,11 +4186,11 @@
       <c r="B96" s="8">
         <v>241</v>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="6">
+        <v>247</v>
+      </c>
+      <c r="D96" s="6">
         <v>47</v>
-      </c>
-      <c r="D96" s="6">
-        <v>247</v>
       </c>
       <c r="E96" s="8">
         <v>410003</v>
@@ -4211,10 +4210,10 @@
         <v>242</v>
       </c>
       <c r="C97" s="6">
+        <v>248</v>
+      </c>
+      <c r="D97" s="6">
         <v>48</v>
-      </c>
-      <c r="D97" s="6">
-        <v>248</v>
       </c>
       <c r="E97" s="6">
         <v>410004</v>
@@ -4233,11 +4232,11 @@
       <c r="B98" s="8">
         <v>243</v>
       </c>
-      <c r="C98" s="8">
+      <c r="C98" s="6">
+        <v>249</v>
+      </c>
+      <c r="D98" s="6">
         <v>49</v>
-      </c>
-      <c r="D98" s="6">
-        <v>249</v>
       </c>
       <c r="E98" s="8">
         <v>411000</v>
@@ -4257,10 +4256,10 @@
         <v>244</v>
       </c>
       <c r="C99" s="6">
+        <v>250</v>
+      </c>
+      <c r="D99" s="6">
         <v>50</v>
-      </c>
-      <c r="D99" s="6">
-        <v>250</v>
       </c>
       <c r="E99" s="6">
         <v>411001</v>
@@ -4279,11 +4278,11 @@
       <c r="B100" s="8">
         <v>245</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="6">
+        <v>251</v>
+      </c>
+      <c r="D100" s="6">
         <v>51</v>
-      </c>
-      <c r="D100" s="6">
-        <v>251</v>
       </c>
       <c r="E100" s="8">
         <v>411500</v>
@@ -4303,10 +4302,10 @@
         <v>246</v>
       </c>
       <c r="C101" s="6">
+        <v>252</v>
+      </c>
+      <c r="D101" s="6">
         <v>52</v>
-      </c>
-      <c r="D101" s="6">
-        <v>252</v>
       </c>
       <c r="E101" s="6">
         <v>412501</v>
@@ -4325,11 +4324,11 @@
       <c r="B102" s="8">
         <v>247</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="6">
+        <v>253</v>
+      </c>
+      <c r="D102" s="6">
         <v>53</v>
-      </c>
-      <c r="D102" s="6">
-        <v>253</v>
       </c>
       <c r="E102" s="8">
         <v>412502</v>
@@ -4349,10 +4348,10 @@
         <v>248</v>
       </c>
       <c r="C103" s="6">
+        <v>254</v>
+      </c>
+      <c r="D103" s="6">
         <v>54</v>
-      </c>
-      <c r="D103" s="6">
-        <v>254</v>
       </c>
       <c r="E103" s="6">
         <v>412500</v>
@@ -4371,11 +4370,11 @@
       <c r="B104" s="8">
         <v>249</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="6">
+        <v>255</v>
+      </c>
+      <c r="D104" s="6">
         <v>55</v>
-      </c>
-      <c r="D104" s="6">
-        <v>255</v>
       </c>
       <c r="E104" s="8">
         <v>413501</v>
@@ -4395,10 +4394,10 @@
         <v>250</v>
       </c>
       <c r="C105" s="6">
+        <v>256</v>
+      </c>
+      <c r="D105" s="6">
         <v>56</v>
-      </c>
-      <c r="D105" s="6">
-        <v>256</v>
       </c>
       <c r="E105" s="6">
         <v>413502</v>
@@ -4417,11 +4416,11 @@
       <c r="B106" s="8">
         <v>251</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="6">
+        <v>257</v>
+      </c>
+      <c r="D106" s="6">
         <v>57</v>
-      </c>
-      <c r="D106" s="6">
-        <v>257</v>
       </c>
       <c r="E106" s="8">
         <v>413500</v>
@@ -4441,10 +4440,10 @@
         <v>252</v>
       </c>
       <c r="C107" s="6">
+        <v>258</v>
+      </c>
+      <c r="D107" s="6">
         <v>58</v>
-      </c>
-      <c r="D107" s="6">
-        <v>258</v>
       </c>
       <c r="E107" s="6">
         <v>413202</v>
@@ -4463,11 +4462,11 @@
       <c r="B108" s="8">
         <v>253</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C108" s="6">
+        <v>259</v>
+      </c>
+      <c r="D108" s="6">
         <v>59</v>
-      </c>
-      <c r="D108" s="6">
-        <v>259</v>
       </c>
       <c r="E108" s="8">
         <v>413201</v>
@@ -4487,10 +4486,10 @@
         <v>254</v>
       </c>
       <c r="C109" s="6">
+        <v>260</v>
+      </c>
+      <c r="D109" s="6">
         <v>60</v>
-      </c>
-      <c r="D109" s="6">
-        <v>260</v>
       </c>
       <c r="E109" s="6">
         <v>413200</v>
@@ -4509,11 +4508,11 @@
       <c r="B110" s="8">
         <v>301</v>
       </c>
-      <c r="C110" s="8">
+      <c r="C110" s="6">
+        <v>309</v>
+      </c>
+      <c r="D110" s="6">
         <v>9</v>
-      </c>
-      <c r="D110" s="6">
-        <v>309</v>
       </c>
       <c r="E110" s="8">
         <v>403007</v>
@@ -4533,10 +4532,10 @@
         <v>302</v>
       </c>
       <c r="C111" s="6">
+        <v>310</v>
+      </c>
+      <c r="D111" s="6">
         <v>10</v>
-      </c>
-      <c r="D111" s="6">
-        <v>310</v>
       </c>
       <c r="E111" s="6">
         <v>403008</v>
@@ -4555,11 +4554,11 @@
       <c r="B112" s="8">
         <v>303</v>
       </c>
-      <c r="C112" s="8">
+      <c r="C112" s="6">
+        <v>311</v>
+      </c>
+      <c r="D112" s="6">
         <v>11</v>
-      </c>
-      <c r="D112" s="6">
-        <v>311</v>
       </c>
       <c r="E112" s="8">
         <v>403004</v>
@@ -4579,10 +4578,10 @@
         <v>304</v>
       </c>
       <c r="C113" s="6">
+        <v>312</v>
+      </c>
+      <c r="D113" s="6">
         <v>12</v>
-      </c>
-      <c r="D113" s="6">
-        <v>312</v>
       </c>
       <c r="E113" s="6">
         <v>403003</v>
@@ -4601,11 +4600,11 @@
       <c r="B114" s="8">
         <v>305</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="6">
+        <v>313</v>
+      </c>
+      <c r="D114" s="6">
         <v>13</v>
-      </c>
-      <c r="D114" s="6">
-        <v>313</v>
       </c>
       <c r="E114" s="8">
         <v>403006</v>
@@ -4625,10 +4624,10 @@
         <v>306</v>
       </c>
       <c r="C115" s="6">
+        <v>314</v>
+      </c>
+      <c r="D115" s="6">
         <v>14</v>
-      </c>
-      <c r="D115" s="6">
-        <v>314</v>
       </c>
       <c r="E115" s="6">
         <v>403002</v>
@@ -4647,11 +4646,11 @@
       <c r="B116" s="8">
         <v>307</v>
       </c>
-      <c r="C116" s="8">
+      <c r="C116" s="6">
+        <v>315</v>
+      </c>
+      <c r="D116" s="6">
         <v>15</v>
-      </c>
-      <c r="D116" s="6">
-        <v>315</v>
       </c>
       <c r="E116" s="8">
         <v>403005</v>
@@ -4671,10 +4670,10 @@
         <v>308</v>
       </c>
       <c r="C117" s="6">
+        <v>316</v>
+      </c>
+      <c r="D117" s="6">
         <v>16</v>
-      </c>
-      <c r="D117" s="6">
-        <v>316</v>
       </c>
       <c r="E117" s="6">
         <v>403001</v>
@@ -4693,11 +4692,11 @@
       <c r="B118" s="8">
         <v>309</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="6">
+        <v>317</v>
+      </c>
+      <c r="D118" s="6">
         <v>17</v>
-      </c>
-      <c r="D118" s="6">
-        <v>317</v>
       </c>
       <c r="E118" s="8">
         <v>1017</v>
@@ -4717,10 +4716,10 @@
         <v>310</v>
       </c>
       <c r="C119" s="6">
+        <v>318</v>
+      </c>
+      <c r="D119" s="6">
         <v>18</v>
-      </c>
-      <c r="D119" s="6">
-        <v>318</v>
       </c>
       <c r="E119" s="6">
         <v>1018</v>
@@ -4739,11 +4738,11 @@
       <c r="B120" s="8">
         <v>311</v>
       </c>
-      <c r="C120" s="8">
+      <c r="C120" s="6">
+        <v>319</v>
+      </c>
+      <c r="D120" s="6">
         <v>19</v>
-      </c>
-      <c r="D120" s="6">
-        <v>319</v>
       </c>
       <c r="E120" s="8">
         <v>1015</v>
@@ -4763,10 +4762,10 @@
         <v>312</v>
       </c>
       <c r="C121" s="6">
+        <v>320</v>
+      </c>
+      <c r="D121" s="6">
         <v>20</v>
-      </c>
-      <c r="D121" s="6">
-        <v>320</v>
       </c>
       <c r="E121" s="6">
         <v>1109</v>
@@ -4785,11 +4784,11 @@
       <c r="B122" s="8">
         <v>313</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="6">
+        <v>321</v>
+      </c>
+      <c r="D122" s="6">
         <v>21</v>
-      </c>
-      <c r="D122" s="6">
-        <v>321</v>
       </c>
       <c r="E122" s="8">
         <v>1122</v>
@@ -4809,10 +4808,10 @@
         <v>314</v>
       </c>
       <c r="C123" s="6">
+        <v>322</v>
+      </c>
+      <c r="D123" s="6">
         <v>22</v>
-      </c>
-      <c r="D123" s="6">
-        <v>322</v>
       </c>
       <c r="E123" s="6">
         <v>1123</v>
@@ -4831,11 +4830,11 @@
       <c r="B124" s="8">
         <v>315</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C124" s="6">
+        <v>323</v>
+      </c>
+      <c r="D124" s="6">
         <v>23</v>
-      </c>
-      <c r="D124" s="6">
-        <v>323</v>
       </c>
       <c r="E124" s="8">
         <v>1124</v>
@@ -4855,10 +4854,10 @@
         <v>316</v>
       </c>
       <c r="C125" s="6">
+        <v>328</v>
+      </c>
+      <c r="D125" s="6">
         <v>28</v>
-      </c>
-      <c r="D125" s="6">
-        <v>328</v>
       </c>
       <c r="E125" s="6">
         <v>1014</v>
@@ -4877,11 +4876,11 @@
       <c r="B126" s="8">
         <v>317</v>
       </c>
-      <c r="C126" s="8">
+      <c r="C126" s="6">
+        <v>329</v>
+      </c>
+      <c r="D126" s="6">
         <v>29</v>
-      </c>
-      <c r="D126" s="6">
-        <v>329</v>
       </c>
       <c r="E126" s="8">
         <v>1012</v>
@@ -4901,10 +4900,10 @@
         <v>318</v>
       </c>
       <c r="C127" s="6">
+        <v>330</v>
+      </c>
+      <c r="D127" s="6">
         <v>30</v>
-      </c>
-      <c r="D127" s="6">
-        <v>330</v>
       </c>
       <c r="E127" s="6">
         <v>1013</v>
@@ -4923,11 +4922,11 @@
       <c r="B128" s="8">
         <v>319</v>
       </c>
-      <c r="C128" s="8">
+      <c r="C128" s="6">
+        <v>331</v>
+      </c>
+      <c r="D128" s="6">
         <v>31</v>
-      </c>
-      <c r="D128" s="6">
-        <v>331</v>
       </c>
       <c r="E128" s="8">
         <v>1049</v>
@@ -4947,10 +4946,10 @@
         <v>320</v>
       </c>
       <c r="C129" s="6">
+        <v>333</v>
+      </c>
+      <c r="D129" s="6">
         <v>33</v>
-      </c>
-      <c r="D129" s="6">
-        <v>333</v>
       </c>
       <c r="E129" s="6">
         <v>1107</v>
@@ -4969,11 +4968,11 @@
       <c r="B130" s="8">
         <v>321</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="6">
+        <v>332</v>
+      </c>
+      <c r="D130" s="6">
         <v>32</v>
-      </c>
-      <c r="D130" s="6">
-        <v>332</v>
       </c>
       <c r="E130" s="8">
         <v>1106</v>
@@ -4993,10 +4992,10 @@
         <v>322</v>
       </c>
       <c r="C131" s="6">
+        <v>334</v>
+      </c>
+      <c r="D131" s="6">
         <v>34</v>
-      </c>
-      <c r="D131" s="6">
-        <v>334</v>
       </c>
       <c r="E131" s="6">
         <v>1005</v>
@@ -5015,11 +5014,11 @@
       <c r="B132" s="8">
         <v>323</v>
       </c>
-      <c r="C132" s="8">
+      <c r="C132" s="6">
+        <v>335</v>
+      </c>
+      <c r="D132" s="6">
         <v>35</v>
-      </c>
-      <c r="D132" s="6">
-        <v>335</v>
       </c>
       <c r="E132" s="8">
         <v>1047</v>
@@ -5039,10 +5038,10 @@
         <v>324</v>
       </c>
       <c r="C133" s="6">
+        <v>336</v>
+      </c>
+      <c r="D133" s="6">
         <v>36</v>
-      </c>
-      <c r="D133" s="6">
-        <v>336</v>
       </c>
       <c r="E133" s="6">
         <v>1048</v>
@@ -5061,11 +5060,11 @@
       <c r="B134" s="8">
         <v>325</v>
       </c>
-      <c r="C134" s="8">
+      <c r="C134" s="6">
+        <v>326</v>
+      </c>
+      <c r="D134" s="6">
         <v>26</v>
-      </c>
-      <c r="D134" s="6">
-        <v>326</v>
       </c>
       <c r="E134" s="8">
         <v>1168</v>
@@ -5085,10 +5084,10 @@
         <v>326</v>
       </c>
       <c r="C135" s="6">
+        <v>324</v>
+      </c>
+      <c r="D135" s="6">
         <v>24</v>
-      </c>
-      <c r="D135" s="6">
-        <v>324</v>
       </c>
       <c r="E135" s="6">
         <v>1166</v>
@@ -5107,11 +5106,11 @@
       <c r="B136" s="8">
         <v>327</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C136" s="6">
+        <v>325</v>
+      </c>
+      <c r="D136" s="6">
         <v>25</v>
-      </c>
-      <c r="D136" s="6">
-        <v>325</v>
       </c>
       <c r="E136" s="8">
         <v>1167</v>
@@ -5131,10 +5130,10 @@
         <v>328</v>
       </c>
       <c r="C137" s="6">
+        <v>337</v>
+      </c>
+      <c r="D137" s="6">
         <v>37</v>
-      </c>
-      <c r="D137" s="6">
-        <v>337</v>
       </c>
       <c r="E137" s="6">
         <v>400001</v>
@@ -5153,11 +5152,11 @@
       <c r="B138" s="8">
         <v>329</v>
       </c>
-      <c r="C138" s="8">
+      <c r="C138" s="6">
+        <v>338</v>
+      </c>
+      <c r="D138" s="6">
         <v>38</v>
-      </c>
-      <c r="D138" s="6">
-        <v>338</v>
       </c>
       <c r="E138" s="8">
         <v>400002</v>
@@ -5177,10 +5176,10 @@
         <v>330</v>
       </c>
       <c r="C139" s="6">
+        <v>339</v>
+      </c>
+      <c r="D139" s="6">
         <v>39</v>
-      </c>
-      <c r="D139" s="6">
-        <v>339</v>
       </c>
       <c r="E139" s="6">
         <v>400003</v>
@@ -5199,11 +5198,11 @@
       <c r="B140" s="8">
         <v>331</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="6">
+        <v>327</v>
+      </c>
+      <c r="D140" s="6">
         <v>27</v>
-      </c>
-      <c r="D140" s="6">
-        <v>327</v>
       </c>
       <c r="E140" s="8">
         <v>1120</v>
@@ -5223,10 +5222,10 @@
         <v>332</v>
       </c>
       <c r="C141" s="6">
+        <v>340</v>
+      </c>
+      <c r="D141" s="6">
         <v>40</v>
-      </c>
-      <c r="D141" s="6">
-        <v>340</v>
       </c>
       <c r="E141" s="6">
         <v>1011</v>
@@ -5245,11 +5244,11 @@
       <c r="B142" s="8">
         <v>333</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="6">
+        <v>341</v>
+      </c>
+      <c r="D142" s="6">
         <v>41</v>
-      </c>
-      <c r="D142" s="6">
-        <v>341</v>
       </c>
       <c r="E142" s="8">
         <v>1165</v>
@@ -5269,10 +5268,10 @@
         <v>334</v>
       </c>
       <c r="C143" s="6">
+        <v>342</v>
+      </c>
+      <c r="D143" s="6">
         <v>42</v>
-      </c>
-      <c r="D143" s="6">
-        <v>342</v>
       </c>
       <c r="E143" s="6">
         <v>1157</v>
@@ -5291,11 +5290,11 @@
       <c r="B144" s="8">
         <v>335</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="6">
+        <v>370</v>
+      </c>
+      <c r="D144" s="6">
         <v>70</v>
-      </c>
-      <c r="D144" s="6">
-        <v>370</v>
       </c>
       <c r="E144" s="8">
         <v>1174</v>
@@ -5315,10 +5314,10 @@
         <v>336</v>
       </c>
       <c r="C145" s="6">
+        <v>369</v>
+      </c>
+      <c r="D145" s="6">
         <v>69</v>
-      </c>
-      <c r="D145" s="6">
-        <v>369</v>
       </c>
       <c r="E145" s="6">
         <v>1020</v>
@@ -5337,11 +5336,11 @@
       <c r="B146" s="8">
         <v>337</v>
       </c>
-      <c r="C146" s="8">
+      <c r="C146" s="6">
+        <v>368</v>
+      </c>
+      <c r="D146" s="6">
         <v>68</v>
-      </c>
-      <c r="D146" s="6">
-        <v>368</v>
       </c>
       <c r="E146" s="8">
         <v>1019</v>
@@ -5361,10 +5360,10 @@
         <v>338</v>
       </c>
       <c r="C147" s="6">
+        <v>343</v>
+      </c>
+      <c r="D147" s="6">
         <v>43</v>
-      </c>
-      <c r="D147" s="6">
-        <v>343</v>
       </c>
       <c r="E147" s="6">
         <v>1154</v>
@@ -5383,11 +5382,11 @@
       <c r="B148" s="8">
         <v>339</v>
       </c>
-      <c r="C148" s="8">
+      <c r="C148" s="6">
+        <v>344</v>
+      </c>
+      <c r="D148" s="6">
         <v>44</v>
-      </c>
-      <c r="D148" s="6">
-        <v>344</v>
       </c>
       <c r="E148" s="8">
         <v>1000</v>
@@ -5407,10 +5406,10 @@
         <v>340</v>
       </c>
       <c r="C149" s="6">
+        <v>345</v>
+      </c>
+      <c r="D149" s="6">
         <v>45</v>
-      </c>
-      <c r="D149" s="6">
-        <v>345</v>
       </c>
       <c r="E149" s="6">
         <v>1002</v>
@@ -5429,11 +5428,11 @@
       <c r="B150" s="8">
         <v>341</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="6">
+        <v>346</v>
+      </c>
+      <c r="D150" s="6">
         <v>46</v>
-      </c>
-      <c r="D150" s="6">
-        <v>346</v>
       </c>
       <c r="E150" s="8">
         <v>1004</v>
@@ -5453,10 +5452,10 @@
         <v>342</v>
       </c>
       <c r="C151" s="6">
+        <v>347</v>
+      </c>
+      <c r="D151" s="6">
         <v>47</v>
-      </c>
-      <c r="D151" s="6">
-        <v>347</v>
       </c>
       <c r="E151" s="6">
         <v>1001</v>
@@ -5475,11 +5474,11 @@
       <c r="B152" s="8">
         <v>343</v>
       </c>
-      <c r="C152" s="8">
+      <c r="C152" s="6">
+        <v>366</v>
+      </c>
+      <c r="D152" s="6">
         <v>66</v>
-      </c>
-      <c r="D152" s="6">
-        <v>366</v>
       </c>
       <c r="E152" s="8">
         <v>1175</v>
@@ -5499,10 +5498,10 @@
         <v>344</v>
       </c>
       <c r="C153" s="6">
+        <v>367</v>
+      </c>
+      <c r="D153" s="6">
         <v>67</v>
-      </c>
-      <c r="D153" s="6">
-        <v>367</v>
       </c>
       <c r="E153" s="6">
         <v>1006</v>
@@ -5521,11 +5520,11 @@
       <c r="B154" s="8">
         <v>345</v>
       </c>
-      <c r="C154" s="8">
+      <c r="C154" s="6">
+        <v>364</v>
+      </c>
+      <c r="D154" s="6">
         <v>64</v>
-      </c>
-      <c r="D154" s="6">
-        <v>364</v>
       </c>
       <c r="E154" s="8">
         <v>1164</v>
@@ -5545,10 +5544,10 @@
         <v>346</v>
       </c>
       <c r="C155" s="6">
+        <v>365</v>
+      </c>
+      <c r="D155" s="6">
         <v>65</v>
-      </c>
-      <c r="D155" s="6">
-        <v>365</v>
       </c>
       <c r="E155" s="6">
         <v>1163</v>
@@ -5567,11 +5566,11 @@
       <c r="B156" s="8">
         <v>347</v>
       </c>
-      <c r="C156" s="8">
+      <c r="C156" s="6">
+        <v>348</v>
+      </c>
+      <c r="D156" s="6">
         <v>48</v>
-      </c>
-      <c r="D156" s="6">
-        <v>348</v>
       </c>
       <c r="E156" s="8">
         <v>1170</v>
@@ -5591,10 +5590,10 @@
         <v>348</v>
       </c>
       <c r="C157" s="6">
+        <v>349</v>
+      </c>
+      <c r="D157" s="6">
         <v>49</v>
-      </c>
-      <c r="D157" s="6">
-        <v>349</v>
       </c>
       <c r="E157" s="6">
         <v>1173</v>
@@ -5613,11 +5612,11 @@
       <c r="B158" s="8">
         <v>349</v>
       </c>
-      <c r="C158" s="8">
+      <c r="C158" s="6">
+        <v>350</v>
+      </c>
+      <c r="D158" s="6">
         <v>50</v>
-      </c>
-      <c r="D158" s="6">
-        <v>350</v>
       </c>
       <c r="E158" s="8">
         <v>1171</v>
@@ -5637,10 +5636,10 @@
         <v>350</v>
       </c>
       <c r="C159" s="6">
+        <v>351</v>
+      </c>
+      <c r="D159" s="6">
         <v>51</v>
-      </c>
-      <c r="D159" s="6">
-        <v>351</v>
       </c>
       <c r="E159" s="6">
         <v>1172</v>
@@ -5659,11 +5658,11 @@
       <c r="B160" s="8">
         <v>351</v>
       </c>
-      <c r="C160" s="8">
+      <c r="C160" s="6">
+        <v>363</v>
+      </c>
+      <c r="D160" s="6">
         <v>63</v>
-      </c>
-      <c r="D160" s="6">
-        <v>363</v>
       </c>
       <c r="E160" s="8">
         <v>1055</v>
@@ -5683,10 +5682,10 @@
         <v>352</v>
       </c>
       <c r="C161" s="6">
+        <v>362</v>
+      </c>
+      <c r="D161" s="6">
         <v>62</v>
-      </c>
-      <c r="D161" s="6">
-        <v>362</v>
       </c>
       <c r="E161" s="6">
         <v>1056</v>
@@ -5705,11 +5704,11 @@
       <c r="B162" s="8">
         <v>353</v>
       </c>
-      <c r="C162" s="8">
+      <c r="C162" s="6">
+        <v>361</v>
+      </c>
+      <c r="D162" s="6">
         <v>61</v>
-      </c>
-      <c r="D162" s="6">
-        <v>361</v>
       </c>
       <c r="E162" s="8">
         <v>1057</v>
@@ -5729,10 +5728,10 @@
         <v>354</v>
       </c>
       <c r="C163" s="6">
+        <v>360</v>
+      </c>
+      <c r="D163" s="6">
         <v>60</v>
-      </c>
-      <c r="D163" s="6">
-        <v>360</v>
       </c>
       <c r="E163" s="6">
         <v>1108</v>
@@ -5751,11 +5750,11 @@
       <c r="B164" s="8">
         <v>355</v>
       </c>
-      <c r="C164" s="8">
+      <c r="C164" s="6">
+        <v>358</v>
+      </c>
+      <c r="D164" s="6">
         <v>58</v>
-      </c>
-      <c r="D164" s="6">
-        <v>358</v>
       </c>
       <c r="E164" s="8">
         <v>1010</v>
@@ -5775,10 +5774,10 @@
         <v>356</v>
       </c>
       <c r="C165" s="6">
+        <v>359</v>
+      </c>
+      <c r="D165" s="6">
         <v>59</v>
-      </c>
-      <c r="D165" s="6">
-        <v>359</v>
       </c>
       <c r="E165" s="6">
         <v>1009</v>
@@ -5797,11 +5796,11 @@
       <c r="B166" s="8">
         <v>357</v>
       </c>
-      <c r="C166" s="8">
+      <c r="C166" s="6">
+        <v>353</v>
+      </c>
+      <c r="D166" s="6">
         <v>53</v>
-      </c>
-      <c r="D166" s="6">
-        <v>353</v>
       </c>
       <c r="E166" s="8">
         <v>1126</v>
@@ -5821,10 +5820,10 @@
         <v>358</v>
       </c>
       <c r="C167" s="6">
+        <v>352</v>
+      </c>
+      <c r="D167" s="6">
         <v>52</v>
-      </c>
-      <c r="D167" s="6">
-        <v>352</v>
       </c>
       <c r="E167" s="6">
         <v>1127</v>
@@ -5843,11 +5842,11 @@
       <c r="B168" s="8">
         <v>359</v>
       </c>
-      <c r="C168" s="8">
+      <c r="C168" s="6">
+        <v>354</v>
+      </c>
+      <c r="D168" s="6">
         <v>54</v>
-      </c>
-      <c r="D168" s="6">
-        <v>354</v>
       </c>
       <c r="E168" s="8">
         <v>1125</v>
@@ -5864,22 +5863,22 @@
         <v>195</v>
       </c>
       <c r="B169" s="6">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C169" s="6">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="D169" s="6">
-        <v>401</v>
+        <v>9</v>
       </c>
       <c r="E169" s="6">
-        <v>721</v>
+        <v>1112</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5887,22 +5886,22 @@
         <v>195</v>
       </c>
       <c r="B170" s="8">
-        <v>402</v>
-      </c>
-      <c r="C170" s="8">
-        <v>2</v>
+        <v>410</v>
+      </c>
+      <c r="C170" s="6">
+        <v>410</v>
       </c>
       <c r="D170" s="6">
-        <v>402</v>
+        <v>10</v>
       </c>
       <c r="E170" s="8">
-        <v>717</v>
+        <v>1113</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5910,22 +5909,22 @@
         <v>195</v>
       </c>
       <c r="B171" s="6">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C171" s="6">
-        <v>3</v>
+        <v>411</v>
       </c>
       <c r="D171" s="6">
-        <v>403</v>
+        <v>11</v>
       </c>
       <c r="E171" s="6">
-        <v>724</v>
+        <v>1114</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5933,22 +5932,22 @@
         <v>195</v>
       </c>
       <c r="B172" s="8">
-        <v>404</v>
-      </c>
-      <c r="C172" s="8">
-        <v>4</v>
+        <v>412</v>
+      </c>
+      <c r="C172" s="6">
+        <v>412</v>
       </c>
       <c r="D172" s="6">
-        <v>404</v>
+        <v>12</v>
       </c>
       <c r="E172" s="8">
-        <v>719</v>
+        <v>1115</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5956,22 +5955,22 @@
         <v>195</v>
       </c>
       <c r="B173" s="6">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C173" s="6">
-        <v>5</v>
+        <v>413</v>
       </c>
       <c r="D173" s="6">
-        <v>405</v>
+        <v>13</v>
       </c>
       <c r="E173" s="6">
-        <v>725</v>
+        <v>1116</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5979,22 +5978,22 @@
         <v>195</v>
       </c>
       <c r="B174" s="8">
-        <v>406</v>
-      </c>
-      <c r="C174" s="8">
-        <v>6</v>
+        <v>414</v>
+      </c>
+      <c r="C174" s="6">
+        <v>414</v>
       </c>
       <c r="D174" s="6">
-        <v>406</v>
+        <v>14</v>
       </c>
       <c r="E174" s="8">
-        <v>726</v>
+        <v>1117</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6002,22 +6001,22 @@
         <v>195</v>
       </c>
       <c r="B175" s="6">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C175" s="6">
-        <v>7</v>
+        <v>415</v>
       </c>
       <c r="D175" s="6">
-        <v>407</v>
+        <v>15</v>
       </c>
       <c r="E175" s="6">
-        <v>727</v>
+        <v>1118</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6025,275 +6024,275 @@
         <v>195</v>
       </c>
       <c r="B176" s="8">
-        <v>408</v>
-      </c>
-      <c r="C176" s="8">
-        <v>8</v>
+        <v>416</v>
+      </c>
+      <c r="C176" s="6">
+        <v>416</v>
       </c>
       <c r="D176" s="6">
-        <v>408</v>
+        <v>16</v>
       </c>
       <c r="E176" s="8">
-        <v>728</v>
+        <v>1119</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="5" t="s">
+      <c r="A177" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B177" s="6">
-        <v>409</v>
+      <c r="B177" s="8">
+        <v>420</v>
       </c>
       <c r="C177" s="6">
-        <v>9</v>
+        <v>422</v>
       </c>
       <c r="D177" s="6">
-        <v>409</v>
-      </c>
-      <c r="E177" s="6">
-        <v>1112</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G177" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E177" s="8">
+        <v>1105</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G177" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
+      <c r="A178" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B178" s="8">
-        <v>410</v>
-      </c>
-      <c r="C178" s="8">
-        <v>10</v>
+      <c r="B178" s="6">
+        <v>421</v>
+      </c>
+      <c r="C178" s="6">
+        <v>423</v>
       </c>
       <c r="D178" s="6">
-        <v>410</v>
-      </c>
-      <c r="E178" s="8">
-        <v>1113</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G178" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E178" s="6">
+        <v>1102</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="G178" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="5" t="s">
+      <c r="A179" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B179" s="6">
-        <v>411</v>
+      <c r="B179" s="8">
+        <v>422</v>
       </c>
       <c r="C179" s="6">
-        <v>11</v>
+        <v>424</v>
       </c>
       <c r="D179" s="6">
-        <v>411</v>
-      </c>
-      <c r="E179" s="6">
-        <v>1114</v>
-      </c>
-      <c r="F179" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G179" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E179" s="8">
+        <v>1104</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G179" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="7" t="s">
+      <c r="A180" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B180" s="8">
-        <v>412</v>
-      </c>
-      <c r="C180" s="8">
-        <v>12</v>
+      <c r="B180" s="6">
+        <v>423</v>
+      </c>
+      <c r="C180" s="6">
+        <v>425</v>
       </c>
       <c r="D180" s="6">
-        <v>412</v>
-      </c>
-      <c r="E180" s="8">
-        <v>1115</v>
-      </c>
-      <c r="F180" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="G180" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E180" s="6">
+        <v>1101</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G180" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
+      <c r="A181" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B181" s="6">
-        <v>413</v>
+      <c r="B181" s="8">
+        <v>424</v>
       </c>
       <c r="C181" s="6">
-        <v>13</v>
+        <v>426</v>
       </c>
       <c r="D181" s="6">
-        <v>413</v>
-      </c>
-      <c r="E181" s="6">
-        <v>1116</v>
-      </c>
-      <c r="F181" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="G181" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E181" s="8">
+        <v>1100</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G181" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="7" t="s">
+      <c r="A182" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B182" s="8">
-        <v>414</v>
-      </c>
-      <c r="C182" s="8">
-        <v>14</v>
+      <c r="B182" s="6">
+        <v>425</v>
+      </c>
+      <c r="C182" s="6">
+        <v>427</v>
       </c>
       <c r="D182" s="6">
-        <v>414</v>
-      </c>
-      <c r="E182" s="8">
-        <v>1117</v>
-      </c>
-      <c r="F182" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G182" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E182" s="6">
+        <v>714</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="G182" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
+      <c r="A183" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B183" s="6">
-        <v>415</v>
+      <c r="B183" s="8">
+        <v>426</v>
       </c>
       <c r="C183" s="6">
-        <v>15</v>
+        <v>428</v>
       </c>
       <c r="D183" s="6">
-        <v>415</v>
-      </c>
-      <c r="E183" s="6">
-        <v>1118</v>
-      </c>
-      <c r="F183" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G183" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E183" s="8">
+        <v>704</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G183" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="7" t="s">
+      <c r="A184" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B184" s="8">
-        <v>416</v>
-      </c>
-      <c r="C184" s="8">
-        <v>16</v>
+      <c r="B184" s="6">
+        <v>427</v>
+      </c>
+      <c r="C184" s="6">
+        <v>429</v>
       </c>
       <c r="D184" s="6">
-        <v>416</v>
-      </c>
-      <c r="E184" s="8">
-        <v>1119</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="G184" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E184" s="6">
+        <v>701</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G184" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="5" t="s">
+      <c r="A185" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B185" s="6">
-        <v>417</v>
+      <c r="B185" s="8">
+        <v>428</v>
       </c>
       <c r="C185" s="6">
-        <v>19</v>
+        <v>430</v>
       </c>
       <c r="D185" s="6">
-        <v>419</v>
-      </c>
-      <c r="E185" s="6">
-        <v>245</v>
-      </c>
-      <c r="F185" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G185" s="6" t="s">
-        <v>215</v>
+        <v>30</v>
+      </c>
+      <c r="E185" s="8">
+        <v>713</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="7" t="s">
+      <c r="A186" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B186" s="8">
-        <v>418</v>
-      </c>
-      <c r="C186" s="8">
-        <v>20</v>
+      <c r="B186" s="6">
+        <v>429</v>
+      </c>
+      <c r="C186" s="6">
+        <v>431</v>
       </c>
       <c r="D186" s="6">
-        <v>420</v>
-      </c>
-      <c r="E186" s="8">
-        <v>246</v>
-      </c>
-      <c r="F186" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="G186" s="8" t="s">
-        <v>215</v>
+        <v>31</v>
+      </c>
+      <c r="E186" s="6">
+        <v>712</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="5" t="s">
+      <c r="A187" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B187" s="6">
-        <v>419</v>
+      <c r="B187" s="8">
+        <v>430</v>
       </c>
       <c r="C187" s="6">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="D187" s="6">
-        <v>421</v>
-      </c>
-      <c r="E187" s="6">
-        <v>247</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="G187" s="6" t="s">
-        <v>215</v>
+        <v>32</v>
+      </c>
+      <c r="E187" s="8">
+        <v>711</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6301,19 +6300,19 @@
         <v>195</v>
       </c>
       <c r="B188" s="8">
-        <v>420</v>
-      </c>
-      <c r="C188" s="8">
-        <v>22</v>
+        <v>436</v>
+      </c>
+      <c r="C188" s="6">
+        <v>438</v>
       </c>
       <c r="D188" s="6">
-        <v>422</v>
+        <v>38</v>
       </c>
       <c r="E188" s="8">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="G188" s="8" t="s">
         <v>206</v>
@@ -6324,90 +6323,90 @@
         <v>195</v>
       </c>
       <c r="B189" s="6">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="C189" s="6">
-        <v>23</v>
+        <v>446</v>
       </c>
       <c r="D189" s="6">
-        <v>423</v>
+        <v>46</v>
       </c>
       <c r="E189" s="6">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="G189" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="7" t="s">
+      <c r="A190" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B190" s="8">
-        <v>422</v>
-      </c>
-      <c r="C190" s="8">
-        <v>24</v>
+      <c r="B190" s="6">
+        <v>443</v>
+      </c>
+      <c r="C190" s="6">
+        <v>450</v>
       </c>
       <c r="D190" s="6">
-        <v>424</v>
-      </c>
-      <c r="E190" s="8">
-        <v>1104</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="G190" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E190" s="6">
+        <v>1103</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G190" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
+      <c r="A191" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B191" s="6">
-        <v>423</v>
+      <c r="B191" s="8">
+        <v>444</v>
       </c>
       <c r="C191" s="6">
-        <v>25</v>
+        <v>451</v>
       </c>
       <c r="D191" s="6">
-        <v>425</v>
-      </c>
-      <c r="E191" s="6">
-        <v>1101</v>
-      </c>
-      <c r="F191" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G191" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E191" s="8">
+        <v>715</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G191" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="7" t="s">
+      <c r="A192" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B192" s="8">
-        <v>424</v>
-      </c>
-      <c r="C192" s="8">
-        <v>26</v>
+      <c r="B192" s="6">
+        <v>445</v>
+      </c>
+      <c r="C192" s="6">
+        <v>452</v>
       </c>
       <c r="D192" s="6">
-        <v>426</v>
-      </c>
-      <c r="E192" s="8">
-        <v>1100</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="G192" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E192" s="6">
+        <v>716</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G192" s="6" t="s">
         <v>206</v>
       </c>
     </row>
@@ -6416,22 +6415,22 @@
         <v>195</v>
       </c>
       <c r="B193" s="6">
-        <v>425</v>
+        <v>601</v>
       </c>
       <c r="C193" s="6">
-        <v>27</v>
+        <v>401</v>
       </c>
       <c r="D193" s="6">
-        <v>427</v>
+        <v>1</v>
       </c>
       <c r="E193" s="6">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6439,22 +6438,22 @@
         <v>195</v>
       </c>
       <c r="B194" s="8">
-        <v>426</v>
-      </c>
-      <c r="C194" s="8">
-        <v>28</v>
+        <v>602</v>
+      </c>
+      <c r="C194" s="6">
+        <v>402</v>
       </c>
       <c r="D194" s="6">
-        <v>428</v>
+        <v>2</v>
       </c>
       <c r="E194" s="8">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -6462,22 +6461,22 @@
         <v>195</v>
       </c>
       <c r="B195" s="6">
-        <v>427</v>
+        <v>603</v>
       </c>
       <c r="C195" s="6">
-        <v>29</v>
+        <v>403</v>
       </c>
       <c r="D195" s="6">
-        <v>429</v>
+        <v>3</v>
       </c>
       <c r="E195" s="6">
-        <v>701</v>
+        <v>724</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6485,22 +6484,22 @@
         <v>195</v>
       </c>
       <c r="B196" s="8">
-        <v>428</v>
-      </c>
-      <c r="C196" s="8">
-        <v>30</v>
+        <v>604</v>
+      </c>
+      <c r="C196" s="6">
+        <v>404</v>
       </c>
       <c r="D196" s="6">
-        <v>430</v>
+        <v>4</v>
       </c>
       <c r="E196" s="8">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6508,22 +6507,22 @@
         <v>195</v>
       </c>
       <c r="B197" s="6">
-        <v>429</v>
+        <v>605</v>
       </c>
       <c r="C197" s="6">
-        <v>31</v>
+        <v>405</v>
       </c>
       <c r="D197" s="6">
-        <v>431</v>
+        <v>5</v>
       </c>
       <c r="E197" s="6">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="G197" s="6" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6531,22 +6530,22 @@
         <v>195</v>
       </c>
       <c r="B198" s="8">
-        <v>430</v>
-      </c>
-      <c r="C198" s="8">
-        <v>32</v>
+        <v>606</v>
+      </c>
+      <c r="C198" s="6">
+        <v>406</v>
       </c>
       <c r="D198" s="6">
-        <v>432</v>
+        <v>6</v>
       </c>
       <c r="E198" s="8">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6554,22 +6553,22 @@
         <v>195</v>
       </c>
       <c r="B199" s="6">
-        <v>431</v>
+        <v>607</v>
       </c>
       <c r="C199" s="6">
-        <v>33</v>
+        <v>407</v>
       </c>
       <c r="D199" s="6">
-        <v>433</v>
+        <v>7</v>
       </c>
       <c r="E199" s="6">
-        <v>237</v>
+        <v>727</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="G199" s="6" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -6577,22 +6576,22 @@
         <v>195</v>
       </c>
       <c r="B200" s="8">
-        <v>432</v>
-      </c>
-      <c r="C200" s="8">
-        <v>34</v>
+        <v>608</v>
+      </c>
+      <c r="C200" s="6">
+        <v>408</v>
       </c>
       <c r="D200" s="6">
-        <v>434</v>
+        <v>8</v>
       </c>
       <c r="E200" s="8">
-        <v>239</v>
+        <v>728</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -6600,22 +6599,22 @@
         <v>195</v>
       </c>
       <c r="B201" s="6">
-        <v>433</v>
+        <v>609</v>
       </c>
       <c r="C201" s="6">
-        <v>35</v>
+        <v>444</v>
       </c>
       <c r="D201" s="6">
-        <v>435</v>
+        <v>44</v>
       </c>
       <c r="E201" s="6">
-        <v>240</v>
+        <v>722</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -6623,22 +6622,22 @@
         <v>195</v>
       </c>
       <c r="B202" s="8">
-        <v>434</v>
-      </c>
-      <c r="C202" s="8">
-        <v>36</v>
+        <v>610</v>
+      </c>
+      <c r="C202" s="6">
+        <v>449</v>
       </c>
       <c r="D202" s="6">
-        <v>436</v>
+        <v>49</v>
       </c>
       <c r="E202" s="8">
-        <v>241</v>
+        <v>720</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -6646,19 +6645,19 @@
         <v>195</v>
       </c>
       <c r="B203" s="6">
-        <v>435</v>
+        <v>611</v>
       </c>
       <c r="C203" s="6">
-        <v>37</v>
+        <v>419</v>
       </c>
       <c r="D203" s="6">
-        <v>437</v>
+        <v>19</v>
       </c>
       <c r="E203" s="6">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="G203" s="6" t="s">
         <v>215</v>
@@ -6669,22 +6668,22 @@
         <v>195</v>
       </c>
       <c r="B204" s="8">
-        <v>436</v>
-      </c>
-      <c r="C204" s="8">
-        <v>38</v>
+        <v>612</v>
+      </c>
+      <c r="C204" s="6">
+        <v>420</v>
       </c>
       <c r="D204" s="6">
-        <v>438</v>
+        <v>20</v>
       </c>
       <c r="E204" s="8">
-        <v>1099</v>
+        <v>246</v>
       </c>
       <c r="F204" s="8" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -6692,160 +6691,160 @@
         <v>195</v>
       </c>
       <c r="B205" s="6">
+        <v>613</v>
+      </c>
+      <c r="C205" s="6">
+        <v>421</v>
+      </c>
+      <c r="D205" s="6">
+        <v>21</v>
+      </c>
+      <c r="E205" s="6">
+        <v>247</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="G205" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B206" s="6">
+        <v>431</v>
+      </c>
+      <c r="C206" s="6">
+        <v>433</v>
+      </c>
+      <c r="D206" s="6">
+        <v>33</v>
+      </c>
+      <c r="E206" s="6">
+        <v>237</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="G206" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B207" s="8">
+        <v>432</v>
+      </c>
+      <c r="C207" s="6">
+        <v>434</v>
+      </c>
+      <c r="D207" s="6">
+        <v>34</v>
+      </c>
+      <c r="E207" s="8">
+        <v>239</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B208" s="6">
+        <v>614</v>
+      </c>
+      <c r="C208" s="6">
+        <v>435</v>
+      </c>
+      <c r="D208" s="6">
+        <v>35</v>
+      </c>
+      <c r="E208" s="6">
+        <v>240</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B209" s="8">
+        <v>615</v>
+      </c>
+      <c r="C209" s="6">
+        <v>436</v>
+      </c>
+      <c r="D209" s="6">
+        <v>36</v>
+      </c>
+      <c r="E209" s="8">
+        <v>241</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B210" s="6">
+        <v>616</v>
+      </c>
+      <c r="C210" s="6">
         <v>437</v>
       </c>
-      <c r="C205" s="6">
-        <v>44</v>
-      </c>
-      <c r="D205" s="6">
-        <v>444</v>
-      </c>
-      <c r="E205" s="6">
-        <v>722</v>
-      </c>
-      <c r="F205" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="G205" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="7" t="s">
+      <c r="D210" s="6">
+        <v>37</v>
+      </c>
+      <c r="E210" s="6">
+        <v>242</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="G210" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B206" s="8">
+      <c r="B211" s="8">
         <v>438</v>
       </c>
-      <c r="C206" s="8">
+      <c r="C211" s="6">
+        <v>445</v>
+      </c>
+      <c r="D211" s="6">
         <v>45</v>
       </c>
-      <c r="D206" s="6">
-        <v>445</v>
-      </c>
-      <c r="E206" s="8">
+      <c r="E211" s="8">
         <v>238</v>
       </c>
-      <c r="F206" s="8" t="s">
+      <c r="F211" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G206" s="8" t="s">
+      <c r="G211" s="8" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A207" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B207" s="6">
-        <v>439</v>
-      </c>
-      <c r="C207" s="6">
-        <v>46</v>
-      </c>
-      <c r="D207" s="6">
-        <v>446</v>
-      </c>
-      <c r="E207" s="6">
-        <v>1098</v>
-      </c>
-      <c r="F207" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="G207" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A208" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B208" s="8">
-        <v>440</v>
-      </c>
-      <c r="C208" s="8">
-        <v>47</v>
-      </c>
-      <c r="D208" s="6">
-        <v>447</v>
-      </c>
-      <c r="E208" s="8">
-        <v>244</v>
-      </c>
-      <c r="F208" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G208" s="8" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A209" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B209" s="6">
-        <v>441</v>
-      </c>
-      <c r="C209" s="6">
-        <v>48</v>
-      </c>
-      <c r="D209" s="6">
-        <v>448</v>
-      </c>
-      <c r="E209" s="6">
-        <v>243</v>
-      </c>
-      <c r="F209" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="G209" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A210" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B210" s="8">
-        <v>442</v>
-      </c>
-      <c r="C210" s="8">
-        <v>49</v>
-      </c>
-      <c r="D210" s="6">
-        <v>449</v>
-      </c>
-      <c r="E210" s="8">
-        <v>720</v>
-      </c>
-      <c r="F210" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="G210" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A211" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B211" s="6">
-        <v>443</v>
-      </c>
-      <c r="C211" s="6">
-        <v>50</v>
-      </c>
-      <c r="D211" s="6">
-        <v>450</v>
-      </c>
-      <c r="E211" s="6">
-        <v>1103</v>
-      </c>
-      <c r="F211" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="G211" s="6" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -6853,22 +6852,22 @@
         <v>195</v>
       </c>
       <c r="B212" s="8">
-        <v>444</v>
-      </c>
-      <c r="C212" s="8">
-        <v>51</v>
+        <v>617</v>
+      </c>
+      <c r="C212" s="6">
+        <v>447</v>
       </c>
       <c r="D212" s="6">
-        <v>451</v>
+        <v>47</v>
       </c>
       <c r="E212" s="8">
-        <v>715</v>
+        <v>244</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -6876,22 +6875,22 @@
         <v>195</v>
       </c>
       <c r="B213" s="6">
-        <v>445</v>
+        <v>618</v>
       </c>
       <c r="C213" s="6">
-        <v>52</v>
+        <v>448</v>
       </c>
       <c r="D213" s="6">
-        <v>452</v>
+        <v>48</v>
       </c>
       <c r="E213" s="2">
-        <v>716</v>
+        <v>243</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/planogram/breira-default/FOR-ALL.xlsx
+++ b/planogram/breira-default/FOR-ALL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sverdlik\Desktop\WORKSPACE\COLUMBUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287ECEB9-45E1-4E25-B1EB-AC2AE6BD46BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB31084E-07B9-4890-AFCE-130657B8F889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" xr2:uid="{62A603EA-5BBD-476C-B555-DE322FFD4B76}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17040" xr2:uid="{62A603EA-5BBD-476C-B555-DE322FFD4B76}"/>
   </bookViews>
   <sheets>
     <sheet name="planogram-all-2026-05-31" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="247">
   <si>
     <t>מחלקה</t>
   </si>
@@ -769,6 +769,9 @@
   </si>
   <si>
     <t>בי</t>
+  </si>
+  <si>
+    <t>חלוקה</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1351,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1359,6 +1362,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1404,7 +1409,43 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="177"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1690,19 +1731,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B42FE6-343B-4F83-8C87-75AA163AECE2}" name="Table2" displayName="Table2" ref="A2:G213" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
-  <autoFilter ref="A2:G213" xr:uid="{C8B42FE6-343B-4F83-8C87-75AA163AECE2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A169:G213">
-    <sortCondition ref="G2:G213"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B42FE6-343B-4F83-8C87-75AA163AECE2}" name="Table2" displayName="Table2" ref="A2:H213" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
+  <autoFilter ref="A2:H213" xr:uid="{C8B42FE6-343B-4F83-8C87-75AA163AECE2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H213">
+    <sortCondition ref="H2:H213"/>
   </sortState>
-  <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{2899FD27-9C4F-4A76-BC34-E3378399681D}" name="מחלקה" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{F090C2AC-4F62-4BB7-92ED-E19E15C9B3F8}" name="סדר הדפסה" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{9B0849F3-129A-43F9-9247-D13729C620D2}" name="מיקום" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DA08E62A-0D8B-44F0-96AD-81021848C7F1}" name="בי" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{EDDE42CC-C936-4028-8824-1CDEA3BE2F62}" name="מקט" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{33A04FA6-060E-492F-A89C-053CB4C02FFC}" name="שם" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{7DFD70C4-42DD-4369-9871-2BAA01B67DF1}" name="משפחה" dataDxfId="0"/>
+  <tableColumns count="8">
+    <tableColumn id="2" xr3:uid="{2899FD27-9C4F-4A76-BC34-E3378399681D}" name="מחלקה" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{F090C2AC-4F62-4BB7-92ED-E19E15C9B3F8}" name="סדר הדפסה" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{9B0849F3-129A-43F9-9247-D13729C620D2}" name="מיקום" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DA08E62A-0D8B-44F0-96AD-81021848C7F1}" name="בי" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{EDDE42CC-C936-4028-8824-1CDEA3BE2F62}" name="מקט" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{33A04FA6-060E-492F-A89C-053CB4C02FFC}" name="שם" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{7DFD70C4-42DD-4369-9871-2BAA01B67DF1}" name="משפחה" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4410103B-9BAE-4216-9DEB-E9F216D7F67B}" name="חלוקה" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2005,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2812B666-52D0-447F-BE4C-9A621E492C4D}">
-  <dimension ref="A2:G213"/>
+  <dimension ref="A2:H213"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.09765625" bestFit="1" customWidth="1"/>
@@ -2017,7 +2059,7 @@
     <col min="7" max="7" width="26.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2039,2474 +2081,2798 @@
       <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6">
-        <v>101</v>
+      <c r="H2" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="8">
+        <v>247</v>
       </c>
       <c r="C3" s="6">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="D3" s="6">
         <v>1</v>
       </c>
-      <c r="E3" s="6">
-        <v>800</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>5</v>
+      <c r="E3" s="8">
+        <v>755</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B4" s="8">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="C4" s="6">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="D4" s="6">
         <v>2</v>
       </c>
-      <c r="E4" s="8">
-        <v>732</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="6">
-        <v>103</v>
+      <c r="E4" s="6">
+        <v>660</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="8">
+        <v>249</v>
       </c>
       <c r="C5" s="6">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="D5" s="6">
         <v>3</v>
       </c>
-      <c r="E5" s="6">
-        <v>604</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>5</v>
+      <c r="E5" s="8">
+        <v>662</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B6" s="8">
-        <v>104</v>
+        <v>250</v>
       </c>
       <c r="C6" s="6">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6" s="8">
-        <v>736</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6">
-        <v>105</v>
+      <c r="E6" s="6">
+        <v>661</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="8">
+        <v>251</v>
       </c>
       <c r="C7" s="6">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="D7" s="6">
         <v>5</v>
       </c>
-      <c r="E7" s="6">
-        <v>739</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>5</v>
+      <c r="E7" s="8">
+        <v>664</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B8" s="8">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="C8" s="6">
-        <v>106</v>
+        <v>206</v>
       </c>
       <c r="D8" s="6">
         <v>6</v>
       </c>
-      <c r="E8" s="8">
-        <v>740</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="6">
+        <v>413001</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="8">
+        <v>253</v>
+      </c>
+      <c r="C9" s="6">
+        <v>207</v>
+      </c>
+      <c r="D9" s="6">
+        <v>7</v>
+      </c>
+      <c r="E9" s="8">
+        <v>413002</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="8">
+        <v>254</v>
+      </c>
+      <c r="C10" s="6">
+        <v>208</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>413000</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="8">
+        <v>201</v>
+      </c>
+      <c r="C11" s="6">
+        <v>224</v>
+      </c>
+      <c r="D11" s="6">
+        <v>24</v>
+      </c>
+      <c r="E11" s="8">
+        <v>630</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="8">
+        <v>202</v>
+      </c>
+      <c r="C12" s="6">
+        <v>223</v>
+      </c>
+      <c r="D12" s="6">
+        <v>23</v>
+      </c>
+      <c r="E12" s="6">
+        <v>624</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="8">
+        <v>203</v>
+      </c>
+      <c r="C13" s="6">
+        <v>222</v>
+      </c>
+      <c r="D13" s="6">
+        <v>22</v>
+      </c>
+      <c r="E13" s="8">
+        <v>631</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="8">
+        <v>204</v>
+      </c>
+      <c r="C14" s="6">
+        <v>221</v>
+      </c>
+      <c r="D14" s="6">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1076</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="8">
+        <v>205</v>
+      </c>
+      <c r="C15" s="6">
+        <v>220</v>
+      </c>
+      <c r="D15" s="6">
+        <v>20</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1077</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="8">
+        <v>206</v>
+      </c>
+      <c r="C16" s="6">
+        <v>219</v>
+      </c>
+      <c r="D16" s="6">
+        <v>19</v>
+      </c>
+      <c r="E16" s="6">
+        <v>659</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="8">
+        <v>207</v>
+      </c>
+      <c r="C17" s="6">
+        <v>216</v>
+      </c>
+      <c r="D17" s="6">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1052</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="8">
+        <v>208</v>
+      </c>
+      <c r="C18" s="6">
+        <v>217</v>
+      </c>
+      <c r="D18" s="6">
+        <v>17</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1050</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="8">
+        <v>209</v>
+      </c>
+      <c r="C19" s="6">
+        <v>218</v>
+      </c>
+      <c r="D19" s="6">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1053</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="8">
+        <v>210</v>
+      </c>
+      <c r="C20" s="6">
+        <v>215</v>
+      </c>
+      <c r="D20" s="6">
+        <v>15</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1060</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="8">
+        <v>211</v>
+      </c>
+      <c r="C21" s="6">
+        <v>214</v>
+      </c>
+      <c r="D21" s="6">
         <v>14</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="E21" s="8">
+        <v>1062</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="8">
+        <v>212</v>
+      </c>
+      <c r="C22" s="6">
+        <v>225</v>
+      </c>
+      <c r="D22" s="6">
+        <v>25</v>
+      </c>
+      <c r="E22" s="6">
+        <v>677</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="8">
+        <v>213</v>
+      </c>
+      <c r="C23" s="6">
+        <v>226</v>
+      </c>
+      <c r="D23" s="6">
+        <v>26</v>
+      </c>
+      <c r="E23" s="8">
+        <v>669</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="8">
+        <v>214</v>
+      </c>
+      <c r="C24" s="6">
+        <v>227</v>
+      </c>
+      <c r="D24" s="6">
+        <v>27</v>
+      </c>
+      <c r="E24" s="6">
+        <v>667</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="8">
+        <v>215</v>
+      </c>
+      <c r="C25" s="6">
+        <v>228</v>
+      </c>
+      <c r="D25" s="6">
+        <v>28</v>
+      </c>
+      <c r="E25" s="8">
+        <v>668</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="8">
+        <v>216</v>
+      </c>
+      <c r="C26" s="6">
+        <v>229</v>
+      </c>
+      <c r="D26" s="6">
+        <v>29</v>
+      </c>
+      <c r="E26" s="6">
+        <v>650</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="8">
+        <v>217</v>
+      </c>
+      <c r="C27" s="6">
+        <v>230</v>
+      </c>
+      <c r="D27" s="6">
+        <v>30</v>
+      </c>
+      <c r="E27" s="8">
+        <v>649</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="8">
+        <v>218</v>
+      </c>
+      <c r="C28" s="6">
+        <v>231</v>
+      </c>
+      <c r="D28" s="6">
+        <v>31</v>
+      </c>
+      <c r="E28" s="6">
+        <v>645</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="8">
+        <v>219</v>
+      </c>
+      <c r="C29" s="6">
+        <v>232</v>
+      </c>
+      <c r="D29" s="6">
+        <v>32</v>
+      </c>
+      <c r="E29" s="8">
+        <v>646</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="8">
+        <v>220</v>
+      </c>
+      <c r="C30" s="6">
+        <v>233</v>
+      </c>
+      <c r="D30" s="6">
+        <v>33</v>
+      </c>
+      <c r="E30" s="6">
+        <v>644</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="8">
+        <v>221</v>
+      </c>
+      <c r="C31" s="6">
+        <v>234</v>
+      </c>
+      <c r="D31" s="6">
+        <v>34</v>
+      </c>
+      <c r="E31" s="8">
+        <v>643</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="6">
+      <c r="G31" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="8">
+        <v>222</v>
+      </c>
+      <c r="C32" s="6">
+        <v>235</v>
+      </c>
+      <c r="D32" s="6">
+        <v>35</v>
+      </c>
+      <c r="E32" s="6">
+        <v>628</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="6">
-        <v>8</v>
-      </c>
-      <c r="E9" s="6">
-        <v>802</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="8">
-        <v>108</v>
-      </c>
-      <c r="C10" s="6">
-        <v>107</v>
-      </c>
-      <c r="D10" s="6">
-        <v>7</v>
-      </c>
-      <c r="E10" s="8">
-        <v>803</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="G32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="8">
+        <v>223</v>
+      </c>
+      <c r="C33" s="6">
+        <v>237</v>
+      </c>
+      <c r="D33" s="6">
+        <v>37</v>
+      </c>
+      <c r="E33" s="8">
+        <v>665</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="6">
+      <c r="G33" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="8">
+        <v>224</v>
+      </c>
+      <c r="C34" s="6">
+        <v>238</v>
+      </c>
+      <c r="D34" s="6">
+        <v>38</v>
+      </c>
+      <c r="E34" s="6">
+        <v>673</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="6">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1191</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="8">
-        <v>110</v>
-      </c>
-      <c r="C12" s="6">
-        <v>109</v>
-      </c>
-      <c r="D12" s="6">
-        <v>9</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1192</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="G34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H34" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="8">
+        <v>225</v>
+      </c>
+      <c r="C35" s="6">
+        <v>239</v>
+      </c>
+      <c r="D35" s="6">
+        <v>39</v>
+      </c>
+      <c r="E35" s="8">
+        <v>670</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="6">
-        <v>111</v>
-      </c>
-      <c r="D13" s="6">
-        <v>11</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1190</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="G35" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H35" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="8">
+        <v>226</v>
+      </c>
+      <c r="C36" s="6">
+        <v>240</v>
+      </c>
+      <c r="D36" s="6">
+        <v>40</v>
+      </c>
+      <c r="E36" s="6">
+        <v>672</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="6">
-        <v>112</v>
-      </c>
-      <c r="D14" s="6">
-        <v>12</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1193</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="6">
+      <c r="G36" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="8">
+        <v>227</v>
+      </c>
+      <c r="C37" s="6">
+        <v>241</v>
+      </c>
+      <c r="D37" s="6">
+        <v>41</v>
+      </c>
+      <c r="E37" s="8">
+        <v>412202</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="6">
-        <v>113</v>
-      </c>
-      <c r="D15" s="6">
-        <v>13</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1198</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="8">
+      <c r="G37" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="8">
+        <v>228</v>
+      </c>
+      <c r="C38" s="6">
+        <v>242</v>
+      </c>
+      <c r="D38" s="6">
+        <v>42</v>
+      </c>
+      <c r="E38" s="6">
+        <v>412200</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="6">
-        <v>114</v>
-      </c>
-      <c r="D16" s="6">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1185</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="6">
+      <c r="G38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H38" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="8">
+        <v>229</v>
+      </c>
+      <c r="C39" s="6">
+        <v>243</v>
+      </c>
+      <c r="D39" s="6">
+        <v>43</v>
+      </c>
+      <c r="E39" s="8">
+        <v>412201</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="6">
-        <v>115</v>
-      </c>
-      <c r="D17" s="6">
-        <v>15</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1187</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="8">
-        <v>116</v>
-      </c>
-      <c r="C18" s="6">
-        <v>116</v>
-      </c>
-      <c r="D18" s="6">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1180</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="6">
-        <v>117</v>
-      </c>
-      <c r="C19" s="6">
-        <v>117</v>
-      </c>
-      <c r="D19" s="6">
-        <v>17</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1184</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="8">
-        <v>118</v>
-      </c>
-      <c r="C20" s="6">
-        <v>118</v>
-      </c>
-      <c r="D20" s="6">
-        <v>18</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1182</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="6">
-        <v>119</v>
-      </c>
-      <c r="C21" s="6">
-        <v>119</v>
-      </c>
-      <c r="D21" s="6">
-        <v>19</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1195</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="8">
-        <v>120</v>
-      </c>
-      <c r="C22" s="6">
-        <v>120</v>
-      </c>
-      <c r="D22" s="6">
-        <v>20</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1196</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="6">
-        <v>121</v>
-      </c>
-      <c r="C23" s="6">
-        <v>121</v>
-      </c>
-      <c r="D23" s="6">
-        <v>21</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1197</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="8">
-        <v>122</v>
-      </c>
-      <c r="C24" s="6">
-        <v>122</v>
-      </c>
-      <c r="D24" s="6">
-        <v>22</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1194</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="6">
-        <v>123</v>
-      </c>
-      <c r="C25" s="6">
-        <v>123</v>
-      </c>
-      <c r="D25" s="6">
-        <v>23</v>
-      </c>
-      <c r="E25" s="6">
-        <v>420003</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="8">
-        <v>124</v>
-      </c>
-      <c r="C26" s="6">
-        <v>124</v>
-      </c>
-      <c r="D26" s="6">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8">
-        <v>420004</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="6">
-        <v>125</v>
-      </c>
-      <c r="C27" s="6">
-        <v>125</v>
-      </c>
-      <c r="D27" s="6">
-        <v>25</v>
-      </c>
-      <c r="E27" s="6">
-        <v>420005</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="8">
-        <v>126</v>
-      </c>
-      <c r="C28" s="6">
-        <v>126</v>
-      </c>
-      <c r="D28" s="6">
-        <v>26</v>
-      </c>
-      <c r="E28" s="8">
-        <v>420006</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="6">
-        <v>127</v>
-      </c>
-      <c r="C29" s="6">
-        <v>127</v>
-      </c>
-      <c r="D29" s="6">
-        <v>27</v>
-      </c>
-      <c r="E29" s="6">
-        <v>420007</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="8">
-        <v>128</v>
-      </c>
-      <c r="C30" s="6">
-        <v>128</v>
-      </c>
-      <c r="D30" s="6">
-        <v>28</v>
-      </c>
-      <c r="E30" s="8">
-        <v>420008</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="6">
-        <v>129</v>
-      </c>
-      <c r="C31" s="6">
-        <v>129</v>
-      </c>
-      <c r="D31" s="6">
-        <v>29</v>
-      </c>
-      <c r="E31" s="6">
-        <v>420002</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="8">
-        <v>130</v>
-      </c>
-      <c r="C32" s="6">
-        <v>130</v>
-      </c>
-      <c r="D32" s="6">
-        <v>30</v>
-      </c>
-      <c r="E32" s="8">
-        <v>420001</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="6">
-        <v>131</v>
-      </c>
-      <c r="C33" s="6">
-        <v>131</v>
-      </c>
-      <c r="D33" s="6">
-        <v>31</v>
-      </c>
-      <c r="E33" s="6">
-        <v>818</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="8">
-        <v>132</v>
-      </c>
-      <c r="C34" s="6">
-        <v>132</v>
-      </c>
-      <c r="D34" s="6">
-        <v>32</v>
-      </c>
-      <c r="E34" s="8">
-        <v>815</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="6">
-        <v>133</v>
-      </c>
-      <c r="C35" s="6">
-        <v>133</v>
-      </c>
-      <c r="D35" s="6">
-        <v>33</v>
-      </c>
-      <c r="E35" s="6">
-        <v>816</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="8">
-        <v>134</v>
-      </c>
-      <c r="C36" s="6">
-        <v>134</v>
-      </c>
-      <c r="D36" s="6">
-        <v>34</v>
-      </c>
-      <c r="E36" s="8">
-        <v>817</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="6">
-        <v>135</v>
-      </c>
-      <c r="C37" s="6">
-        <v>137</v>
-      </c>
-      <c r="D37" s="6">
-        <v>37</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1051</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="8">
-        <v>136</v>
-      </c>
-      <c r="C38" s="6">
-        <v>135</v>
-      </c>
-      <c r="D38" s="6">
-        <v>35</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1045</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="6">
-        <v>137</v>
-      </c>
-      <c r="C39" s="6">
-        <v>136</v>
-      </c>
-      <c r="D39" s="6">
-        <v>36</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1046</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>5</v>
+      <c r="G39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B40" s="8">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="C40" s="6">
-        <v>144</v>
+        <v>244</v>
       </c>
       <c r="D40" s="6">
         <v>44</v>
       </c>
-      <c r="E40" s="8">
-        <v>1031</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" s="6">
-        <v>139</v>
+      <c r="E40" s="6">
+        <v>410000</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="8">
+        <v>231</v>
       </c>
       <c r="C41" s="6">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="D41" s="6">
         <v>45</v>
       </c>
-      <c r="E41" s="6">
-        <v>1030</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>5</v>
+      <c r="E41" s="8">
+        <v>410001</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B42" s="8">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="C42" s="6">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="D42" s="6">
         <v>46</v>
       </c>
-      <c r="E42" s="8">
-        <v>1032</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" s="6">
-        <v>141</v>
+      <c r="E42" s="6">
+        <v>410002</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="8">
+        <v>233</v>
       </c>
       <c r="C43" s="6">
-        <v>147</v>
+        <v>247</v>
       </c>
       <c r="D43" s="6">
         <v>47</v>
       </c>
-      <c r="E43" s="6">
-        <v>1034</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>5</v>
+      <c r="E43" s="8">
+        <v>410003</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B44" s="8">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="C44" s="6">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="D44" s="6">
         <v>48</v>
       </c>
-      <c r="E44" s="8">
-        <v>1035</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="6">
-        <v>143</v>
+      <c r="E44" s="6">
+        <v>410004</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="8">
+        <v>235</v>
       </c>
       <c r="C45" s="6">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="D45" s="6">
         <v>49</v>
       </c>
-      <c r="E45" s="6">
-        <v>1036</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>5</v>
+      <c r="E45" s="8">
+        <v>411000</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H45" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B46" s="8">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="C46" s="6">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D46" s="6">
         <v>50</v>
       </c>
-      <c r="E46" s="8">
-        <v>1216</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="6">
-        <v>145</v>
+      <c r="E46" s="6">
+        <v>411001</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="8">
+        <v>237</v>
       </c>
       <c r="C47" s="6">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="D47" s="6">
         <v>51</v>
       </c>
-      <c r="E47" s="6">
-        <v>1215</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>5</v>
+      <c r="E47" s="8">
+        <v>411500</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H47" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B48" s="8">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="C48" s="6">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="D48" s="6">
         <v>52</v>
       </c>
-      <c r="E48" s="8">
-        <v>1214</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="6">
-        <v>147</v>
+      <c r="E48" s="6">
+        <v>412501</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="8">
+        <v>239</v>
       </c>
       <c r="C49" s="6">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="D49" s="6">
         <v>53</v>
       </c>
-      <c r="E49" s="6">
-        <v>1213</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>5</v>
+      <c r="E49" s="8">
+        <v>412502</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B50" s="8">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="C50" s="6">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="D50" s="6">
         <v>54</v>
       </c>
-      <c r="E50" s="8">
-        <v>1217</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="6">
-        <v>149</v>
+      <c r="E50" s="6">
+        <v>412500</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H50" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="8">
+        <v>241</v>
       </c>
       <c r="C51" s="6">
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="D51" s="6">
         <v>55</v>
       </c>
-      <c r="E51" s="6">
-        <v>1218</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>5</v>
+      <c r="E51" s="8">
+        <v>413501</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B52" s="8">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="C52" s="6">
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="D52" s="6">
         <v>56</v>
       </c>
-      <c r="E52" s="8">
-        <v>1219</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="E52" s="6">
+        <v>413502</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="8">
+        <v>243</v>
+      </c>
+      <c r="C53" s="6">
+        <v>257</v>
+      </c>
+      <c r="D53" s="6">
+        <v>57</v>
+      </c>
+      <c r="E53" s="8">
+        <v>413500</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="8">
+        <v>244</v>
+      </c>
+      <c r="C54" s="6">
+        <v>258</v>
+      </c>
+      <c r="D54" s="6">
+        <v>58</v>
+      </c>
+      <c r="E54" s="6">
+        <v>413202</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H54" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="8">
+        <v>245</v>
+      </c>
+      <c r="C55" s="6">
+        <v>259</v>
+      </c>
+      <c r="D55" s="6">
+        <v>59</v>
+      </c>
+      <c r="E55" s="8">
+        <v>413201</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H55" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="8">
+        <v>246</v>
+      </c>
+      <c r="C56" s="6">
+        <v>260</v>
+      </c>
+      <c r="D56" s="6">
+        <v>60</v>
+      </c>
+      <c r="E56" s="6">
+        <v>413200</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H56" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="6">
-        <v>151</v>
-      </c>
-      <c r="C53" s="6">
-        <v>159</v>
-      </c>
-      <c r="D53" s="6">
-        <v>59</v>
-      </c>
-      <c r="E53" s="6">
-        <v>1208</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="B57" s="8">
+        <v>101</v>
+      </c>
+      <c r="C57" s="6">
+        <v>101</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1</v>
+      </c>
+      <c r="E57" s="6">
+        <v>800</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B54" s="8">
-        <v>152</v>
-      </c>
-      <c r="C54" s="6">
-        <v>160</v>
-      </c>
-      <c r="D54" s="6">
-        <v>60</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1211</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="B58" s="8">
+        <v>102</v>
+      </c>
+      <c r="C58" s="6">
+        <v>102</v>
+      </c>
+      <c r="D58" s="6">
+        <v>2</v>
+      </c>
+      <c r="E58" s="8">
+        <v>732</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="6">
-        <v>153</v>
-      </c>
-      <c r="C55" s="6">
-        <v>161</v>
-      </c>
-      <c r="D55" s="6">
-        <v>61</v>
-      </c>
-      <c r="E55" s="6">
-        <v>1209</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="8">
-        <v>501</v>
-      </c>
-      <c r="C56" s="6">
-        <v>201</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1</v>
-      </c>
-      <c r="E56" s="8">
-        <v>755</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="6">
-        <v>502</v>
-      </c>
-      <c r="C57" s="6">
-        <v>202</v>
-      </c>
-      <c r="D57" s="6">
-        <v>2</v>
-      </c>
-      <c r="E57" s="6">
-        <v>660</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="8">
-        <v>503</v>
-      </c>
-      <c r="C58" s="6">
-        <v>203</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="B59" s="8">
+        <v>103</v>
+      </c>
+      <c r="C59" s="6">
+        <v>103</v>
+      </c>
+      <c r="D59" s="6">
         <v>3</v>
       </c>
-      <c r="E58" s="8">
-        <v>662</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="6">
-        <v>504</v>
-      </c>
-      <c r="C59" s="6">
-        <v>204</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="E59" s="6">
+        <v>604</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="10">
         <v>4</v>
       </c>
-      <c r="E59" s="6">
-        <v>661</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="B60" s="8">
-        <v>505</v>
+        <v>104</v>
       </c>
       <c r="C60" s="6">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="D60" s="6">
+        <v>4</v>
+      </c>
+      <c r="E60" s="8">
+        <v>736</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="8">
-        <v>664</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="6">
-        <v>506</v>
+      <c r="B61" s="8">
+        <v>105</v>
       </c>
       <c r="C61" s="6">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="D61" s="6">
+        <v>5</v>
+      </c>
+      <c r="E61" s="6">
+        <v>739</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="8">
+        <v>106</v>
+      </c>
+      <c r="C62" s="6">
+        <v>106</v>
+      </c>
+      <c r="D62" s="6">
         <v>6</v>
       </c>
-      <c r="E61" s="6">
-        <v>413001</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B62" s="8">
-        <v>507</v>
-      </c>
-      <c r="C62" s="6">
-        <v>207</v>
-      </c>
-      <c r="D62" s="6">
-        <v>7</v>
-      </c>
       <c r="E62" s="8">
-        <v>413002</v>
+        <v>740</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H62" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B63" s="6">
-        <v>508</v>
+        <v>5</v>
+      </c>
+      <c r="B63" s="8">
+        <v>107</v>
       </c>
       <c r="C63" s="6">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="D63" s="6">
         <v>8</v>
       </c>
       <c r="E63" s="6">
-        <v>413000</v>
+        <v>802</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H63" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="B64" s="8">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="C64" s="6">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="D64" s="6">
+        <v>7</v>
+      </c>
+      <c r="E64" s="8">
+        <v>803</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="8">
+        <v>109</v>
+      </c>
+      <c r="C65" s="6">
+        <v>110</v>
+      </c>
+      <c r="D65" s="6">
+        <v>10</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1191</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="8">
+        <v>110</v>
+      </c>
+      <c r="C66" s="6">
+        <v>109</v>
+      </c>
+      <c r="D66" s="6">
+        <v>9</v>
+      </c>
+      <c r="E66" s="8">
+        <v>1192</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="8">
+        <v>111</v>
+      </c>
+      <c r="C67" s="6">
+        <v>111</v>
+      </c>
+      <c r="D67" s="6">
+        <v>11</v>
+      </c>
+      <c r="E67" s="6">
+        <v>1190</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="8">
+        <v>112</v>
+      </c>
+      <c r="C68" s="6">
+        <v>112</v>
+      </c>
+      <c r="D68" s="6">
+        <v>12</v>
+      </c>
+      <c r="E68" s="8">
+        <v>1193</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="8">
+        <v>113</v>
+      </c>
+      <c r="C69" s="6">
+        <v>113</v>
+      </c>
+      <c r="D69" s="6">
+        <v>13</v>
+      </c>
+      <c r="E69" s="6">
+        <v>1198</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="8">
+        <v>114</v>
+      </c>
+      <c r="C70" s="6">
+        <v>114</v>
+      </c>
+      <c r="D70" s="6">
+        <v>14</v>
+      </c>
+      <c r="E70" s="8">
+        <v>1185</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E64" s="8">
-        <v>630</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="6">
-        <v>210</v>
-      </c>
-      <c r="C65" s="6">
-        <v>223</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="H70" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="8">
+        <v>115</v>
+      </c>
+      <c r="C71" s="6">
+        <v>115</v>
+      </c>
+      <c r="D71" s="6">
+        <v>15</v>
+      </c>
+      <c r="E71" s="6">
+        <v>1187</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="8">
+        <v>116</v>
+      </c>
+      <c r="C72" s="6">
+        <v>116</v>
+      </c>
+      <c r="D72" s="6">
+        <v>16</v>
+      </c>
+      <c r="E72" s="8">
+        <v>1180</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="8">
+        <v>117</v>
+      </c>
+      <c r="C73" s="6">
+        <v>117</v>
+      </c>
+      <c r="D73" s="6">
+        <v>17</v>
+      </c>
+      <c r="E73" s="6">
+        <v>1184</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="8">
+        <v>118</v>
+      </c>
+      <c r="C74" s="6">
+        <v>118</v>
+      </c>
+      <c r="D74" s="6">
+        <v>18</v>
+      </c>
+      <c r="E74" s="8">
+        <v>1182</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="8">
+        <v>119</v>
+      </c>
+      <c r="C75" s="6">
+        <v>119</v>
+      </c>
+      <c r="D75" s="6">
+        <v>19</v>
+      </c>
+      <c r="E75" s="6">
+        <v>1195</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H75" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="8">
+        <v>120</v>
+      </c>
+      <c r="C76" s="6">
+        <v>120</v>
+      </c>
+      <c r="D76" s="6">
+        <v>20</v>
+      </c>
+      <c r="E76" s="8">
+        <v>1196</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H76" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="8">
+        <v>121</v>
+      </c>
+      <c r="C77" s="6">
+        <v>121</v>
+      </c>
+      <c r="D77" s="6">
+        <v>21</v>
+      </c>
+      <c r="E77" s="6">
+        <v>1197</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H77" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" s="8">
+        <v>122</v>
+      </c>
+      <c r="C78" s="6">
+        <v>122</v>
+      </c>
+      <c r="D78" s="6">
+        <v>22</v>
+      </c>
+      <c r="E78" s="8">
+        <v>1194</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="8">
+        <v>123</v>
+      </c>
+      <c r="C79" s="6">
+        <v>123</v>
+      </c>
+      <c r="D79" s="6">
         <v>23</v>
       </c>
-      <c r="E65" s="6">
-        <v>624</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="8">
-        <v>211</v>
-      </c>
-      <c r="C66" s="6">
-        <v>222</v>
-      </c>
-      <c r="D66" s="6">
-        <v>22</v>
-      </c>
-      <c r="E66" s="8">
-        <v>631</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="6">
-        <v>212</v>
-      </c>
-      <c r="C67" s="6">
-        <v>221</v>
-      </c>
-      <c r="D67" s="6">
-        <v>21</v>
-      </c>
-      <c r="E67" s="6">
-        <v>1076</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B68" s="8">
-        <v>213</v>
-      </c>
-      <c r="C68" s="6">
-        <v>220</v>
-      </c>
-      <c r="D68" s="6">
-        <v>20</v>
-      </c>
-      <c r="E68" s="8">
-        <v>1077</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B69" s="6">
-        <v>214</v>
-      </c>
-      <c r="C69" s="6">
-        <v>219</v>
-      </c>
-      <c r="D69" s="6">
-        <v>19</v>
-      </c>
-      <c r="E69" s="6">
-        <v>659</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="8">
-        <v>215</v>
-      </c>
-      <c r="C70" s="6">
-        <v>216</v>
-      </c>
-      <c r="D70" s="6">
-        <v>16</v>
-      </c>
-      <c r="E70" s="8">
-        <v>1052</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B71" s="6">
-        <v>216</v>
-      </c>
-      <c r="C71" s="6">
-        <v>217</v>
-      </c>
-      <c r="D71" s="6">
-        <v>17</v>
-      </c>
-      <c r="E71" s="6">
-        <v>1050</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B72" s="8">
-        <v>217</v>
-      </c>
-      <c r="C72" s="6">
-        <v>218</v>
-      </c>
-      <c r="D72" s="6">
-        <v>18</v>
-      </c>
-      <c r="E72" s="8">
-        <v>1053</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B73" s="6">
-        <v>218</v>
-      </c>
-      <c r="C73" s="6">
-        <v>215</v>
-      </c>
-      <c r="D73" s="6">
-        <v>15</v>
-      </c>
-      <c r="E73" s="6">
-        <v>1060</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B74" s="8">
-        <v>219</v>
-      </c>
-      <c r="C74" s="6">
-        <v>214</v>
-      </c>
-      <c r="D74" s="6">
-        <v>14</v>
-      </c>
-      <c r="E74" s="8">
-        <v>1062</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="6">
-        <v>220</v>
-      </c>
-      <c r="C75" s="6">
-        <v>225</v>
-      </c>
-      <c r="D75" s="6">
+      <c r="E79" s="6">
+        <v>420003</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" s="8">
+        <v>124</v>
+      </c>
+      <c r="C80" s="6">
+        <v>124</v>
+      </c>
+      <c r="D80" s="6">
+        <v>24</v>
+      </c>
+      <c r="E80" s="8">
+        <v>420004</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H80" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" s="8">
+        <v>125</v>
+      </c>
+      <c r="C81" s="6">
+        <v>125</v>
+      </c>
+      <c r="D81" s="6">
         <v>25</v>
       </c>
-      <c r="E75" s="6">
-        <v>677</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B76" s="8">
-        <v>221</v>
-      </c>
-      <c r="C76" s="6">
-        <v>226</v>
-      </c>
-      <c r="D76" s="6">
+      <c r="E81" s="6">
+        <v>420005</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H81" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="8">
+        <v>126</v>
+      </c>
+      <c r="C82" s="6">
+        <v>126</v>
+      </c>
+      <c r="D82" s="6">
         <v>26</v>
       </c>
-      <c r="E76" s="8">
-        <v>669</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B77" s="6">
-        <v>222</v>
-      </c>
-      <c r="C77" s="6">
-        <v>227</v>
-      </c>
-      <c r="D77" s="6">
+      <c r="E82" s="8">
+        <v>420006</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H82" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" s="8">
+        <v>127</v>
+      </c>
+      <c r="C83" s="6">
+        <v>127</v>
+      </c>
+      <c r="D83" s="6">
         <v>27</v>
       </c>
-      <c r="E77" s="6">
-        <v>667</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B78" s="8">
-        <v>223</v>
-      </c>
-      <c r="C78" s="6">
-        <v>228</v>
-      </c>
-      <c r="D78" s="6">
+      <c r="E83" s="6">
+        <v>420007</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H83" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" s="8">
+        <v>128</v>
+      </c>
+      <c r="C84" s="6">
+        <v>128</v>
+      </c>
+      <c r="D84" s="6">
         <v>28</v>
       </c>
-      <c r="E78" s="8">
-        <v>668</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B79" s="6">
-        <v>224</v>
-      </c>
-      <c r="C79" s="6">
-        <v>229</v>
-      </c>
-      <c r="D79" s="6">
+      <c r="E84" s="8">
+        <v>420008</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H84" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" s="8">
+        <v>129</v>
+      </c>
+      <c r="C85" s="6">
+        <v>129</v>
+      </c>
+      <c r="D85" s="6">
         <v>29</v>
       </c>
-      <c r="E79" s="6">
-        <v>650</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="8">
-        <v>225</v>
-      </c>
-      <c r="C80" s="6">
-        <v>230</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="E85" s="6">
+        <v>420002</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" s="8">
+        <v>130</v>
+      </c>
+      <c r="C86" s="6">
+        <v>130</v>
+      </c>
+      <c r="D86" s="6">
         <v>30</v>
       </c>
-      <c r="E80" s="8">
-        <v>649</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B81" s="6">
-        <v>226</v>
-      </c>
-      <c r="C81" s="6">
-        <v>231</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="E86" s="8">
+        <v>420001</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H86" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" s="8">
+        <v>131</v>
+      </c>
+      <c r="C87" s="6">
+        <v>131</v>
+      </c>
+      <c r="D87" s="6">
         <v>31</v>
       </c>
-      <c r="E81" s="6">
-        <v>645</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B82" s="8">
-        <v>227</v>
-      </c>
-      <c r="C82" s="6">
-        <v>232</v>
-      </c>
-      <c r="D82" s="6">
+      <c r="E87" s="6">
+        <v>818</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H87" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" s="8">
+        <v>132</v>
+      </c>
+      <c r="C88" s="6">
+        <v>132</v>
+      </c>
+      <c r="D88" s="6">
         <v>32</v>
       </c>
-      <c r="E82" s="8">
-        <v>646</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B83" s="6">
-        <v>228</v>
-      </c>
-      <c r="C83" s="6">
-        <v>233</v>
-      </c>
-      <c r="D83" s="6">
+      <c r="E88" s="8">
+        <v>815</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H88" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" s="8">
+        <v>133</v>
+      </c>
+      <c r="C89" s="6">
+        <v>133</v>
+      </c>
+      <c r="D89" s="6">
         <v>33</v>
       </c>
-      <c r="E83" s="6">
-        <v>644</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B84" s="8">
-        <v>229</v>
-      </c>
-      <c r="C84" s="6">
-        <v>234</v>
-      </c>
-      <c r="D84" s="6">
+      <c r="E89" s="6">
+        <v>816</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H89" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" s="8">
+        <v>134</v>
+      </c>
+      <c r="C90" s="6">
+        <v>134</v>
+      </c>
+      <c r="D90" s="6">
         <v>34</v>
       </c>
-      <c r="E84" s="8">
-        <v>643</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B85" s="6">
-        <v>230</v>
-      </c>
-      <c r="C85" s="6">
-        <v>235</v>
-      </c>
-      <c r="D85" s="6">
+      <c r="E90" s="8">
+        <v>817</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H90" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" s="8">
+        <v>135</v>
+      </c>
+      <c r="C91" s="6">
+        <v>137</v>
+      </c>
+      <c r="D91" s="6">
+        <v>37</v>
+      </c>
+      <c r="E91" s="6">
+        <v>1051</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H91" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="8">
+        <v>136</v>
+      </c>
+      <c r="C92" s="6">
+        <v>135</v>
+      </c>
+      <c r="D92" s="6">
         <v>35</v>
       </c>
-      <c r="E85" s="6">
-        <v>628</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B86" s="8">
-        <v>231</v>
-      </c>
-      <c r="C86" s="6">
-        <v>237</v>
-      </c>
-      <c r="D86" s="6">
-        <v>37</v>
-      </c>
-      <c r="E86" s="8">
-        <v>665</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B87" s="6">
-        <v>232</v>
-      </c>
-      <c r="C87" s="6">
-        <v>238</v>
-      </c>
-      <c r="D87" s="6">
-        <v>38</v>
-      </c>
-      <c r="E87" s="6">
-        <v>673</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B88" s="8">
-        <v>233</v>
-      </c>
-      <c r="C88" s="6">
-        <v>239</v>
-      </c>
-      <c r="D88" s="6">
-        <v>39</v>
-      </c>
-      <c r="E88" s="8">
-        <v>670</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B89" s="6">
-        <v>234</v>
-      </c>
-      <c r="C89" s="6">
-        <v>240</v>
-      </c>
-      <c r="D89" s="6">
-        <v>40</v>
-      </c>
-      <c r="E89" s="6">
-        <v>672</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B90" s="8">
-        <v>235</v>
-      </c>
-      <c r="C90" s="6">
-        <v>241</v>
-      </c>
-      <c r="D90" s="6">
-        <v>41</v>
-      </c>
-      <c r="E90" s="8">
-        <v>412202</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B91" s="6">
-        <v>236</v>
-      </c>
-      <c r="C91" s="6">
-        <v>242</v>
-      </c>
-      <c r="D91" s="6">
-        <v>42</v>
-      </c>
-      <c r="E91" s="6">
-        <v>412200</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B92" s="8">
-        <v>237</v>
-      </c>
-      <c r="C92" s="6">
-        <v>243</v>
-      </c>
-      <c r="D92" s="6">
-        <v>43</v>
-      </c>
       <c r="E92" s="8">
-        <v>412201</v>
+        <v>1045</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="H92" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B93" s="6">
-        <v>238</v>
+        <v>5</v>
+      </c>
+      <c r="B93" s="8">
+        <v>137</v>
       </c>
       <c r="C93" s="6">
-        <v>244</v>
+        <v>136</v>
       </c>
       <c r="D93" s="6">
+        <v>36</v>
+      </c>
+      <c r="E93" s="6">
+        <v>1046</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H93" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="8">
+        <v>138</v>
+      </c>
+      <c r="C94" s="6">
+        <v>144</v>
+      </c>
+      <c r="D94" s="6">
         <v>44</v>
       </c>
-      <c r="E93" s="6">
-        <v>410000</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B94" s="8">
-        <v>239</v>
-      </c>
-      <c r="C94" s="6">
-        <v>245</v>
-      </c>
-      <c r="D94" s="6">
+      <c r="E94" s="8">
+        <v>1031</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H94" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="8">
+        <v>139</v>
+      </c>
+      <c r="C95" s="6">
+        <v>145</v>
+      </c>
+      <c r="D95" s="6">
         <v>45</v>
       </c>
-      <c r="E94" s="8">
-        <v>410001</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B95" s="6">
-        <v>240</v>
-      </c>
-      <c r="C95" s="6">
-        <v>246</v>
-      </c>
-      <c r="D95" s="6">
+      <c r="E95" s="6">
+        <v>1030</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H95" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="8">
+        <v>140</v>
+      </c>
+      <c r="C96" s="6">
+        <v>146</v>
+      </c>
+      <c r="D96" s="6">
         <v>46</v>
       </c>
-      <c r="E95" s="6">
-        <v>410002</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B96" s="8">
-        <v>241</v>
-      </c>
-      <c r="C96" s="6">
-        <v>247</v>
-      </c>
-      <c r="D96" s="6">
+      <c r="E96" s="8">
+        <v>1032</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H96" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" s="8">
+        <v>141</v>
+      </c>
+      <c r="C97" s="6">
+        <v>147</v>
+      </c>
+      <c r="D97" s="6">
         <v>47</v>
       </c>
-      <c r="E96" s="8">
-        <v>410003</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B97" s="6">
-        <v>242</v>
-      </c>
-      <c r="C97" s="6">
-        <v>248</v>
-      </c>
-      <c r="D97" s="6">
+      <c r="E97" s="6">
+        <v>1034</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H97" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" s="8">
+        <v>142</v>
+      </c>
+      <c r="C98" s="6">
+        <v>148</v>
+      </c>
+      <c r="D98" s="6">
         <v>48</v>
       </c>
-      <c r="E97" s="6">
-        <v>410004</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B98" s="8">
-        <v>243</v>
-      </c>
-      <c r="C98" s="6">
-        <v>249</v>
-      </c>
-      <c r="D98" s="6">
+      <c r="E98" s="8">
+        <v>1035</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H98" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" s="8">
+        <v>143</v>
+      </c>
+      <c r="C99" s="6">
+        <v>149</v>
+      </c>
+      <c r="D99" s="6">
         <v>49</v>
       </c>
-      <c r="E98" s="8">
-        <v>411000</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B99" s="6">
-        <v>244</v>
-      </c>
-      <c r="C99" s="6">
-        <v>250</v>
-      </c>
-      <c r="D99" s="6">
+      <c r="E99" s="6">
+        <v>1036</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H99" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" s="8">
+        <v>144</v>
+      </c>
+      <c r="C100" s="6">
+        <v>150</v>
+      </c>
+      <c r="D100" s="6">
         <v>50</v>
       </c>
-      <c r="E99" s="6">
-        <v>411001</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B100" s="8">
-        <v>245</v>
-      </c>
-      <c r="C100" s="6">
-        <v>251</v>
-      </c>
-      <c r="D100" s="6">
+      <c r="E100" s="8">
+        <v>1216</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H100" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" s="8">
+        <v>145</v>
+      </c>
+      <c r="C101" s="6">
+        <v>151</v>
+      </c>
+      <c r="D101" s="6">
         <v>51</v>
       </c>
-      <c r="E100" s="8">
-        <v>411500</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B101" s="6">
-        <v>246</v>
-      </c>
-      <c r="C101" s="6">
-        <v>252</v>
-      </c>
-      <c r="D101" s="6">
+      <c r="E101" s="6">
+        <v>1215</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H101" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" s="8">
+        <v>146</v>
+      </c>
+      <c r="C102" s="6">
+        <v>152</v>
+      </c>
+      <c r="D102" s="6">
         <v>52</v>
       </c>
-      <c r="E101" s="6">
-        <v>412501</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B102" s="8">
-        <v>247</v>
-      </c>
-      <c r="C102" s="6">
-        <v>253</v>
-      </c>
-      <c r="D102" s="6">
+      <c r="E102" s="8">
+        <v>1214</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H102" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" s="8">
+        <v>147</v>
+      </c>
+      <c r="C103" s="6">
+        <v>153</v>
+      </c>
+      <c r="D103" s="6">
         <v>53</v>
       </c>
-      <c r="E102" s="8">
-        <v>412502</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B103" s="6">
-        <v>248</v>
-      </c>
-      <c r="C103" s="6">
-        <v>254</v>
-      </c>
-      <c r="D103" s="6">
+      <c r="E103" s="6">
+        <v>1213</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H103" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" s="8">
+        <v>148</v>
+      </c>
+      <c r="C104" s="6">
+        <v>154</v>
+      </c>
+      <c r="D104" s="6">
         <v>54</v>
       </c>
-      <c r="E103" s="6">
-        <v>412500</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B104" s="8">
-        <v>249</v>
-      </c>
-      <c r="C104" s="6">
-        <v>255</v>
-      </c>
-      <c r="D104" s="6">
+      <c r="E104" s="8">
+        <v>1217</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H104" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" s="8">
+        <v>149</v>
+      </c>
+      <c r="C105" s="6">
+        <v>155</v>
+      </c>
+      <c r="D105" s="6">
         <v>55</v>
       </c>
-      <c r="E104" s="8">
-        <v>413501</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B105" s="6">
-        <v>250</v>
-      </c>
-      <c r="C105" s="6">
-        <v>256</v>
-      </c>
-      <c r="D105" s="6">
+      <c r="E105" s="6">
+        <v>1218</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H105" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" s="8">
+        <v>150</v>
+      </c>
+      <c r="C106" s="6">
+        <v>156</v>
+      </c>
+      <c r="D106" s="6">
         <v>56</v>
       </c>
-      <c r="E105" s="6">
-        <v>413502</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B106" s="8">
-        <v>251</v>
-      </c>
-      <c r="C106" s="6">
-        <v>257</v>
-      </c>
-      <c r="D106" s="6">
-        <v>57</v>
-      </c>
       <c r="E106" s="8">
-        <v>413500</v>
+        <v>1219</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="H106" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B107" s="6">
-        <v>252</v>
+        <v>5</v>
+      </c>
+      <c r="B107" s="8">
+        <v>151</v>
       </c>
       <c r="C107" s="6">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="D107" s="6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E107" s="6">
-        <v>413202</v>
+        <v>1208</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="H107" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="B108" s="8">
-        <v>253</v>
+        <v>152</v>
       </c>
       <c r="C108" s="6">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="D108" s="6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E108" s="8">
-        <v>413201</v>
+        <v>1211</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="H108" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B109" s="6">
-        <v>254</v>
+        <v>5</v>
+      </c>
+      <c r="B109" s="8">
+        <v>153</v>
       </c>
       <c r="C109" s="6">
-        <v>260</v>
+        <v>161</v>
       </c>
       <c r="D109" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E109" s="6">
-        <v>413200</v>
+        <v>1209</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="H109" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B110" s="8">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C110" s="6">
         <v>309</v>
@@ -4523,13 +4889,16 @@
       <c r="G110" s="8" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H110" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B111" s="6">
-        <v>302</v>
+      <c r="B111" s="8">
+        <v>308</v>
       </c>
       <c r="C111" s="6">
         <v>310</v>
@@ -4546,13 +4915,16 @@
       <c r="G111" s="6" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B112" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C112" s="6">
         <v>311</v>
@@ -4569,13 +4941,16 @@
       <c r="G112" s="8" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B113" s="6">
-        <v>304</v>
+      <c r="B113" s="8">
+        <v>303</v>
       </c>
       <c r="C113" s="6">
         <v>312</v>
@@ -4592,13 +4967,16 @@
       <c r="G113" s="6" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B114" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C114" s="6">
         <v>313</v>
@@ -4615,13 +4993,16 @@
       <c r="G114" s="8" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B115" s="6">
-        <v>306</v>
+      <c r="B115" s="8">
+        <v>302</v>
       </c>
       <c r="C115" s="6">
         <v>314</v>
@@ -4638,13 +5019,16 @@
       <c r="G115" s="6" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H115" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B116" s="8">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C116" s="6">
         <v>315</v>
@@ -4661,13 +5045,16 @@
       <c r="G116" s="8" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B117" s="6">
-        <v>308</v>
+      <c r="B117" s="8">
+        <v>301</v>
       </c>
       <c r="C117" s="6">
         <v>316</v>
@@ -4684,13 +5071,16 @@
       <c r="G117" s="6" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B118" s="8">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C118" s="6">
         <v>317</v>
@@ -4707,13 +5097,16 @@
       <c r="G118" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B119" s="6">
-        <v>310</v>
+      <c r="B119" s="8">
+        <v>317</v>
       </c>
       <c r="C119" s="6">
         <v>318</v>
@@ -4730,13 +5123,16 @@
       <c r="G119" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B120" s="8">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C120" s="6">
         <v>319</v>
@@ -4753,13 +5149,16 @@
       <c r="G120" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B121" s="6">
-        <v>312</v>
+      <c r="B121" s="8">
+        <v>318</v>
       </c>
       <c r="C121" s="6">
         <v>320</v>
@@ -4776,13 +5175,16 @@
       <c r="G121" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B122" s="8">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C122" s="6">
         <v>321</v>
@@ -4799,13 +5201,16 @@
       <c r="G122" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B123" s="6">
-        <v>314</v>
+      <c r="B123" s="8">
+        <v>320</v>
       </c>
       <c r="C123" s="6">
         <v>322</v>
@@ -4822,13 +5227,16 @@
       <c r="G123" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B124" s="8">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C124" s="6">
         <v>323</v>
@@ -4845,13 +5253,16 @@
       <c r="G124" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B125" s="6">
-        <v>316</v>
+      <c r="B125" s="8">
+        <v>309</v>
       </c>
       <c r="C125" s="6">
         <v>328</v>
@@ -4868,13 +5279,16 @@
       <c r="G125" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B126" s="8">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C126" s="6">
         <v>329</v>
@@ -4891,13 +5305,16 @@
       <c r="G126" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B127" s="6">
-        <v>318</v>
+      <c r="B127" s="8">
+        <v>311</v>
       </c>
       <c r="C127" s="6">
         <v>330</v>
@@ -4914,13 +5331,16 @@
       <c r="G127" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B128" s="8">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C128" s="6">
         <v>331</v>
@@ -4937,13 +5357,16 @@
       <c r="G128" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B129" s="6">
-        <v>320</v>
+      <c r="B129" s="8">
+        <v>314</v>
       </c>
       <c r="C129" s="6">
         <v>333</v>
@@ -4960,13 +5383,16 @@
       <c r="G129" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B130" s="8">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C130" s="6">
         <v>332</v>
@@ -4983,12 +5409,15 @@
       <c r="G130" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B131" s="6">
+      <c r="B131" s="8">
         <v>322</v>
       </c>
       <c r="C131" s="6">
@@ -5006,8 +5435,11 @@
       <c r="G131" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>133</v>
       </c>
@@ -5029,12 +5461,15 @@
       <c r="G132" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="6">
+      <c r="B133" s="8">
         <v>324</v>
       </c>
       <c r="C133" s="6">
@@ -5052,13 +5487,16 @@
       <c r="G133" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B134" s="8">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C134" s="6">
         <v>326</v>
@@ -5075,13 +5513,16 @@
       <c r="G134" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B135" s="6">
-        <v>326</v>
+      <c r="B135" s="8">
+        <v>328</v>
       </c>
       <c r="C135" s="6">
         <v>324</v>
@@ -5098,13 +5539,16 @@
       <c r="G135" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B136" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C136" s="6">
         <v>325</v>
@@ -5121,13 +5565,16 @@
       <c r="G136" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B137" s="6">
-        <v>328</v>
+      <c r="B137" s="8">
+        <v>325</v>
       </c>
       <c r="C137" s="6">
         <v>337</v>
@@ -5144,13 +5591,16 @@
       <c r="G137" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B138" s="8">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C138" s="6">
         <v>338</v>
@@ -5167,13 +5617,16 @@
       <c r="G138" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B139" s="6">
-        <v>330</v>
+      <c r="B139" s="8">
+        <v>327</v>
       </c>
       <c r="C139" s="6">
         <v>339</v>
@@ -5190,13 +5643,16 @@
       <c r="G139" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H139" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B140" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C140" s="6">
         <v>327</v>
@@ -5213,13 +5669,16 @@
       <c r="G140" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B141" s="6">
-        <v>332</v>
+      <c r="B141" s="8">
+        <v>331</v>
       </c>
       <c r="C141" s="6">
         <v>340</v>
@@ -5236,8 +5695,11 @@
       <c r="G141" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>133</v>
       </c>
@@ -5259,12 +5721,15 @@
       <c r="G142" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B143" s="6">
+      <c r="B143" s="8">
         <v>334</v>
       </c>
       <c r="C143" s="6">
@@ -5282,13 +5747,16 @@
       <c r="G143" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B144" s="8">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C144" s="6">
         <v>370</v>
@@ -5305,13 +5773,16 @@
       <c r="G144" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B145" s="6">
-        <v>336</v>
+      <c r="B145" s="8">
+        <v>342</v>
       </c>
       <c r="C145" s="6">
         <v>369</v>
@@ -5328,13 +5799,16 @@
       <c r="G145" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B146" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C146" s="6">
         <v>368</v>
@@ -5351,13 +5825,16 @@
       <c r="G146" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B147" s="6">
-        <v>338</v>
+      <c r="B147" s="8">
+        <v>335</v>
       </c>
       <c r="C147" s="6">
         <v>343</v>
@@ -5374,13 +5851,16 @@
       <c r="G147" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B148" s="8">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C148" s="6">
         <v>344</v>
@@ -5397,13 +5877,16 @@
       <c r="G148" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B149" s="6">
-        <v>340</v>
+      <c r="B149" s="8">
+        <v>338</v>
       </c>
       <c r="C149" s="6">
         <v>345</v>
@@ -5420,13 +5903,16 @@
       <c r="G149" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B150" s="8">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C150" s="6">
         <v>346</v>
@@ -5443,13 +5929,16 @@
       <c r="G150" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B151" s="6">
-        <v>342</v>
+      <c r="B151" s="8">
+        <v>337</v>
       </c>
       <c r="C151" s="6">
         <v>347</v>
@@ -5466,13 +5955,16 @@
       <c r="G151" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B152" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C152" s="6">
         <v>366</v>
@@ -5489,13 +5981,16 @@
       <c r="G152" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B153" s="6">
-        <v>344</v>
+      <c r="B153" s="8">
+        <v>343</v>
       </c>
       <c r="C153" s="6">
         <v>367</v>
@@ -5512,13 +6007,16 @@
       <c r="G153" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B154" s="8">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C154" s="6">
         <v>364</v>
@@ -5535,13 +6033,16 @@
       <c r="G154" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B155" s="6">
-        <v>346</v>
+      <c r="B155" s="8">
+        <v>345</v>
       </c>
       <c r="C155" s="6">
         <v>365</v>
@@ -5558,13 +6059,16 @@
       <c r="G155" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H155" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B156" s="8">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C156" s="6">
         <v>348</v>
@@ -5581,13 +6085,16 @@
       <c r="G156" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B157" s="6">
-        <v>348</v>
+      <c r="B157" s="8">
+        <v>354</v>
       </c>
       <c r="C157" s="6">
         <v>349</v>
@@ -5604,13 +6111,16 @@
       <c r="G157" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H157" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B158" s="8">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C158" s="6">
         <v>350</v>
@@ -5627,13 +6137,16 @@
       <c r="G158" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B159" s="6">
-        <v>350</v>
+      <c r="B159" s="8">
+        <v>353</v>
       </c>
       <c r="C159" s="6">
         <v>351</v>
@@ -5650,13 +6163,16 @@
       <c r="G159" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B160" s="8">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C160" s="6">
         <v>363</v>
@@ -5673,13 +6189,16 @@
       <c r="G160" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B161" s="6">
-        <v>352</v>
+      <c r="B161" s="8">
+        <v>348</v>
       </c>
       <c r="C161" s="6">
         <v>362</v>
@@ -5696,13 +6215,16 @@
       <c r="G161" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B162" s="8">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C162" s="6">
         <v>361</v>
@@ -5719,13 +6241,16 @@
       <c r="G162" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B163" s="6">
-        <v>354</v>
+      <c r="B163" s="8">
+        <v>350</v>
       </c>
       <c r="C163" s="6">
         <v>360</v>
@@ -5742,13 +6267,16 @@
       <c r="G163" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B164" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C164" s="6">
         <v>358</v>
@@ -5765,13 +6293,16 @@
       <c r="G164" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B165" s="6">
-        <v>356</v>
+      <c r="B165" s="8">
+        <v>359</v>
       </c>
       <c r="C165" s="6">
         <v>359</v>
@@ -5788,13 +6319,16 @@
       <c r="G165" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B166" s="8">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C166" s="6">
         <v>353</v>
@@ -5811,13 +6345,16 @@
       <c r="G166" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B167" s="6">
-        <v>358</v>
+      <c r="B167" s="8">
+        <v>357</v>
       </c>
       <c r="C167" s="6">
         <v>352</v>
@@ -5834,13 +6371,16 @@
       <c r="G167" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B168" s="8">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C168" s="6">
         <v>354</v>
@@ -5857,13 +6397,16 @@
       <c r="G168" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B169" s="6">
-        <v>409</v>
+      <c r="B169" s="8">
+        <v>401</v>
       </c>
       <c r="C169" s="6">
         <v>409</v>
@@ -5880,13 +6423,16 @@
       <c r="G169" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B170" s="8">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C170" s="6">
         <v>410</v>
@@ -5903,13 +6449,16 @@
       <c r="G170" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B171" s="6">
-        <v>411</v>
+      <c r="B171" s="8">
+        <v>403</v>
       </c>
       <c r="C171" s="6">
         <v>411</v>
@@ -5926,13 +6475,16 @@
       <c r="G171" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B172" s="8">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C172" s="6">
         <v>412</v>
@@ -5949,13 +6501,16 @@
       <c r="G172" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B173" s="6">
-        <v>413</v>
+      <c r="B173" s="8">
+        <v>405</v>
       </c>
       <c r="C173" s="6">
         <v>413</v>
@@ -5972,13 +6527,16 @@
       <c r="G173" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B174" s="8">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C174" s="6">
         <v>414</v>
@@ -5995,13 +6553,16 @@
       <c r="G174" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B175" s="6">
-        <v>415</v>
+      <c r="B175" s="8">
+        <v>407</v>
       </c>
       <c r="C175" s="6">
         <v>415</v>
@@ -6018,13 +6579,16 @@
       <c r="G175" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B176" s="8">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C176" s="6">
         <v>416</v>
@@ -6041,13 +6605,16 @@
       <c r="G176" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B177" s="8">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="C177" s="6">
         <v>422</v>
@@ -6064,13 +6631,16 @@
       <c r="G177" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B178" s="6">
-        <v>421</v>
+      <c r="B178" s="8">
+        <v>410</v>
       </c>
       <c r="C178" s="6">
         <v>423</v>
@@ -6087,13 +6657,16 @@
       <c r="G178" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B179" s="8">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="C179" s="6">
         <v>424</v>
@@ -6110,13 +6683,16 @@
       <c r="G179" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B180" s="6">
-        <v>423</v>
+      <c r="B180" s="8">
+        <v>412</v>
       </c>
       <c r="C180" s="6">
         <v>425</v>
@@ -6133,13 +6709,16 @@
       <c r="G180" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B181" s="8">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C181" s="6">
         <v>426</v>
@@ -6156,13 +6735,16 @@
       <c r="G181" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B182" s="6">
-        <v>425</v>
+      <c r="B182" s="8">
+        <v>414</v>
       </c>
       <c r="C182" s="6">
         <v>427</v>
@@ -6179,13 +6761,16 @@
       <c r="G182" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B183" s="8">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C183" s="6">
         <v>428</v>
@@ -6202,13 +6787,16 @@
       <c r="G183" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B184" s="6">
-        <v>427</v>
+      <c r="B184" s="8">
+        <v>416</v>
       </c>
       <c r="C184" s="6">
         <v>429</v>
@@ -6225,13 +6813,16 @@
       <c r="G184" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B185" s="8">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="C185" s="6">
         <v>430</v>
@@ -6248,13 +6839,16 @@
       <c r="G185" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B186" s="6">
-        <v>429</v>
+      <c r="B186" s="8">
+        <v>418</v>
       </c>
       <c r="C186" s="6">
         <v>431</v>
@@ -6271,13 +6865,16 @@
       <c r="G186" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B187" s="8">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C187" s="6">
         <v>432</v>
@@ -6294,13 +6891,16 @@
       <c r="G187" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B188" s="8">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="C188" s="6">
         <v>438</v>
@@ -6317,13 +6917,16 @@
       <c r="G188" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H188" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B189" s="6">
-        <v>439</v>
+      <c r="B189" s="8">
+        <v>421</v>
       </c>
       <c r="C189" s="6">
         <v>446</v>
@@ -6340,13 +6943,16 @@
       <c r="G189" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H189" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B190" s="6">
-        <v>443</v>
+      <c r="B190" s="8">
+        <v>422</v>
       </c>
       <c r="C190" s="6">
         <v>450</v>
@@ -6363,13 +6969,16 @@
       <c r="G190" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H190" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B191" s="8">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C191" s="6">
         <v>451</v>
@@ -6386,13 +6995,16 @@
       <c r="G191" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H191" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B192" s="6">
-        <v>445</v>
+      <c r="B192" s="8">
+        <v>444</v>
       </c>
       <c r="C192" s="6">
         <v>452</v>
@@ -6409,358 +7021,406 @@
       <c r="G192" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H192" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="6">
-        <v>601</v>
+      <c r="B193" s="8">
+        <v>445</v>
       </c>
       <c r="C193" s="6">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="D193" s="6">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E193" s="6">
-        <v>721</v>
+        <v>237</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="H193" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B194" s="8">
-        <v>602</v>
+        <v>446</v>
       </c>
       <c r="C194" s="6">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="D194" s="6">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E194" s="8">
-        <v>717</v>
+        <v>239</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="H194" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="6">
-        <v>603</v>
+      <c r="B195" s="8">
+        <v>447</v>
       </c>
       <c r="C195" s="6">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D195" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E195" s="6">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G195" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H195" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B196" s="8">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="C196" s="6">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D196" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E196" s="8">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H196" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B197" s="6">
-        <v>605</v>
+      <c r="B197" s="8">
+        <v>449</v>
       </c>
       <c r="C197" s="6">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D197" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E197" s="6">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G197" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H197" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B198" s="8">
-        <v>606</v>
+        <v>450</v>
       </c>
       <c r="C198" s="6">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D198" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E198" s="8">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G198" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H198" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B199" s="6">
-        <v>607</v>
+      <c r="B199" s="8">
+        <v>451</v>
       </c>
       <c r="C199" s="6">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D199" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E199" s="6">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G199" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H199" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B200" s="8">
-        <v>608</v>
+        <v>452</v>
       </c>
       <c r="C200" s="6">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D200" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E200" s="8">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G200" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H200" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B201" s="6">
-        <v>609</v>
+      <c r="B201" s="8">
+        <v>453</v>
       </c>
       <c r="C201" s="6">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="D201" s="6">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E201" s="6">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="G201" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H201" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B202" s="8">
-        <v>610</v>
+        <v>454</v>
       </c>
       <c r="C202" s="6">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="D202" s="6">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E202" s="8">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H202" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B203" s="6">
-        <v>611</v>
+      <c r="B203" s="8">
+        <v>455</v>
       </c>
       <c r="C203" s="6">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="D203" s="6">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E203" s="6">
-        <v>245</v>
+        <v>722</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="G203" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="H203" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B204" s="8">
-        <v>612</v>
+        <v>456</v>
       </c>
       <c r="C204" s="6">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="D204" s="6">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E204" s="8">
-        <v>246</v>
+        <v>720</v>
       </c>
       <c r="F204" s="8" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="H204" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B205" s="6">
-        <v>613</v>
+      <c r="B205" s="8">
+        <v>457</v>
       </c>
       <c r="C205" s="6">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D205" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E205" s="6">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G205" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="5" t="s">
+      <c r="H205" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B206" s="6">
-        <v>431</v>
+      <c r="B206" s="8">
+        <v>458</v>
       </c>
       <c r="C206" s="6">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="D206" s="6">
-        <v>33</v>
-      </c>
-      <c r="E206" s="6">
-        <v>237</v>
-      </c>
-      <c r="F206" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="G206" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E206" s="8">
+        <v>246</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G206" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A207" s="7" t="s">
+      <c r="H206" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="5" t="s">
         <v>195</v>
       </c>
       <c r="B207" s="8">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="C207" s="6">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="D207" s="6">
-        <v>34</v>
-      </c>
-      <c r="E207" s="8">
-        <v>239</v>
-      </c>
-      <c r="F207" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="G207" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E207" s="6">
+        <v>247</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="G207" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H207" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B208" s="6">
-        <v>614</v>
+      <c r="B208" s="8">
+        <v>460</v>
       </c>
       <c r="C208" s="6">
         <v>435</v>
@@ -6777,13 +7437,16 @@
       <c r="G208" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H208" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B209" s="8">
-        <v>615</v>
+        <v>461</v>
       </c>
       <c r="C209" s="6">
         <v>436</v>
@@ -6800,13 +7463,16 @@
       <c r="G209" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H209" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B210" s="6">
-        <v>616</v>
+      <c r="B210" s="8">
+        <v>462</v>
       </c>
       <c r="C210" s="6">
         <v>437</v>
@@ -6823,13 +7489,16 @@
       <c r="G210" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H210" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B211" s="8">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="C211" s="6">
         <v>445</v>
@@ -6846,13 +7515,16 @@
       <c r="G211" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H211" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B212" s="8">
-        <v>617</v>
+        <v>464</v>
       </c>
       <c r="C212" s="6">
         <v>447</v>
@@ -6869,13 +7541,16 @@
       <c r="G212" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H212" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B213" s="6">
-        <v>618</v>
+      <c r="B213" s="8">
+        <v>465</v>
       </c>
       <c r="C213" s="6">
         <v>448</v>
@@ -6892,9 +7567,24 @@
       <c r="G213" s="2" t="s">
         <v>215</v>
       </c>
+      <c r="H213" s="10">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="H3:H213">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/planogram/breira-default/FOR-ALL.xlsx
+++ b/planogram/breira-default/FOR-ALL.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H233"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5911,9 +5911,555 @@
         <v>15</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B213">
+        <v>247</v>
+      </c>
+      <c r="C213">
+        <v>261</v>
+      </c>
+      <c r="D213">
+        <v>61</v>
+      </c>
+      <c r="E213">
+        <v>908001</v>
+      </c>
+      <c r="F213" t="str">
+        <v>(82X180) גדול צדדי דו סטנד</v>
+      </c>
+      <c r="G213" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B214">
+        <v>248</v>
+      </c>
+      <c r="C214">
+        <v>262</v>
+      </c>
+      <c r="D214">
+        <v>62</v>
+      </c>
+      <c r="E214">
+        <v>908002</v>
+      </c>
+      <c r="F214" t="str">
+        <v>(56X180) בינוני צדדי דו סטנד</v>
+      </c>
+      <c r="G214" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B215">
+        <v>249</v>
+      </c>
+      <c r="C215">
+        <v>263</v>
+      </c>
+      <c r="D215">
+        <v>63</v>
+      </c>
+      <c r="E215">
+        <v>908003</v>
+      </c>
+      <c r="F215" t="str">
+        <v>(50X168) קיר רשת</v>
+      </c>
+      <c r="G215" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B216">
+        <v>250</v>
+      </c>
+      <c r="C216">
+        <v>264</v>
+      </c>
+      <c r="D216">
+        <v>64</v>
+      </c>
+      <c r="E216">
+        <v>908004</v>
+      </c>
+      <c r="F216" t="str">
+        <v>'סמ20 לרשת וו</v>
+      </c>
+      <c r="G216" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B217">
+        <v>251</v>
+      </c>
+      <c r="C217">
+        <v>265</v>
+      </c>
+      <c r="D217">
+        <v>65</v>
+      </c>
+      <c r="E217">
+        <v>908005</v>
+      </c>
+      <c r="F217" t="str">
+        <v>(50X190) רשת סטנד</v>
+      </c>
+      <c r="G217" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B218">
+        <v>252</v>
+      </c>
+      <c r="C218">
+        <v>266</v>
+      </c>
+      <c r="D218">
+        <v>66</v>
+      </c>
+      <c r="E218">
+        <v>908006</v>
+      </c>
+      <c r="F218" t="str">
+        <v>'סמ30 לרשת וו</v>
+      </c>
+      <c r="G218" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B219">
+        <v>253</v>
+      </c>
+      <c r="C219">
+        <v>267</v>
+      </c>
+      <c r="D219">
+        <v>67</v>
+      </c>
+      <c r="E219">
+        <v>908007</v>
+      </c>
+      <c r="F219" t="str">
+        <v>NORD PORT לוגו 12.5 מגשית</v>
+      </c>
+      <c r="G219" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B220">
+        <v>254</v>
+      </c>
+      <c r="C220">
+        <v>268</v>
+      </c>
+      <c r="D220">
+        <v>68</v>
+      </c>
+      <c r="E220">
+        <v>908008</v>
+      </c>
+      <c r="F220" t="str">
+        <v>SANTA BREMOR לוגו 12.5 מגשית</v>
+      </c>
+      <c r="G220" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B221">
+        <v>255</v>
+      </c>
+      <c r="C221">
+        <v>269</v>
+      </c>
+      <c r="D221">
+        <v>69</v>
+      </c>
+      <c r="E221">
+        <v>908010</v>
+      </c>
+      <c r="F221" t="str">
+        <v>(55) 33X39X16.5 קירור צידנית</v>
+      </c>
+      <c r="G221" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B222">
+        <v>256</v>
+      </c>
+      <c r="C222">
+        <v>270</v>
+      </c>
+      <c r="D222">
+        <v>70</v>
+      </c>
+      <c r="E222">
+        <v>908011</v>
+      </c>
+      <c r="F222" t="str">
+        <v>DADU ('יח 5) 'ג250-325 קרימוש גלידות צידנית</v>
+      </c>
+      <c r="G222" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B223">
+        <v>257</v>
+      </c>
+      <c r="C223">
+        <v>271</v>
+      </c>
+      <c r="D223">
+        <v>71</v>
+      </c>
+      <c r="E223">
+        <v>908012</v>
+      </c>
+      <c r="F223" t="str">
+        <v>(100) הונגרית קוביה</v>
+      </c>
+      <c r="G223" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B224">
+        <v>258</v>
+      </c>
+      <c r="C224">
+        <v>272</v>
+      </c>
+      <c r="D224">
+        <v>72</v>
+      </c>
+      <c r="E224">
+        <v>908013</v>
+      </c>
+      <c r="F224" t="str">
+        <v>מגנטים 8 כולל מ"ס205X66 למקרר כיסוי</v>
+      </c>
+      <c r="G224" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B225">
+        <v>259</v>
+      </c>
+      <c r="C225">
+        <v>273</v>
+      </c>
+      <c r="D225">
+        <v>73</v>
+      </c>
+      <c r="E225">
+        <v>908014</v>
+      </c>
+      <c r="F225" t="str">
+        <v>סטריפ</v>
+      </c>
+      <c r="G225" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B226">
+        <v>260</v>
+      </c>
+      <c r="C226">
+        <v>274</v>
+      </c>
+      <c r="D226">
+        <v>74</v>
+      </c>
+      <c r="E226">
+        <v>908015</v>
+      </c>
+      <c r="F226" t="str">
+        <v>מקודד</v>
+      </c>
+      <c r="G226" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B227">
+        <v>261</v>
+      </c>
+      <c r="C227">
+        <v>275</v>
+      </c>
+      <c r="D227">
+        <v>75</v>
+      </c>
+      <c r="E227">
+        <v>908016</v>
+      </c>
+      <c r="F227" t="str">
+        <v>(50) ברמור סנטה לבנה צידנית</v>
+      </c>
+      <c r="G227" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B228">
+        <v>262</v>
+      </c>
+      <c r="C228">
+        <v>276</v>
+      </c>
+      <c r="D228">
+        <v>76</v>
+      </c>
+      <c r="E228">
+        <v>908017</v>
+      </c>
+      <c r="F228" t="str">
+        <v>(50) פורט נורד לבנה צידנית</v>
+      </c>
+      <c r="G228" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B229">
+        <v>263</v>
+      </c>
+      <c r="C229">
+        <v>277</v>
+      </c>
+      <c r="D229">
+        <v>77</v>
+      </c>
+      <c r="E229">
+        <v>908018</v>
+      </c>
+      <c r="F229" t="str">
+        <v>(50) קרימוש לבנה צידנית</v>
+      </c>
+      <c r="G229" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B230">
+        <v>264</v>
+      </c>
+      <c r="C230">
+        <v>278</v>
+      </c>
+      <c r="D230">
+        <v>78</v>
+      </c>
+      <c r="E230">
+        <v>908032</v>
+      </c>
+      <c r="F230" t="str">
+        <v>PUSHER NORD PORT דחפן</v>
+      </c>
+      <c r="G230" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B231">
+        <v>265</v>
+      </c>
+      <c r="C231">
+        <v>279</v>
+      </c>
+      <c r="D231">
+        <v>79</v>
+      </c>
+      <c r="E231">
+        <v>908033</v>
+      </c>
+      <c r="F231" t="str">
+        <v>PUSHER MATIES דחפן</v>
+      </c>
+      <c r="G231" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B232">
+        <v>266</v>
+      </c>
+      <c r="C232">
+        <v>280</v>
+      </c>
+      <c r="D232">
+        <v>80</v>
+      </c>
+      <c r="E232">
+        <v>908034</v>
+      </c>
+      <c r="F232" t="str">
+        <v>RELS מ"ס 90 מסילה</v>
+      </c>
+      <c r="G232" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>חלבי</v>
+      </c>
+      <c r="B233">
+        <v>267</v>
+      </c>
+      <c r="C233">
+        <v>281</v>
+      </c>
+      <c r="D233">
+        <v>81</v>
+      </c>
+      <c r="E233">
+        <v>908035</v>
+      </c>
+      <c r="F233" t="str">
+        <v>PUSHER PRESIDENT דחפן</v>
+      </c>
+      <c r="G233" t="str">
+        <v>סטנד</v>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H233"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planogram/breira-default/FOR-ALL.xlsx
+++ b/planogram/breira-default/FOR-ALL.xlsx
@@ -5933,8 +5933,8 @@
       <c r="G213" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H213" t="str">
-        <v/>
+      <c r="H213">
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -5959,8 +5959,8 @@
       <c r="G214" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H214" t="str">
-        <v/>
+      <c r="H214">
+        <v>3</v>
       </c>
     </row>
     <row r="215">
@@ -5985,8 +5985,8 @@
       <c r="G215" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H215" t="str">
-        <v/>
+      <c r="H215">
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -6011,8 +6011,8 @@
       <c r="G216" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H216" t="str">
-        <v/>
+      <c r="H216">
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -6037,8 +6037,8 @@
       <c r="G217" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H217" t="str">
-        <v/>
+      <c r="H217">
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -6063,8 +6063,8 @@
       <c r="G218" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H218" t="str">
-        <v/>
+      <c r="H218">
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -6089,8 +6089,8 @@
       <c r="G219" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H219" t="str">
-        <v/>
+      <c r="H219">
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -6115,8 +6115,8 @@
       <c r="G220" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H220" t="str">
-        <v/>
+      <c r="H220">
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -6141,8 +6141,8 @@
       <c r="G221" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H221" t="str">
-        <v/>
+      <c r="H221">
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -6167,8 +6167,8 @@
       <c r="G222" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H222" t="str">
-        <v/>
+      <c r="H222">
+        <v>3</v>
       </c>
     </row>
     <row r="223">
@@ -6193,8 +6193,8 @@
       <c r="G223" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H223" t="str">
-        <v/>
+      <c r="H223">
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -6219,8 +6219,8 @@
       <c r="G224" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H224" t="str">
-        <v/>
+      <c r="H224">
+        <v>3</v>
       </c>
     </row>
     <row r="225">
@@ -6245,8 +6245,8 @@
       <c r="G225" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H225" t="str">
-        <v/>
+      <c r="H225">
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -6271,8 +6271,8 @@
       <c r="G226" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H226" t="str">
-        <v/>
+      <c r="H226">
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6297,8 +6297,8 @@
       <c r="G227" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H227" t="str">
-        <v/>
+      <c r="H227">
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6323,8 +6323,8 @@
       <c r="G228" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H228" t="str">
-        <v/>
+      <c r="H228">
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6349,8 +6349,8 @@
       <c r="G229" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H229" t="str">
-        <v/>
+      <c r="H229">
+        <v>3</v>
       </c>
     </row>
     <row r="230">
@@ -6375,8 +6375,8 @@
       <c r="G230" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H230" t="str">
-        <v/>
+      <c r="H230">
+        <v>3</v>
       </c>
     </row>
     <row r="231">
@@ -6401,8 +6401,8 @@
       <c r="G231" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H231" t="str">
-        <v/>
+      <c r="H231">
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -6427,8 +6427,8 @@
       <c r="G232" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H232" t="str">
-        <v/>
+      <c r="H232">
+        <v>3</v>
       </c>
     </row>
     <row r="233">
@@ -6453,8 +6453,8 @@
       <c r="G233" t="str">
         <v>סטנד</v>
       </c>
-      <c r="H233" t="str">
-        <v/>
+      <c r="H233">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/planogram/breira-default/FOR-ALL.xlsx
+++ b/planogram/breira-default/FOR-ALL.xlsx
@@ -3209,3252 +3209,3252 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B109">
-        <v>307</v>
+        <v>401</v>
       </c>
       <c r="C109">
-        <v>309</v>
+        <v>409</v>
       </c>
       <c r="D109">
         <v>9</v>
       </c>
       <c r="E109">
-        <v>403007</v>
+        <v>1112</v>
       </c>
       <c r="F109" t="str">
-        <v xml:space="preserve">פילה מקרל מומלח בעישון חם מצונן150 גרם8) NP) </v>
+        <v>‬שבבי דיונון בטעם סרטן מבושל,מיובש ומומלח90 ג(50)'‭</v>
       </c>
       <c r="G109" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H109">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B110">
-        <v>308</v>
+        <v>402</v>
       </c>
       <c r="C110">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="D110">
         <v>10</v>
       </c>
       <c r="E110">
-        <v>403008</v>
+        <v>1113</v>
       </c>
       <c r="F110" t="str">
-        <v xml:space="preserve">פילה מקרל מומלח בעישון חם עם פלפל שחור גרוס150 גרם8) NP) </v>
+        <v>‬שבבי קלמר מיובש ומומלח90 ג(50)'‭</v>
       </c>
       <c r="G110" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H110">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B111">
-        <v>304</v>
+        <v>403</v>
       </c>
       <c r="C111">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="D111">
         <v>11</v>
       </c>
       <c r="E111">
-        <v>403004</v>
+        <v>1114</v>
       </c>
       <c r="F111" t="str">
-        <v xml:space="preserve">פילה פורל מעושן פרוס מצונן250 גרםNP </v>
+        <v>‬רצועות קלמר מיובש ומומלח בטעם סרטן90 ג(50)'‭</v>
       </c>
       <c r="G111" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H111">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B112">
-        <v>303</v>
+        <v>404</v>
       </c>
       <c r="C112">
-        <v>312</v>
+        <v>412</v>
       </c>
       <c r="D112">
         <v>12</v>
       </c>
       <c r="E112">
-        <v>403003</v>
+        <v>1115</v>
       </c>
       <c r="F112" t="str">
-        <v xml:space="preserve">פילה סלמון מעושן פרוס מצונן250 גרםNP </v>
+        <v>‬רצועות קלמר מעושן מיובש ומומלח90 ג(50)'‭</v>
       </c>
       <c r="G112" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H112">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B113">
-        <v>306</v>
+        <v>405</v>
       </c>
       <c r="C113">
-        <v>313</v>
+        <v>413</v>
       </c>
       <c r="D113">
         <v>13</v>
       </c>
       <c r="E113">
-        <v>403006</v>
+        <v>1116</v>
       </c>
       <c r="F113" t="str">
-        <v xml:space="preserve">פילה פורל מעושן מצונן200 גרםNP </v>
+        <v>‬רצועות קלמר מיובש ומומלח עם פלפל צ'ילי90 ג(50)'‭</v>
       </c>
       <c r="G113" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H113">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B114">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="C114">
-        <v>314</v>
+        <v>414</v>
       </c>
       <c r="D114">
         <v>14</v>
       </c>
       <c r="E114">
-        <v>403002</v>
+        <v>1117</v>
       </c>
       <c r="F114" t="str">
-        <v xml:space="preserve">פילה פורל מעושן פרוס מצונן100 גרםNP </v>
+        <v>‬פרוסות דג שיבוט אלבין מיובש ומומלח100 ג(50)'‭</v>
       </c>
       <c r="G114" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H114">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B115">
-        <v>305</v>
+        <v>407</v>
       </c>
       <c r="C115">
-        <v>315</v>
+        <v>415</v>
       </c>
       <c r="D115">
         <v>15</v>
       </c>
       <c r="E115">
-        <v>403005</v>
+        <v>1118</v>
       </c>
       <c r="F115" t="str">
-        <v xml:space="preserve">פילה סלמון מעושן מצונן200 גרםNP </v>
+        <v>‬פרוסות דג שיבוט אלבין מיובש עם צ'ילי100 ג(50)'‭</v>
       </c>
       <c r="G115" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H115">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B116">
-        <v>301</v>
+        <v>408</v>
       </c>
       <c r="C116">
-        <v>316</v>
+        <v>416</v>
       </c>
       <c r="D116">
         <v>16</v>
       </c>
       <c r="E116">
-        <v>403001</v>
+        <v>1119</v>
       </c>
       <c r="F116" t="str">
-        <v xml:space="preserve">פילה סלמון מעושן פרוס מצונן100 גרםNP </v>
+        <v>‬פרוסות דג שיבוט אלבין מיובש ומומלח ללא עור90 ג(50)'‭</v>
       </c>
       <c r="G116" t="str">
-        <v>NORD PORT מצונן פורל/סלמון</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H116">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B117">
-        <v>316</v>
+        <v>409</v>
       </c>
       <c r="C117">
-        <v>317</v>
+        <v>422</v>
       </c>
       <c r="D117">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E117">
-        <v>1017</v>
+        <v>1105</v>
       </c>
       <c r="F117" t="str">
-        <v>איקרה ביצי דג טרוטונית והרינג עם פורל וסלמון180 ג'</v>
+        <v>‬ (287)BAR CHILIדג ברקודה צ'ילי מלוח100 ג(52)'חום‭</v>
       </c>
       <c r="G117" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H117">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B118">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="C118">
-        <v>318</v>
+        <v>423</v>
       </c>
       <c r="D118">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E118">
-        <v>1018</v>
+        <v>1102</v>
       </c>
       <c r="F118" t="str">
-        <v>ביצי דג טרוטונית MOIVA עם חסילונים180 ג'</v>
+        <v>‬ 256)IMPERATOR)דג צנינית צהובה פסים מלוח100 ג(52)'תכלת‭</v>
       </c>
       <c r="G118" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H118">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B119">
-        <v>315</v>
+        <v>411</v>
       </c>
       <c r="C119">
-        <v>319</v>
+        <v>424</v>
       </c>
       <c r="D119">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E119">
-        <v>1015</v>
+        <v>1104</v>
       </c>
       <c r="F119" t="str">
-        <v>איקרה ביצי דג טרוטונית והרינג180 ג'</v>
+        <v>‬ 270)BARAKUDA)דג ברקודה  מיובש100 ג(52)'כתום‭</v>
       </c>
       <c r="G119" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H119">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B120">
-        <v>318</v>
+        <v>412</v>
       </c>
       <c r="C120">
-        <v>320</v>
+        <v>425</v>
       </c>
       <c r="D120">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E120">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="F120" t="str">
-        <v>איקרה ביצי דג טרוטונית והרינג עם אבקדו,פורל וסלמון180 ג'</v>
+        <v>‬ 232)POLOSATIK)דג צנינון הכתם מיובש100 ג(52)'סגול‭</v>
       </c>
       <c r="G120" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H120">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B121">
-        <v>319</v>
+        <v>413</v>
       </c>
       <c r="C121">
-        <v>321</v>
+        <v>426</v>
       </c>
       <c r="D121">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E121">
-        <v>1122</v>
+        <v>1100</v>
       </c>
       <c r="F121" t="str">
-        <v xml:space="preserve">סלט איקרה לבנה 180 גרםNP </v>
+        <v>‬ 218)BALICHOK)דג צנינון הכתם מיובש100 ג(52)'אפור‭</v>
       </c>
       <c r="G121" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H121">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B122">
-        <v>320</v>
+        <v>414</v>
       </c>
       <c r="C122">
-        <v>322</v>
+        <v>427</v>
       </c>
       <c r="D122">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E122">
-        <v>1123</v>
+        <v>714</v>
       </c>
       <c r="F122" t="str">
-        <v xml:space="preserve">סלט איקרה ורודה 180 גרםNP </v>
+        <v>‬ 305)ANCHOVY)דג עפינית זוטר מיובש ומומלח120 ג(52)'‭</v>
       </c>
       <c r="G122" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H122">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B123">
-        <v>321</v>
+        <v>415</v>
       </c>
       <c r="C123">
-        <v>323</v>
+        <v>428</v>
       </c>
       <c r="D123">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E123">
-        <v>1124</v>
+        <v>704</v>
       </c>
       <c r="F123" t="str">
-        <v xml:space="preserve">סלט איקרה עם פורל וסלמון מעושנים 180 גרםNP </v>
+        <v>דג צנינית צהובה פסים מלוח100 IMPERATOR ג'</v>
       </c>
       <c r="G123" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H123">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B124">
-        <v>309</v>
+        <v>416</v>
       </c>
       <c r="C124">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="D124">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E124">
-        <v>1014</v>
+        <v>701</v>
       </c>
       <c r="F124" t="str">
-        <v>חתיכות פילה דג הרינג מלוח מצונן260 ג'</v>
+        <v>‬דג ברקודה מלוח מיובש100 (199)ג(52)'‭</v>
       </c>
       <c r="G124" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H124">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B125">
-        <v>310</v>
+        <v>417</v>
       </c>
       <c r="C125">
-        <v>329</v>
+        <v>430</v>
       </c>
       <c r="D125">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E125">
-        <v>1012</v>
+        <v>713</v>
       </c>
       <c r="F125" t="str">
-        <v>חתיכות פילה דג הרינג מלוח מצונן עם בצל260 ג'</v>
+        <v>‬דג ברקודה עם צ'ילי מלוח מיובש100 (727)ג(52)'‭</v>
       </c>
       <c r="G125" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H125">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B126">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="C126">
-        <v>330</v>
+        <v>431</v>
       </c>
       <c r="D126">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E126">
-        <v>1013</v>
+        <v>712</v>
       </c>
       <c r="F126" t="str">
-        <v>חתיכות פילה דג הרינג מלוח מצונן עם תבלין260 ג</v>
+        <v>‬דג צנינון הכתם מלוח מיובש100 (697)ג(52)'‭</v>
       </c>
       <c r="G126" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H126">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B127">
-        <v>312</v>
+        <v>419</v>
       </c>
       <c r="C127">
-        <v>331</v>
+        <v>432</v>
       </c>
       <c r="D127">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E127">
-        <v>1049</v>
+        <v>711</v>
       </c>
       <c r="F127" t="str">
-        <v>חתיכות פילה דג הרינג סקנדינבי מלוח מצונן260 ג'</v>
+        <v>‬דג צנינון הכתם מלוח מיובש100 (734)ג(52)'‭</v>
       </c>
       <c r="G127" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H127">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B128">
-        <v>314</v>
+        <v>420</v>
       </c>
       <c r="C128">
-        <v>333</v>
+        <v>438</v>
       </c>
       <c r="D128">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E128">
-        <v>1107</v>
+        <v>1099</v>
       </c>
       <c r="F128" t="str">
-        <v>בסגנון קוויאר שחור כדורי דג פורל230 ג'</v>
+        <v>‬דג צלופח מטוגן עם צ'ילי מלוח מיובש80 (991)ג(52)'‭</v>
       </c>
       <c r="G128" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H128">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B129">
-        <v>313</v>
+        <v>421</v>
       </c>
       <c r="C129">
-        <v>332</v>
+        <v>446</v>
       </c>
       <c r="D129">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E129">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="F129" t="str">
-        <v>בסגנון קוויאר אדום כדורי דג פורל230 ג'</v>
+        <v>דג צלופח מטוגן מלוח מיובש80ג'</v>
       </c>
       <c r="G129" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H129">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B130">
-        <v>322</v>
+        <v>422</v>
       </c>
       <c r="C130">
-        <v>334</v>
+        <v>450</v>
       </c>
       <c r="D130">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E130">
-        <v>1005</v>
+        <v>1103</v>
       </c>
       <c r="F130" t="str">
-        <v>חתיכות פילה דג הרינג מלוח בשמן מצונן400 ג'</v>
+        <v xml:space="preserve"> TARANOCHKAדג אופירית מלוח מיובש100 ג'אדום</v>
       </c>
       <c r="G130" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H130">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B131">
-        <v>323</v>
+        <v>433</v>
       </c>
       <c r="C131">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="D131">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E131">
-        <v>1047</v>
+        <v>715</v>
       </c>
       <c r="F131" t="str">
-        <v>חתיכות פילה דג הרינג מתובל מלוח בשמן400 ג'</v>
+        <v>SHRIMPSחסילונים מיובשים ומומלחים80 ג'</v>
       </c>
       <c r="G131" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H131">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B132">
-        <v>324</v>
+        <v>444</v>
       </c>
       <c r="C132">
-        <v>336</v>
+        <v>452</v>
       </c>
       <c r="D132">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E132">
-        <v>1048</v>
+        <v>716</v>
       </c>
       <c r="F132" t="str">
-        <v>חתיכות פילה דג הרינג סקנדינבי מלוח בשמן400 ג'</v>
+        <v xml:space="preserve"> SHRIMPS CHILLIחסילונים מיובשים ומומלחים עם צ'ילי80 ג</v>
       </c>
       <c r="G132" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגים פודסטוק</v>
       </c>
       <c r="H132">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B133">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="C133">
-        <v>326</v>
+        <v>433</v>
       </c>
       <c r="D133">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E133">
-        <v>1168</v>
+        <v>237</v>
       </c>
       <c r="F133" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן עם תבלין500 ג</v>
+        <v>רצועות פילה דג לש 'מיובש100 RUSSIA ג'</v>
       </c>
       <c r="G133" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H133">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B134">
-        <v>328</v>
+        <v>446</v>
       </c>
       <c r="C134">
-        <v>324</v>
+        <v>434</v>
       </c>
       <c r="D134">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E134">
-        <v>1166</v>
+        <v>239</v>
       </c>
       <c r="F134" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן500 ג'</v>
+        <v>רצועות פילה דג סום מיובש100 RUSSIA ג'</v>
       </c>
       <c r="G134" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H134">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B135">
-        <v>329</v>
+        <v>447</v>
       </c>
       <c r="C135">
-        <v>325</v>
+        <v>401</v>
       </c>
       <c r="D135">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E135">
-        <v>1167</v>
+        <v>721</v>
       </c>
       <c r="F135" t="str">
-        <v>חתיכות פילה דג הרינג סקנדינבי מומלח בשמן מצונן500 ג</v>
+        <v>‬דג וובלה מיובש‭</v>
       </c>
       <c r="G135" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H135">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B136">
-        <v>325</v>
+        <v>448</v>
       </c>
       <c r="C136">
-        <v>337</v>
+        <v>402</v>
       </c>
       <c r="D136">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E136">
-        <v>400001</v>
+        <v>717</v>
       </c>
       <c r="F136" t="str">
-        <v>נתחי פילה הרינג עם בצל וזיתים מצונן" פרובינציאל500  "ג6)NP)</v>
+        <v>‬דג לש 'מיובש‭</v>
       </c>
       <c r="G136" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H136">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B137">
-        <v>326</v>
+        <v>449</v>
       </c>
       <c r="C137">
-        <v>338</v>
+        <v>403</v>
       </c>
       <c r="D137">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E137">
-        <v>400002</v>
+        <v>724</v>
       </c>
       <c r="F137" t="str">
-        <v>נתחי פילה הרינג כבוש עם בצל מצונן520  ג6)NP)</v>
+        <v>‬דג לש 'מעושן‭</v>
       </c>
       <c r="G137" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H137">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B138">
-        <v>327</v>
+        <v>450</v>
       </c>
       <c r="C138">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="D138">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="E138">
-        <v>400003</v>
+        <v>719</v>
       </c>
       <c r="F138" t="str">
-        <v>נתחי פילה הרינג מומלח עם שמיר בשמן מצונן500 ג6)NP)</v>
+        <v>‬דג סודאק מיובש‭</v>
       </c>
       <c r="G138" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H138">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B139">
-        <v>332</v>
+        <v>451</v>
       </c>
       <c r="C139">
-        <v>327</v>
+        <v>405</v>
       </c>
       <c r="D139">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E139">
-        <v>1120</v>
+        <v>725</v>
       </c>
       <c r="F139" t="str">
-        <v>פילה דג הרינג סקנדינבי מלוח מצונן250 ג'</v>
+        <v>‬דג צ'חון מעושן‭</v>
       </c>
       <c r="G139" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H139">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B140">
-        <v>331</v>
+        <v>452</v>
       </c>
       <c r="C140">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="D140">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E140">
-        <v>1011</v>
+        <v>726</v>
       </c>
       <c r="F140" t="str">
-        <v>פילה דג הרינג מלוח מצונן250 ג'</v>
+        <v>‬דג צ'חון מיובש‭</v>
       </c>
       <c r="G140" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H140">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B141">
-        <v>333</v>
+        <v>453</v>
       </c>
       <c r="C141">
-        <v>341</v>
+        <v>407</v>
       </c>
       <c r="D141">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E141">
-        <v>1165</v>
+        <v>727</v>
       </c>
       <c r="F141" t="str">
-        <v>פילה דג הרינג מומלח בשמן מצונן400 ג'</v>
+        <v>‬דג ז'אריך מיובש‭</v>
       </c>
       <c r="G141" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H141">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B142">
-        <v>334</v>
+        <v>454</v>
       </c>
       <c r="C142">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="D142">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E142">
-        <v>1157</v>
+        <v>728</v>
       </c>
       <c r="F142" t="str">
-        <v>פילה הרינג בשמן400 ג'</v>
+        <v>‬דג ז'אריך מעושן‭</v>
       </c>
       <c r="G142" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H142">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B143">
-        <v>340</v>
+        <v>455</v>
       </c>
       <c r="C143">
-        <v>370</v>
+        <v>444</v>
       </c>
       <c r="D143">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E143">
-        <v>1174</v>
+        <v>722</v>
       </c>
       <c r="F143" t="str">
-        <v>פילה דג הרינג מומלח XXL בשמן מצונן300 ג'</v>
+        <v>דג פילה סום מעושן</v>
       </c>
       <c r="G143" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H143">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B144">
-        <v>342</v>
+        <v>456</v>
       </c>
       <c r="C144">
-        <v>369</v>
+        <v>449</v>
       </c>
       <c r="D144">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E144">
-        <v>1020</v>
+        <v>720</v>
       </c>
       <c r="F144" t="str">
-        <v>ביצי דג שיבוט TRESKA מומלח מצונן130 ג'</v>
+        <v>דג זאב מים מיובש</v>
       </c>
       <c r="G144" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםKAZAHSTAN</v>
       </c>
       <c r="H144">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B145">
-        <v>341</v>
+        <v>457</v>
       </c>
       <c r="C145">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="D145">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="E145">
-        <v>1019</v>
+        <v>245</v>
       </c>
       <c r="F145" t="str">
-        <v>ביצי דג זהבנון MINTAY מומלח מצונן130 ג'</v>
+        <v xml:space="preserve">דג צ'חון מיובשRUSSIA </v>
       </c>
       <c r="G145" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H145">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B146">
-        <v>335</v>
+        <v>458</v>
       </c>
       <c r="C146">
-        <v>343</v>
+        <v>420</v>
       </c>
       <c r="D146">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E146">
-        <v>1154</v>
+        <v>246</v>
       </c>
       <c r="F146" t="str">
-        <v>פילה דג הרינג מומלח בשמן מצונן230 ג'</v>
+        <v xml:space="preserve">דג ז'אריך מיובשRUSSIA </v>
       </c>
       <c r="G146" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H146">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B147">
-        <v>336</v>
+        <v>459</v>
       </c>
       <c r="C147">
-        <v>344</v>
+        <v>421</v>
       </c>
       <c r="D147">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E147">
-        <v>1000</v>
+        <v>247</v>
       </c>
       <c r="F147" t="str">
-        <v>פילה דג הרינג מומלח בשמן מצונן1200 ג(NP (3 '</v>
+        <v xml:space="preserve">דג לש" 'טושקה "מיובשRUSSIA </v>
       </c>
       <c r="G147" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H147">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B148">
-        <v>338</v>
+        <v>460</v>
       </c>
       <c r="C148">
-        <v>345</v>
+        <v>435</v>
       </c>
       <c r="D148">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E148">
-        <v>1002</v>
+        <v>240</v>
       </c>
       <c r="F148" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן1200 ג3) NP)'</v>
+        <v xml:space="preserve">דג קרסנופיורקה מיובשRUSSIA </v>
       </c>
       <c r="G148" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H148">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B149">
-        <v>339</v>
+        <v>461</v>
       </c>
       <c r="C149">
-        <v>346</v>
+        <v>436</v>
       </c>
       <c r="D149">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E149">
-        <v>1004</v>
+        <v>241</v>
       </c>
       <c r="F149" t="str">
-        <v>חתיכות פילה דג הרינג סקנדינבי מומלח בשמן מצונן1200 ג3) NP)'</v>
+        <v xml:space="preserve">דג לש 'מיובשRUSSIA </v>
       </c>
       <c r="G149" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H149">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B150">
-        <v>337</v>
+        <v>462</v>
       </c>
       <c r="C150">
-        <v>347</v>
+        <v>437</v>
       </c>
       <c r="D150">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E150">
-        <v>1001</v>
+        <v>242</v>
       </c>
       <c r="F150" t="str">
-        <v>פילה דג הרינג  סקנדינבי מומלח בשמן מצונן1200 ג3) NP) '</v>
+        <v xml:space="preserve">דג וובלה מיובשRUSSIA </v>
       </c>
       <c r="G150" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H150">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B151">
-        <v>344</v>
+        <v>463</v>
       </c>
       <c r="C151">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="D151">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E151">
-        <v>1175</v>
+        <v>238</v>
       </c>
       <c r="F151" t="str">
-        <v>פילה דג הרינג סקנדינבי מומלח בשמן מצונן1000 ג'</v>
+        <v>רצועות פילה דג ש'יוקה מיובש100 RUSSIA ג'</v>
       </c>
       <c r="G151" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H151">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B152">
-        <v>343</v>
+        <v>464</v>
       </c>
       <c r="C152">
-        <v>367</v>
+        <v>447</v>
       </c>
       <c r="D152">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E152">
-        <v>1006</v>
+        <v>244</v>
       </c>
       <c r="F152" t="str">
-        <v>פילה דג הרינג מומלח בשמן מצונן1000 ג'</v>
+        <v xml:space="preserve">דג ש'יוקה מיובשRUSSIA </v>
       </c>
       <c r="G152" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H152">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>דגים</v>
+        <v>דג יבש</v>
       </c>
       <c r="B153">
-        <v>346</v>
+        <v>465</v>
       </c>
       <c r="C153">
-        <v>364</v>
+        <v>448</v>
       </c>
       <c r="D153">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E153">
-        <v>1164</v>
+        <v>243</v>
       </c>
       <c r="F153" t="str">
-        <v>חתיכות פילה דג הרינג מומלח עם בצל בשמן מצונן150 ג'</v>
+        <v xml:space="preserve">דג סודאק מיובשRUSSIA </v>
       </c>
       <c r="G153" t="str">
-        <v>NORD PORT דגים</v>
+        <v>דגיםRUSSIA</v>
       </c>
       <c r="H153">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B154">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="C154">
-        <v>365</v>
+        <v>261</v>
       </c>
       <c r="D154">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E154">
-        <v>1163</v>
+        <v>908001</v>
       </c>
       <c r="F154" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן150 ג'</v>
+        <v>(82X180) גדול צדדי דו סטנד</v>
       </c>
       <c r="G154" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H154">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B155">
-        <v>351</v>
+        <v>248</v>
       </c>
       <c r="C155">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="D155">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E155">
-        <v>1170</v>
+        <v>908002</v>
       </c>
       <c r="F155" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן290 ג'</v>
+        <v>(56X180) בינוני צדדי דו סטנד</v>
       </c>
       <c r="G155" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H155">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B156">
-        <v>354</v>
+        <v>249</v>
       </c>
       <c r="C156">
-        <v>349</v>
+        <v>263</v>
       </c>
       <c r="D156">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E156">
-        <v>1173</v>
+        <v>908003</v>
       </c>
       <c r="F156" t="str">
-        <v>חתיכות פילה דג הרינג סקנדינבי מומלח בשמן מצונן290 ג</v>
+        <v>(50X168) קיר רשת</v>
       </c>
       <c r="G156" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H156">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B157">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="C157">
-        <v>350</v>
+        <v>264</v>
       </c>
       <c r="D157">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E157">
-        <v>1171</v>
+        <v>908004</v>
       </c>
       <c r="F157" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן עם בצל290 ג'</v>
+        <v>'סמ20 לרשת וו</v>
       </c>
       <c r="G157" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H157">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B158">
-        <v>353</v>
+        <v>251</v>
       </c>
       <c r="C158">
-        <v>351</v>
+        <v>265</v>
       </c>
       <c r="D158">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E158">
-        <v>1172</v>
+        <v>908005</v>
       </c>
       <c r="F158" t="str">
-        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן עם תבלין290 ג</v>
+        <v>(50X190) רשת סטנד</v>
       </c>
       <c r="G158" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H158">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B159">
-        <v>347</v>
+        <v>252</v>
       </c>
       <c r="C159">
-        <v>363</v>
+        <v>266</v>
       </c>
       <c r="D159">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E159">
-        <v>1055</v>
+        <v>908006</v>
       </c>
       <c r="F159" t="str">
-        <v>סלט אצות ים מוחמצות200 ג'</v>
+        <v>'סמ30 לרשת וו</v>
       </c>
       <c r="G159" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H159">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B160">
-        <v>348</v>
+        <v>253</v>
       </c>
       <c r="C160">
-        <v>362</v>
+        <v>267</v>
       </c>
       <c r="D160">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E160">
-        <v>1056</v>
+        <v>908007</v>
       </c>
       <c r="F160" t="str">
-        <v>סלט אצות ים מוחמצות ומתובלות עם גזר200 ג'</v>
+        <v>NORD PORT לוגו 12.5 מגשית</v>
       </c>
       <c r="G160" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H160">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B161">
-        <v>349</v>
+        <v>254</v>
       </c>
       <c r="C161">
-        <v>361</v>
+        <v>268</v>
       </c>
       <c r="D161">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E161">
-        <v>1057</v>
+        <v>908008</v>
       </c>
       <c r="F161" t="str">
-        <v>סלט אצות ים מוחמצות עם בצל ופפריקה מתוקה200 ג'</v>
+        <v>SANTA BREMOR לוגו 12.5 מגשית</v>
       </c>
       <c r="G161" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H161">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B162">
-        <v>350</v>
+        <v>255</v>
       </c>
       <c r="C162">
-        <v>360</v>
+        <v>269</v>
       </c>
       <c r="D162">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E162">
-        <v>1108</v>
+        <v>908010</v>
       </c>
       <c r="F162" t="str">
-        <v>סלט אצות ים-צ'וקה150 ג'</v>
+        <v>(55) 33X39X16.5 קירור צידנית</v>
       </c>
       <c r="G162" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H162">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B163">
-        <v>358</v>
+        <v>256</v>
       </c>
       <c r="C163">
-        <v>358</v>
+        <v>270</v>
       </c>
       <c r="D163">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E163">
-        <v>1010</v>
+        <v>908011</v>
       </c>
       <c r="F163" t="str">
-        <v>חתיכות פילה דג הרינג מלוח מצונן200 ג'</v>
+        <v>DADU ('יח 5) 'ג250-325 קרימוש גלידות צידנית</v>
       </c>
       <c r="G163" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H163">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B164">
-        <v>359</v>
+        <v>257</v>
       </c>
       <c r="C164">
-        <v>359</v>
+        <v>271</v>
       </c>
       <c r="D164">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E164">
-        <v>1009</v>
+        <v>908012</v>
       </c>
       <c r="F164" t="str">
-        <v>חתיכות פילה הרינג מלוח מצונן עם תבלין200 ג'</v>
+        <v>(100) הונגרית קוביה</v>
       </c>
       <c r="G164" t="str">
-        <v>SANTA BREMOR דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H164">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B165">
-        <v>356</v>
+        <v>258</v>
       </c>
       <c r="C165">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="D165">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E165">
-        <v>1126</v>
+        <v>908013</v>
       </c>
       <c r="F165" t="str">
-        <v xml:space="preserve">סלט איקרה ורודה 900 גרםNP </v>
+        <v>מגנטים 8 כולל מ"ס205X66 למקרר כיסוי</v>
       </c>
       <c r="G165" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H165">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B166">
-        <v>357</v>
+        <v>259</v>
       </c>
       <c r="C166">
-        <v>352</v>
+        <v>273</v>
       </c>
       <c r="D166">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E166">
-        <v>1127</v>
+        <v>908014</v>
       </c>
       <c r="F166" t="str">
-        <v xml:space="preserve">סלט איקרה עם פורל וסלמון מעושנים 900 גרםNP </v>
+        <v>סטריפ</v>
       </c>
       <c r="G166" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H166">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>דגים</v>
+        <v>חלבי</v>
       </c>
       <c r="B167">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="C167">
-        <v>354</v>
+        <v>274</v>
       </c>
       <c r="D167">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E167">
-        <v>1125</v>
+        <v>908015</v>
       </c>
       <c r="F167" t="str">
-        <v xml:space="preserve">סלט איקרה לבנה 900 גרםNP </v>
+        <v>מקודד</v>
       </c>
       <c r="G167" t="str">
-        <v>NORD PORT דגים</v>
+        <v>סטנד</v>
       </c>
       <c r="H167">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B168">
-        <v>401</v>
+        <v>261</v>
       </c>
       <c r="C168">
-        <v>409</v>
+        <v>275</v>
       </c>
       <c r="D168">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E168">
-        <v>1112</v>
+        <v>908016</v>
       </c>
       <c r="F168" t="str">
-        <v>‬שבבי דיונון בטעם סרטן מבושל,מיובש ומומלח90 ג(50)'‭</v>
+        <v>(50) ברמור סנטה לבנה צידנית</v>
       </c>
       <c r="G168" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H168">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B169">
-        <v>402</v>
+        <v>262</v>
       </c>
       <c r="C169">
-        <v>410</v>
+        <v>276</v>
       </c>
       <c r="D169">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="E169">
-        <v>1113</v>
+        <v>908017</v>
       </c>
       <c r="F169" t="str">
-        <v>‬שבבי קלמר מיובש ומומלח90 ג(50)'‭</v>
+        <v>(50) פורט נורד לבנה צידנית</v>
       </c>
       <c r="G169" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H169">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B170">
-        <v>403</v>
+        <v>263</v>
       </c>
       <c r="C170">
-        <v>411</v>
+        <v>277</v>
       </c>
       <c r="D170">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="E170">
-        <v>1114</v>
+        <v>908018</v>
       </c>
       <c r="F170" t="str">
-        <v>‬רצועות קלמר מיובש ומומלח בטעם סרטן90 ג(50)'‭</v>
+        <v>(50) קרימוש לבנה צידנית</v>
       </c>
       <c r="G170" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H170">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B171">
-        <v>404</v>
+        <v>264</v>
       </c>
       <c r="C171">
-        <v>412</v>
+        <v>278</v>
       </c>
       <c r="D171">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="E171">
-        <v>1115</v>
+        <v>908032</v>
       </c>
       <c r="F171" t="str">
-        <v>‬רצועות קלמר מעושן מיובש ומומלח90 ג(50)'‭</v>
+        <v>PUSHER NORD PORT דחפן</v>
       </c>
       <c r="G171" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H171">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B172">
-        <v>405</v>
+        <v>265</v>
       </c>
       <c r="C172">
-        <v>413</v>
+        <v>279</v>
       </c>
       <c r="D172">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E172">
-        <v>1116</v>
+        <v>908033</v>
       </c>
       <c r="F172" t="str">
-        <v>‬רצועות קלמר מיובש ומומלח עם פלפל צ'ילי90 ג(50)'‭</v>
+        <v>PUSHER MATIES דחפן</v>
       </c>
       <c r="G172" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H172">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B173">
-        <v>406</v>
+        <v>266</v>
       </c>
       <c r="C173">
-        <v>414</v>
+        <v>280</v>
       </c>
       <c r="D173">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E173">
-        <v>1117</v>
+        <v>908034</v>
       </c>
       <c r="F173" t="str">
-        <v>‬פרוסות דג שיבוט אלבין מיובש ומומלח100 ג(50)'‭</v>
+        <v>RELS מ"ס 90 מסילה</v>
       </c>
       <c r="G173" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H173">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>דג יבש</v>
+        <v>חלבי</v>
       </c>
       <c r="B174">
-        <v>407</v>
+        <v>267</v>
       </c>
       <c r="C174">
-        <v>415</v>
+        <v>281</v>
       </c>
       <c r="D174">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="E174">
-        <v>1118</v>
+        <v>908035</v>
       </c>
       <c r="F174" t="str">
-        <v>‬פרוסות דג שיבוט אלבין מיובש עם צ'ילי100 ג(50)'‭</v>
+        <v>PUSHER PRESIDENT דחפן</v>
       </c>
       <c r="G174" t="str">
-        <v>דגים פודסטוק</v>
+        <v>סטנד</v>
       </c>
       <c r="H174">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B175">
-        <v>408</v>
+        <v>301</v>
       </c>
       <c r="C175">
-        <v>416</v>
+        <v>316</v>
       </c>
       <c r="D175">
         <v>16</v>
       </c>
-      <c r="E175">
-        <v>1119</v>
+      <c r="E175" t="str">
+        <v>403001</v>
       </c>
       <c r="F175" t="str">
-        <v>‬פרוסות דג שיבוט אלבין מיובש ומומלח ללא עור90 ג(50)'‭</v>
+        <v>NP(10) גרם100 מצונן פרוס מעושן סלמון פילה</v>
       </c>
       <c r="G175" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H175">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B176">
-        <v>409</v>
+        <v>302</v>
       </c>
       <c r="C176">
-        <v>422</v>
+        <v>314</v>
       </c>
       <c r="D176">
-        <v>22</v>
-      </c>
-      <c r="E176">
-        <v>1105</v>
+        <v>14</v>
+      </c>
+      <c r="E176" t="str">
+        <v>403002</v>
       </c>
       <c r="F176" t="str">
-        <v>‬ (287)BAR CHILIדג ברקודה צ'ילי מלוח100 ג(52)'חום‭</v>
+        <v>NP(10) גרם100 מצונן פרוס מעושן פורל פילה</v>
       </c>
       <c r="G176" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H176">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B177">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="C177">
-        <v>423</v>
+        <v>312</v>
       </c>
       <c r="D177">
-        <v>23</v>
-      </c>
-      <c r="E177">
-        <v>1102</v>
+        <v>12</v>
+      </c>
+      <c r="E177" t="str">
+        <v>403003</v>
       </c>
       <c r="F177" t="str">
-        <v>‬ 256)IMPERATOR)דג צנינית צהובה פסים מלוח100 ג(52)'תכלת‭</v>
+        <v>NP(9) גרם250 מצונן פרוס מעושן סלמון פילה</v>
       </c>
       <c r="G177" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H177">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B178">
-        <v>411</v>
+        <v>304</v>
       </c>
       <c r="C178">
-        <v>424</v>
+        <v>311</v>
       </c>
       <c r="D178">
-        <v>24</v>
-      </c>
-      <c r="E178">
-        <v>1104</v>
+        <v>11</v>
+      </c>
+      <c r="E178" t="str">
+        <v>403004</v>
       </c>
       <c r="F178" t="str">
-        <v>‬ 270)BARAKUDA)דג ברקודה  מיובש100 ג(52)'כתום‭</v>
+        <v>NP(9) גרם250 מצונן פרוס מעושן פורל פילה</v>
       </c>
       <c r="G178" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H178">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B179">
-        <v>412</v>
+        <v>305</v>
       </c>
       <c r="C179">
-        <v>425</v>
+        <v>315</v>
       </c>
       <c r="D179">
-        <v>25</v>
-      </c>
-      <c r="E179">
-        <v>1101</v>
+        <v>15</v>
+      </c>
+      <c r="E179" t="str">
+        <v>403005</v>
       </c>
       <c r="F179" t="str">
-        <v>‬ 232)POLOSATIK)דג צנינון הכתם מיובש100 ג(52)'סגול‭</v>
+        <v>NP(5) גרם200 מצונן מעושן סלמון פילה</v>
       </c>
       <c r="G179" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H179">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B180">
-        <v>413</v>
+        <v>306</v>
       </c>
       <c r="C180">
-        <v>426</v>
+        <v>313</v>
       </c>
       <c r="D180">
-        <v>26</v>
-      </c>
-      <c r="E180">
-        <v>1100</v>
+        <v>13</v>
+      </c>
+      <c r="E180" t="str">
+        <v>403006</v>
       </c>
       <c r="F180" t="str">
-        <v>‬ 218)BALICHOK)דג צנינון הכתם מיובש100 ג(52)'אפור‭</v>
+        <v>NP(5) גרם200 מצונן מעושן פורל פילה</v>
       </c>
       <c r="G180" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H180">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B181">
-        <v>414</v>
+        <v>307</v>
       </c>
       <c r="C181">
-        <v>427</v>
+        <v>309</v>
       </c>
       <c r="D181">
-        <v>27</v>
-      </c>
-      <c r="E181">
-        <v>714</v>
+        <v>9</v>
+      </c>
+      <c r="E181" t="str">
+        <v>403007</v>
       </c>
       <c r="F181" t="str">
-        <v>‬ 305)ANCHOVY)דג עפינית זוטר מיובש ומומלח120 ג(52)'‭</v>
+        <v>8) NP) גרם150 מצונן חם בעישון מומלח מקרל פילה</v>
       </c>
       <c r="G181" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H181">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B182">
-        <v>415</v>
+        <v>308</v>
       </c>
       <c r="C182">
-        <v>428</v>
+        <v>310</v>
       </c>
       <c r="D182">
-        <v>28</v>
-      </c>
-      <c r="E182">
-        <v>704</v>
+        <v>10</v>
+      </c>
+      <c r="E182" t="str">
+        <v>403008</v>
       </c>
       <c r="F182" t="str">
-        <v>דג צנינית צהובה פסים מלוח100 IMPERATOR ג'</v>
+        <v>8) NP) גרם150 גרוס שחור פלפל עם חם בעישון מומלח מקרל פילה</v>
       </c>
       <c r="G182" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT מצונן פורל/סלמון</v>
       </c>
       <c r="H182">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B183">
-        <v>416</v>
+        <v>309</v>
       </c>
       <c r="C183">
-        <v>429</v>
+        <v>328</v>
       </c>
       <c r="D183">
-        <v>29</v>
-      </c>
-      <c r="E183">
-        <v>701</v>
+        <v>28</v>
+      </c>
+      <c r="E183" t="str">
+        <v>1014</v>
       </c>
       <c r="F183" t="str">
-        <v>‬דג ברקודה מלוח מיובש100 (199)ג(52)'‭</v>
+        <v>(6)'ג260 מצונן מלוח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G183" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H183">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B184">
-        <v>417</v>
+        <v>310</v>
       </c>
       <c r="C184">
-        <v>430</v>
+        <v>329</v>
       </c>
       <c r="D184">
-        <v>30</v>
-      </c>
-      <c r="E184">
-        <v>713</v>
+        <v>29</v>
+      </c>
+      <c r="E184" t="str">
+        <v>1012</v>
       </c>
       <c r="F184" t="str">
-        <v>‬דג ברקודה עם צ'ילי מלוח מיובש100 (727)ג(52)'‭</v>
+        <v>(6)'ג260 בצל עם מצונן מלוח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G184" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H184">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B185">
-        <v>418</v>
+        <v>311</v>
       </c>
       <c r="C185">
-        <v>431</v>
+        <v>330</v>
       </c>
       <c r="D185">
-        <v>31</v>
-      </c>
-      <c r="E185">
-        <v>712</v>
+        <v>30</v>
+      </c>
+      <c r="E185" t="str">
+        <v>1013</v>
       </c>
       <c r="F185" t="str">
-        <v>‬דג צנינון הכתם מלוח מיובש100 (697)ג(52)'‭</v>
+        <v>(6)ג260 תבלין עם מצונן מלוח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G185" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H185">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B186">
-        <v>419</v>
+        <v>312</v>
       </c>
       <c r="C186">
-        <v>432</v>
+        <v>331</v>
       </c>
       <c r="D186">
-        <v>32</v>
-      </c>
-      <c r="E186">
-        <v>711</v>
+        <v>31</v>
+      </c>
+      <c r="E186" t="str">
+        <v>1049</v>
       </c>
       <c r="F186" t="str">
-        <v>‬דג צנינון הכתם מלוח מיובש100 (734)ג(52)'‭</v>
+        <v>(6)'ג260 מצונן מלוח סקנדינבי הרינג דג פילה חתיכות</v>
       </c>
       <c r="G186" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H186">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B187">
-        <v>420</v>
+        <v>313</v>
       </c>
       <c r="C187">
-        <v>438</v>
+        <v>332</v>
       </c>
       <c r="D187">
-        <v>38</v>
-      </c>
-      <c r="E187">
-        <v>1099</v>
+        <v>32</v>
+      </c>
+      <c r="E187" t="str">
+        <v>1106</v>
       </c>
       <c r="F187" t="str">
-        <v>‬דג צלופח מטוגן עם צ'ילי מלוח מיובש80 (991)ג(52)'‭</v>
+        <v>(6)'ג230 פורל דג כדורי אדום קוויאר בסגנון</v>
       </c>
       <c r="G187" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H187">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B188">
-        <v>421</v>
+        <v>314</v>
       </c>
       <c r="C188">
-        <v>446</v>
+        <v>333</v>
       </c>
       <c r="D188">
-        <v>46</v>
-      </c>
-      <c r="E188">
-        <v>1098</v>
+        <v>33</v>
+      </c>
+      <c r="E188" t="str">
+        <v>1107</v>
       </c>
       <c r="F188" t="str">
-        <v>דג צלופח מטוגן מלוח מיובש80ג'</v>
+        <v>(6)'ג230 פורל דג כדורי שחור קוויאר בסגנון</v>
       </c>
       <c r="G188" t="str">
-        <v>דגים פודסטוק</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H188">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B189">
-        <v>422</v>
+        <v>315</v>
       </c>
       <c r="C189">
-        <v>450</v>
+        <v>319</v>
       </c>
       <c r="D189">
-        <v>50</v>
-      </c>
-      <c r="E189">
-        <v>1103</v>
+        <v>19</v>
+      </c>
+      <c r="E189" t="str">
+        <v>1015</v>
       </c>
       <c r="F189" t="str">
-        <v xml:space="preserve"> TARANOCHKAדג אופירית מלוח מיובש100 ג'אדום</v>
+        <v>(6)'ג180 והרינג טרוטונית דג ביצי איקרה</v>
       </c>
       <c r="G189" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H189">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B190">
-        <v>433</v>
+        <v>316</v>
       </c>
       <c r="C190">
-        <v>451</v>
+        <v>317</v>
       </c>
       <c r="D190">
-        <v>51</v>
-      </c>
-      <c r="E190">
-        <v>715</v>
+        <v>17</v>
+      </c>
+      <c r="E190" t="str">
+        <v>1017</v>
       </c>
       <c r="F190" t="str">
-        <v>SHRIMPSחסילונים מיובשים ומומלחים80 ג'</v>
+        <v>(6)'ג180 וסלמון פורל עם והרינג טרוטונית דג ביצי איקרה</v>
       </c>
       <c r="G190" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H190">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B191">
-        <v>444</v>
+        <v>317</v>
       </c>
       <c r="C191">
-        <v>452</v>
+        <v>318</v>
       </c>
       <c r="D191">
-        <v>52</v>
-      </c>
-      <c r="E191">
-        <v>716</v>
+        <v>18</v>
+      </c>
+      <c r="E191" t="str">
+        <v>1018</v>
       </c>
       <c r="F191" t="str">
-        <v xml:space="preserve"> SHRIMPS CHILLIחסילונים מיובשים ומומלחים עם צ'ילי80 ג</v>
+        <v>(6)'ג180 חסילונים עם MOIVA טרוטונית דג ביצי</v>
       </c>
       <c r="G191" t="str">
-        <v>דגים פודסטוק</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H191">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B192">
-        <v>445</v>
+        <v>318</v>
       </c>
       <c r="C192">
-        <v>433</v>
+        <v>320</v>
       </c>
       <c r="D192">
-        <v>33</v>
-      </c>
-      <c r="E192">
-        <v>237</v>
+        <v>20</v>
+      </c>
+      <c r="E192" t="str">
+        <v>1109</v>
       </c>
       <c r="F192" t="str">
-        <v>רצועות פילה דג לש 'מיובש100 RUSSIA ג'</v>
+        <v>"איקרה ביצי דג טרוטונית והרינג עם אבקדו</v>
       </c>
       <c r="G192" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>פורל וסלמון180 ג'"</v>
       </c>
       <c r="H192">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B193">
-        <v>446</v>
+        <v>319</v>
       </c>
       <c r="C193">
-        <v>434</v>
+        <v>321</v>
       </c>
       <c r="D193">
-        <v>34</v>
-      </c>
-      <c r="E193">
-        <v>239</v>
+        <v>21</v>
+      </c>
+      <c r="E193" t="str">
+        <v>1122</v>
       </c>
       <c r="F193" t="str">
-        <v>רצועות פילה דג סום מיובש100 RUSSIA ג'</v>
+        <v>NP(6) גרם 180 לבנה איקרה סלט</v>
       </c>
       <c r="G193" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H193">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B194">
-        <v>447</v>
+        <v>320</v>
       </c>
       <c r="C194">
-        <v>401</v>
+        <v>322</v>
       </c>
       <c r="D194">
-        <v>1</v>
-      </c>
-      <c r="E194">
-        <v>721</v>
+        <v>22</v>
+      </c>
+      <c r="E194" t="str">
+        <v>1123</v>
       </c>
       <c r="F194" t="str">
-        <v>‬דג וובלה מיובש‭</v>
+        <v>NP(6) גרם 180 ורודה איקרה סלט</v>
       </c>
       <c r="G194" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H194">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B195">
-        <v>448</v>
+        <v>321</v>
       </c>
       <c r="C195">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="D195">
-        <v>2</v>
-      </c>
-      <c r="E195">
-        <v>717</v>
+        <v>23</v>
+      </c>
+      <c r="E195" t="str">
+        <v>1124</v>
       </c>
       <c r="F195" t="str">
-        <v>‬דג לש 'מיובש‭</v>
+        <v>NP(6) גרם 180 מעושנים וסלמון פורל עם איקרה סלט</v>
       </c>
       <c r="G195" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H195">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B196">
-        <v>449</v>
+        <v>322</v>
       </c>
       <c r="C196">
-        <v>403</v>
+        <v>334</v>
       </c>
       <c r="D196">
-        <v>3</v>
-      </c>
-      <c r="E196">
-        <v>724</v>
+        <v>34</v>
+      </c>
+      <c r="E196" t="str">
+        <v>1005</v>
       </c>
       <c r="F196" t="str">
-        <v>‬דג לש 'מעושן‭</v>
+        <v>(6)'ג400 מצונן בשמן מלוח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G196" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H196">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B197">
-        <v>450</v>
+        <v>323</v>
       </c>
       <c r="C197">
-        <v>404</v>
+        <v>335</v>
       </c>
       <c r="D197">
-        <v>4</v>
-      </c>
-      <c r="E197">
-        <v>719</v>
+        <v>35</v>
+      </c>
+      <c r="E197" t="str">
+        <v>1047</v>
       </c>
       <c r="F197" t="str">
-        <v>‬דג סודאק מיובש‭</v>
+        <v>(6)'ג400 בשמן מלוח מתובל הרינג דג פילה חתיכות</v>
       </c>
       <c r="G197" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H197">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B198">
-        <v>451</v>
+        <v>324</v>
       </c>
       <c r="C198">
-        <v>405</v>
+        <v>336</v>
       </c>
       <c r="D198">
-        <v>5</v>
-      </c>
-      <c r="E198">
-        <v>725</v>
+        <v>36</v>
+      </c>
+      <c r="E198" t="str">
+        <v>1048</v>
       </c>
       <c r="F198" t="str">
-        <v>‬דג צ'חון מעושן‭</v>
+        <v>(6)'ג400 בשמן מלוח סקנדינבי הרינג דג פילה חתיכות</v>
       </c>
       <c r="G198" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H198">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B199">
-        <v>452</v>
+        <v>325</v>
       </c>
       <c r="C199">
-        <v>406</v>
+        <v>337</v>
       </c>
       <c r="D199">
-        <v>6</v>
-      </c>
-      <c r="E199">
-        <v>726</v>
+        <v>37</v>
+      </c>
+      <c r="E199" t="str">
+        <v>400001</v>
       </c>
       <c r="F199" t="str">
-        <v>‬דג צ'חון מיובש‭</v>
+        <v>"6)NP)ג500  ""פרובינציאל"" מצונן וזיתים בצל עם הרינג פילה נתחי"</v>
       </c>
       <c r="G199" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H199">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B200">
-        <v>453</v>
+        <v>326</v>
       </c>
       <c r="C200">
-        <v>407</v>
+        <v>338</v>
       </c>
       <c r="D200">
-        <v>7</v>
-      </c>
-      <c r="E200">
-        <v>727</v>
+        <v>38</v>
+      </c>
+      <c r="E200" t="str">
+        <v>400002</v>
       </c>
       <c r="F200" t="str">
-        <v>‬דג ז'אריך מיובש‭</v>
+        <v>6)NP)ג520  מצונן בצל עם כבוש הרינג פילה נתחי</v>
       </c>
       <c r="G200" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H200">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B201">
-        <v>454</v>
+        <v>327</v>
       </c>
       <c r="C201">
-        <v>408</v>
+        <v>339</v>
       </c>
       <c r="D201">
-        <v>8</v>
-      </c>
-      <c r="E201">
-        <v>728</v>
+        <v>39</v>
+      </c>
+      <c r="E201" t="str">
+        <v>400003</v>
       </c>
       <c r="F201" t="str">
-        <v>‬דג ז'אריך מעושן‭</v>
+        <v>6)NP)ג500 מצונן בשמן שמיר עם מומלח הרינג פילה נתחי</v>
       </c>
       <c r="G201" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H201">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B202">
-        <v>455</v>
+        <v>328</v>
       </c>
       <c r="C202">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="D202">
-        <v>44</v>
-      </c>
-      <c r="E202">
-        <v>722</v>
+        <v>24</v>
+      </c>
+      <c r="E202" t="str">
+        <v>1166</v>
       </c>
       <c r="F202" t="str">
-        <v>דג פילה סום מעושן</v>
+        <v>(6)'ג500 (NP) מצונן בשמן מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G202" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H202">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B203">
-        <v>456</v>
+        <v>329</v>
       </c>
       <c r="C203">
-        <v>449</v>
+        <v>325</v>
       </c>
       <c r="D203">
-        <v>49</v>
-      </c>
-      <c r="E203">
-        <v>720</v>
+        <v>25</v>
+      </c>
+      <c r="E203" t="str">
+        <v>1167</v>
       </c>
       <c r="F203" t="str">
-        <v>דג זאב מים מיובש</v>
+        <v>(6)ג500 (NP) מצונן בשמן מומלח סקנדינבי הרינג דג פילה חתיכות</v>
       </c>
       <c r="G203" t="str">
-        <v>דגיםKAZAHSTAN</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H203">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B204">
-        <v>457</v>
+        <v>330</v>
       </c>
       <c r="C204">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D204">
-        <v>19</v>
-      </c>
-      <c r="E204">
-        <v>245</v>
+        <v>26</v>
+      </c>
+      <c r="E204" t="str">
+        <v>1168</v>
       </c>
       <c r="F204" t="str">
-        <v xml:space="preserve">דג צ'חון מיובשRUSSIA </v>
+        <v>(6)ג500 (NP) תבלין עם מצונן בשמן מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G204" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H204">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B205">
-        <v>458</v>
+        <v>331</v>
       </c>
       <c r="C205">
-        <v>420</v>
+        <v>340</v>
       </c>
       <c r="D205">
-        <v>20</v>
-      </c>
-      <c r="E205">
-        <v>246</v>
+        <v>40</v>
+      </c>
+      <c r="E205" t="str">
+        <v>1011</v>
       </c>
       <c r="F205" t="str">
-        <v xml:space="preserve">דג ז'אריך מיובשRUSSIA </v>
+        <v>(10)'ג250 מצונן מלוח הרינג דג פילה</v>
       </c>
       <c r="G205" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H205">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B206">
-        <v>459</v>
+        <v>332</v>
       </c>
       <c r="C206">
-        <v>421</v>
+        <v>327</v>
       </c>
       <c r="D206">
-        <v>21</v>
-      </c>
-      <c r="E206">
-        <v>247</v>
+        <v>27</v>
+      </c>
+      <c r="E206" t="str">
+        <v>1120</v>
       </c>
       <c r="F206" t="str">
-        <v xml:space="preserve">דג לש" 'טושקה "מיובשRUSSIA </v>
+        <v>(10)'ג250 מצונן מלוח סקנדינבי הרינג דג פילה</v>
       </c>
       <c r="G206" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H206">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B207">
-        <v>460</v>
+        <v>333</v>
       </c>
       <c r="C207">
-        <v>435</v>
+        <v>341</v>
       </c>
       <c r="D207">
-        <v>35</v>
-      </c>
-      <c r="E207">
-        <v>240</v>
+        <v>41</v>
+      </c>
+      <c r="E207" t="str">
+        <v>1165</v>
       </c>
       <c r="F207" t="str">
-        <v xml:space="preserve">דג קרסנופיורקה מיובשRUSSIA </v>
+        <v>(6)'ג400 (NP) מצונן בשמן מומלח הרינג דג פילה</v>
       </c>
       <c r="G207" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H207">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B208">
-        <v>461</v>
+        <v>334</v>
       </c>
       <c r="C208">
-        <v>436</v>
+        <v>342</v>
       </c>
       <c r="D208">
-        <v>36</v>
-      </c>
-      <c r="E208">
-        <v>241</v>
+        <v>42</v>
+      </c>
+      <c r="E208" t="str">
+        <v>1157</v>
       </c>
       <c r="F208" t="str">
-        <v xml:space="preserve">דג לש 'מיובשRUSSIA </v>
+        <v>(6)'ג400 (NP) בשמן (קצוץ) הרינג פילה</v>
       </c>
       <c r="G208" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H208">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B209">
-        <v>462</v>
+        <v>335</v>
       </c>
       <c r="C209">
-        <v>437</v>
+        <v>343</v>
       </c>
       <c r="D209">
-        <v>37</v>
-      </c>
-      <c r="E209">
-        <v>242</v>
+        <v>43</v>
+      </c>
+      <c r="E209" t="str">
+        <v>1000</v>
       </c>
       <c r="F209" t="str">
-        <v xml:space="preserve">דג וובלה מיובשRUSSIA </v>
+        <v>(NP (3 'ג1200 מצונן בשמן מומלח הרינג דג פילה</v>
       </c>
       <c r="G209" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H209">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B210">
-        <v>463</v>
+        <v>336</v>
       </c>
       <c r="C210">
-        <v>445</v>
+        <v>344</v>
       </c>
       <c r="D210">
-        <v>45</v>
-      </c>
-      <c r="E210">
-        <v>238</v>
+        <v>44</v>
+      </c>
+      <c r="E210" t="str">
+        <v>1001</v>
       </c>
       <c r="F210" t="str">
-        <v>רצועות פילה דג ש'יוקה מיובש100 RUSSIA ג'</v>
+        <v>פילה דג הרינג  סקנדינבי מומלח בשמן מצונן1200 ג3) NP) '</v>
       </c>
       <c r="G210" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H210">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B211">
-        <v>464</v>
+        <v>337</v>
       </c>
       <c r="C211">
-        <v>447</v>
+        <v>345</v>
       </c>
       <c r="D211">
-        <v>47</v>
-      </c>
-      <c r="E211">
-        <v>244</v>
+        <v>45</v>
+      </c>
+      <c r="E211" t="str">
+        <v>1002</v>
       </c>
       <c r="F211" t="str">
-        <v xml:space="preserve">דג ש'יוקה מיובשRUSSIA </v>
+        <v>3) NP)'ג1200 מצונן בשמן מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G211" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H211">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>דג יבש</v>
+        <v>דגים</v>
       </c>
       <c r="B212">
-        <v>465</v>
+        <v>338</v>
       </c>
       <c r="C212">
-        <v>448</v>
+        <v>346</v>
       </c>
       <c r="D212">
-        <v>48</v>
-      </c>
-      <c r="E212">
-        <v>243</v>
+        <v>46</v>
+      </c>
+      <c r="E212" t="str">
+        <v>1004</v>
       </c>
       <c r="F212" t="str">
-        <v xml:space="preserve">דג סודאק מיובשRUSSIA </v>
+        <v>3) NP)'ג1200 מצונן בשמן מומלח סקנדינבי הרינג דג פילה חתיכות</v>
       </c>
       <c r="G212" t="str">
-        <v>דגיםRUSSIA</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H212">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B213">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="C213">
-        <v>261</v>
+        <v>370</v>
       </c>
       <c r="D213">
-        <v>61</v>
-      </c>
-      <c r="E213">
-        <v>908001</v>
+        <v>70</v>
+      </c>
+      <c r="E213" t="str">
+        <v>1174</v>
       </c>
       <c r="F213" t="str">
-        <v>(82X180) גדול צדדי דו סטנד</v>
+        <v>(6)'ג300 מצונן בשמן XXL מומלח הרינג דג פילה</v>
       </c>
       <c r="G213" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H213">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B214">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="C214">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="D214">
-        <v>62</v>
-      </c>
-      <c r="E214">
-        <v>908002</v>
+        <v>68</v>
+      </c>
+      <c r="E214" t="str">
+        <v>1019</v>
       </c>
       <c r="F214" t="str">
-        <v>(56X180) בינוני צדדי דו סטנד</v>
+        <v>(12)'ג130 מצונן מומלח MINTAY זהבנון דג ביצי</v>
       </c>
       <c r="G214" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H214">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B215">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="C215">
-        <v>263</v>
+        <v>369</v>
       </c>
       <c r="D215">
-        <v>63</v>
-      </c>
-      <c r="E215">
-        <v>908003</v>
+        <v>69</v>
+      </c>
+      <c r="E215" t="str">
+        <v>1020</v>
       </c>
       <c r="F215" t="str">
-        <v>(50X168) קיר רשת</v>
+        <v>(12)'ג130 מצונן מומלח TRESKA שיבוט דג ביצי</v>
       </c>
       <c r="G215" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H215">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B216">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="C216">
-        <v>264</v>
+        <v>367</v>
       </c>
       <c r="D216">
-        <v>64</v>
-      </c>
-      <c r="E216">
-        <v>908004</v>
+        <v>67</v>
+      </c>
+      <c r="E216" t="str">
+        <v>1006</v>
       </c>
       <c r="F216" t="str">
-        <v>'סמ20 לרשת וו</v>
+        <v>(3)'ג1000 מצונן בשמן מומלח הרינג דג פילה</v>
       </c>
       <c r="G216" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H216">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B217">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="C217">
-        <v>265</v>
+        <v>366</v>
       </c>
       <c r="D217">
-        <v>65</v>
-      </c>
-      <c r="E217">
-        <v>908005</v>
+        <v>66</v>
+      </c>
+      <c r="E217" t="str">
+        <v>1175</v>
       </c>
       <c r="F217" t="str">
-        <v>(50X190) רשת סטנד</v>
+        <v>(3)'ג1000 מצונן בשמן מומלח סקנדינבי הרינג דג פילה</v>
       </c>
       <c r="G217" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H217">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B218">
-        <v>252</v>
+        <v>344</v>
       </c>
       <c r="C218">
-        <v>266</v>
+        <v>365</v>
       </c>
       <c r="D218">
-        <v>66</v>
-      </c>
-      <c r="E218">
-        <v>908006</v>
+        <v>65</v>
+      </c>
+      <c r="E218" t="str">
+        <v>1163</v>
       </c>
       <c r="F218" t="str">
-        <v>'סמ30 לרשת וו</v>
+        <v>(10)'ג150 (NP) מצונן בשמן מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G218" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H218">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B219">
-        <v>253</v>
+        <v>345</v>
       </c>
       <c r="C219">
-        <v>267</v>
+        <v>364</v>
       </c>
       <c r="D219">
-        <v>67</v>
-      </c>
-      <c r="E219">
-        <v>908007</v>
+        <v>64</v>
+      </c>
+      <c r="E219" t="str">
+        <v>1164</v>
       </c>
       <c r="F219" t="str">
-        <v>NORD PORT לוגו 12.5 מגשית</v>
+        <v>(10)'ג150 (NP) מצונן בשמן בצל עם מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G219" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H219">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B220">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="C220">
-        <v>268</v>
+        <v>363</v>
       </c>
       <c r="D220">
-        <v>68</v>
-      </c>
-      <c r="E220">
-        <v>908008</v>
+        <v>63</v>
+      </c>
+      <c r="E220" t="str">
+        <v>1055</v>
       </c>
       <c r="F220" t="str">
-        <v>SANTA BREMOR לוגו 12.5 מגשית</v>
+        <v>(12)'ג200 מוחמצות ים אצות סלט</v>
       </c>
       <c r="G220" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H220">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B221">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="C221">
-        <v>269</v>
+        <v>362</v>
       </c>
       <c r="D221">
-        <v>69</v>
-      </c>
-      <c r="E221">
-        <v>908010</v>
+        <v>62</v>
+      </c>
+      <c r="E221" t="str">
+        <v>1056</v>
       </c>
       <c r="F221" t="str">
-        <v>(55) 33X39X16.5 קירור צידנית</v>
+        <v>(12)'ג200 גזר עם ומתובלות מוחמצות ים אצות סלט</v>
       </c>
       <c r="G221" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H221">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B222">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="C222">
-        <v>270</v>
+        <v>361</v>
       </c>
       <c r="D222">
-        <v>70</v>
-      </c>
-      <c r="E222">
-        <v>908011</v>
+        <v>61</v>
+      </c>
+      <c r="E222" t="str">
+        <v>1057</v>
       </c>
       <c r="F222" t="str">
-        <v>DADU ('יח 5) 'ג250-325 קרימוש גלידות צידנית</v>
+        <v>(12)'ג200 מתוקה ופפריקה בצל עם מוחמצות ים אצות סלט</v>
       </c>
       <c r="G222" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H222">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B223">
-        <v>257</v>
+        <v>349</v>
       </c>
       <c r="C223">
-        <v>271</v>
+        <v>360</v>
       </c>
       <c r="D223">
-        <v>71</v>
-      </c>
-      <c r="E223">
-        <v>908012</v>
+        <v>60</v>
+      </c>
+      <c r="E223" t="str">
+        <v>1108</v>
       </c>
       <c r="F223" t="str">
-        <v>(100) הונגרית קוביה</v>
+        <v>(6)'ג150 וקה'צ-ים אצות סלט</v>
       </c>
       <c r="G223" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H223">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B224">
-        <v>258</v>
+        <v>350</v>
       </c>
       <c r="C224">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="D224">
-        <v>72</v>
-      </c>
-      <c r="E224">
-        <v>908013</v>
+        <v>48</v>
+      </c>
+      <c r="E224" t="str">
+        <v>1170</v>
       </c>
       <c r="F224" t="str">
-        <v>מגנטים 8 כולל מ"ס205X66 למקרר כיסוי</v>
+        <v>(6)'ג290 (NP) מצונן בשמן מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G224" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H224">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B225">
-        <v>259</v>
+        <v>351</v>
       </c>
       <c r="C225">
-        <v>273</v>
+        <v>350</v>
       </c>
       <c r="D225">
-        <v>73</v>
-      </c>
-      <c r="E225">
-        <v>908014</v>
+        <v>50</v>
+      </c>
+      <c r="E225" t="str">
+        <v>1171</v>
       </c>
       <c r="F225" t="str">
-        <v>סטריפ</v>
+        <v>(6)'ג290 (NP) בצל עם מצונן בשמן מומלח הרינג דג פילה חתיכות</v>
       </c>
       <c r="G225" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H225">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B226">
-        <v>260</v>
+        <v>352</v>
       </c>
       <c r="C226">
-        <v>274</v>
+        <v>351</v>
       </c>
       <c r="D226">
-        <v>74</v>
-      </c>
-      <c r="E226">
-        <v>908015</v>
+        <v>51</v>
+      </c>
+      <c r="E226" t="str">
+        <v>1172</v>
       </c>
       <c r="F226" t="str">
-        <v>מקודד</v>
+        <v>חתיכות פילה דג הרינג מומלח בשמן מצונן עם תבלין290 ג</v>
       </c>
       <c r="G226" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H226">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B227">
-        <v>261</v>
+        <v>353</v>
       </c>
       <c r="C227">
-        <v>275</v>
+        <v>349</v>
       </c>
       <c r="D227">
-        <v>75</v>
-      </c>
-      <c r="E227">
-        <v>908016</v>
+        <v>49</v>
+      </c>
+      <c r="E227" t="str">
+        <v>1173</v>
       </c>
       <c r="F227" t="str">
-        <v>(50) ברמור סנטה לבנה צידנית</v>
+        <v>חתיכות פילה דג הרינג סקנדינבי מומלח בשמן מצונן290 ג</v>
       </c>
       <c r="G227" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H227">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B228">
-        <v>262</v>
+        <v>354</v>
       </c>
       <c r="C228">
-        <v>276</v>
+        <v>354</v>
       </c>
       <c r="D228">
-        <v>76</v>
-      </c>
-      <c r="E228">
-        <v>908017</v>
+        <v>54</v>
+      </c>
+      <c r="E228" t="str">
+        <v>1125</v>
       </c>
       <c r="F228" t="str">
-        <v>(50) פורט נורד לבנה צידנית</v>
+        <v>סלט איקרה לבנה 900 גרםNP</v>
       </c>
       <c r="G228" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H228">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B229">
-        <v>263</v>
+        <v>355</v>
       </c>
       <c r="C229">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="D229">
-        <v>77</v>
-      </c>
-      <c r="E229">
-        <v>908018</v>
+        <v>53</v>
+      </c>
+      <c r="E229" t="str">
+        <v>1126</v>
       </c>
       <c r="F229" t="str">
-        <v>(50) קרימוש לבנה צידנית</v>
+        <v>NP(8) גרם 900 ורודה איקרה סלט</v>
       </c>
       <c r="G229" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H229">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B230">
-        <v>264</v>
+        <v>356</v>
       </c>
       <c r="C230">
-        <v>278</v>
+        <v>352</v>
       </c>
       <c r="D230">
-        <v>78</v>
-      </c>
-      <c r="E230">
-        <v>908032</v>
+        <v>52</v>
+      </c>
+      <c r="E230" t="str">
+        <v>1127</v>
       </c>
       <c r="F230" t="str">
-        <v>PUSHER NORD PORT דחפן</v>
+        <v>NP(8) גרם 900 מעושנים וסלמון פורל עם איקרה סלט</v>
       </c>
       <c r="G230" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H230">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B231">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="C231">
-        <v>279</v>
+        <v>358</v>
       </c>
       <c r="D231">
-        <v>79</v>
-      </c>
-      <c r="E231">
-        <v>908033</v>
+        <v>58</v>
+      </c>
+      <c r="E231" t="str">
+        <v>1010</v>
       </c>
       <c r="F231" t="str">
-        <v>PUSHER MATIES דחפן</v>
+        <v>חתיכות פילה דג הרינג מלוח מצונן200 ג'</v>
       </c>
       <c r="G231" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H231">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B232">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="C232">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="D232">
-        <v>80</v>
-      </c>
-      <c r="E232">
-        <v>908034</v>
+        <v>59</v>
+      </c>
+      <c r="E232" t="str">
+        <v>1009</v>
       </c>
       <c r="F232" t="str">
-        <v>RELS מ"ס 90 מסילה</v>
+        <v>חתיכות פילה הרינג מלוח מצונן עם תבלין200 ג'</v>
       </c>
       <c r="G232" t="str">
-        <v>סטנד</v>
+        <v>SANTA BREMOR דגים</v>
       </c>
       <c r="H232">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>חלבי</v>
+        <v>דגים</v>
       </c>
       <c r="B233">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="C233">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="D233">
-        <v>81</v>
-      </c>
-      <c r="E233">
-        <v>908035</v>
+        <v>47</v>
+      </c>
+      <c r="E233" t="str">
+        <v>400004</v>
       </c>
       <c r="F233" t="str">
-        <v>PUSHER PRESIDENT דחפן</v>
+        <v>"6)NP) גרם270 ""פארשמאק"" קצוץ הרינג סלט"</v>
       </c>
       <c r="G233" t="str">
-        <v>סטנד</v>
+        <v>NORD PORT דגים</v>
       </c>
       <c r="H233">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
